--- a/Översikt HÄRNÖSAND.xlsx
+++ b/Översikt HÄRNÖSAND.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45328</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>46044</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 18689-2025</t>
+          <t>A 47711-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45763</v>
+        <v>45588</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1008,25 +1008,20 @@
           <t>HÄRNÖSAND</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I5" t="n">
-        <v>12.2</v>
+        <v>39.5</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1038,21 +1033,153 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
       </c>
       <c r="T5" t="n">
+        <v>49</v>
+      </c>
+      <c r="U5" t="n">
+        <v>35</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Dropptaggsvamp
+Motaggsvamp
+Orange taggsvamp
+Rosenticka
+Svartvit taggsvamp
+Tallticka
+Tretåig hackspett
+Ullticka
+Violettgrå tagellav
+Bronshjon
+Nästlav
+Vedticka
+Kötticka
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 47711-2024 artfynd.xlsx", "A 47711-2024")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 47711-2024 karta.png", "A 47711-2024")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 47711-2024 georefererad karta.tif", "A 47711-2024")</f>
+        <v/>
+      </c>
+      <c r="Z5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/knärot/A 47711-2024 karta knärot.png", "A 47711-2024")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 47711-2024 FSC-klagomål.docx", "A 47711-2024")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 47711-2024 FSC-klagomål mail.docx", "A 47711-2024")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 47711-2024 tillsynsbegäran.docx", "A 47711-2024")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 47711-2024 tillsynsbegäran mail.docx", "A 47711-2024")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/fåglar/A 47711-2024 prioriterade fågelarter.docx", "A 47711-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 18689-2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45763</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HÄRNÖSAND</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>8</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="n">
         <v>28</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>20</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -1071,120 +1198,120 @@
 Nattviol</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 18689-2025 artfynd.xlsx", "A 18689-2025")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 18689-2025 karta.png", "A 18689-2025")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 18689-2025 georefererad karta.tif", "A 18689-2025")</f>
         <v/>
       </c>
-      <c r="Z5">
+      <c r="Z6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/knärot/A 18689-2025 karta knärot.png", "A 18689-2025")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 18689-2025 FSC-klagomål.docx", "A 18689-2025")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 18689-2025 FSC-klagomål mail.docx", "A 18689-2025")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 18689-2025 tillsynsbegäran.docx", "A 18689-2025")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 18689-2025 tillsynsbegäran mail.docx", "A 18689-2025")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/fåglar/A 18689-2025 prioriterade fågelarter.docx", "A 18689-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 18563-2022</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
         <v>44686</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46284</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTERNORRLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>HÄRNÖSAND</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="E7" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HÄRNÖSAND</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I7" t="n">
         <v>17.5</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K7" t="n">
         <v>7</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L7" t="n">
         <v>6</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M7" t="n">
         <v>1</v>
       </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>7</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R7" t="n">
         <v>1</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S7" t="n">
         <v>14</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T7" t="n">
         <v>73</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>4</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Lunglav
@@ -1202,112 +1329,112 @@
 Vedticka</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 18563-2022 artfynd.xlsx", "A 18563-2022")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 18563-2022 karta.png", "A 18563-2022")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 18563-2022 georefererad karta.tif", "A 18563-2022")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 18563-2022 FSC-klagomål.docx", "A 18563-2022")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 18563-2022 FSC-klagomål mail.docx", "A 18563-2022")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 18563-2022 tillsynsbegäran.docx", "A 18563-2022")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 18563-2022 tillsynsbegäran mail.docx", "A 18563-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>A 49355-2025</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
         <v>45938</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46284</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTERNORRLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HÄRNÖSAND</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="E8" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HÄRNÖSAND</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="I8" t="n">
         <v>10.3</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J8" t="n">
         <v>3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K8" t="n">
         <v>3</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L8" t="n">
         <v>6</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M8" t="n">
         <v>4</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>10</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R8" t="n">
         <v>4</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S8" t="n">
         <v>14</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T8" t="n">
         <v>59</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>38</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -1325,120 +1452,120 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 49355-2025 artfynd.xlsx", "A 49355-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 49355-2025 karta.png", "A 49355-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 49355-2025 georefererad karta.tif", "A 49355-2025")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/knärot/A 49355-2025 karta knärot.png", "A 49355-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 49355-2025 FSC-klagomål.docx", "A 49355-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 49355-2025 FSC-klagomål mail.docx", "A 49355-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 49355-2025 tillsynsbegäran.docx", "A 49355-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 49355-2025 tillsynsbegäran mail.docx", "A 49355-2025")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/fåglar/A 49355-2025 prioriterade fågelarter.docx", "A 49355-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A 27496-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>46189</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46284</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTERNORRLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HÄRNÖSAND</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="E9" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HÄRNÖSAND</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="I9" t="n">
         <v>4.2</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J9" t="n">
         <v>3</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K9" t="n">
         <v>4</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L9" t="n">
         <v>5</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M9" t="n">
         <v>2</v>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>7</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R9" t="n">
         <v>2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S9" t="n">
         <v>14</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>17</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Aspfjädermossa
 Lappticka
@@ -1456,116 +1583,116 @@
 Utter</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 27496-2026 artfynd.xlsx", "A 27496-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 27496-2026 karta.png", "A 27496-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 27496-2026 georefererad karta.tif", "A 27496-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 27496-2026 FSC-klagomål.docx", "A 27496-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 27496-2026 FSC-klagomål mail.docx", "A 27496-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 27496-2026 tillsynsbegäran.docx", "A 27496-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 27496-2026 tillsynsbegäran mail.docx", "A 27496-2026")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/fåglar/A 27496-2026 prioriterade fågelarter.docx", "A 27496-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 38409-2024</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D10" s="1" t="n">
         <v>45546</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46284</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTERNORRLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>HÄRNÖSAND</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="E10" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÄRNÖSAND</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="I10" t="n">
         <v>7.7</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J10" t="n">
         <v>3</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K10" t="n">
         <v>2</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L10" t="n">
         <v>7</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M10" t="n">
         <v>3</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>10</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R10" t="n">
         <v>3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S10" t="n">
         <v>12</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>40</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>40</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -1581,120 +1708,120 @@
 Mörk husmossa</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 38409-2024 artfynd.xlsx", "A 38409-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 38409-2024 karta.png", "A 38409-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 38409-2024 georefererad karta.tif", "A 38409-2024")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="Z10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/knärot/A 38409-2024 karta knärot.png", "A 38409-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 38409-2024 FSC-klagomål.docx", "A 38409-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 38409-2024 FSC-klagomål mail.docx", "A 38409-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 38409-2024 tillsynsbegäran.docx", "A 38409-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 38409-2024 tillsynsbegäran mail.docx", "A 38409-2024")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/fåglar/A 38409-2024 prioriterade fågelarter.docx", "A 38409-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 14582-2024</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>45394</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46284</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTERNORRLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÄRNÖSAND</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="E11" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÄRNÖSAND</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="I11" t="n">
         <v>4.1</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>10</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M11" t="n">
         <v>1</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>11</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R11" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S11" t="n">
         <v>11</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>19</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>18</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Dvärgbägarlav
@@ -1709,116 +1836,116 @@
 Vedskivlav</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 14582-2024 artfynd.xlsx", "A 14582-2024")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 14582-2024 karta.png", "A 14582-2024")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 14582-2024 georefererad karta.tif", "A 14582-2024")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 14582-2024 FSC-klagomål.docx", "A 14582-2024")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 14582-2024 FSC-klagomål mail.docx", "A 14582-2024")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 14582-2024 tillsynsbegäran.docx", "A 14582-2024")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 14582-2024 tillsynsbegäran mail.docx", "A 14582-2024")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/fåglar/A 14582-2024 prioriterade fågelarter.docx", "A 14582-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 47485-2025</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46284</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTERNORRLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÄRNÖSAND</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="E12" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HÄRNÖSAND</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I12" t="n">
         <v>10.6</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" t="n">
         <v>2</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K12" t="n">
         <v>2</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L12" t="n">
         <v>6</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>7</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S12" t="n">
         <v>10</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T12" t="n">
         <v>15</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Lunglav
@@ -1832,120 +1959,120 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 47485-2025 artfynd.xlsx", "A 47485-2025")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 47485-2025 karta.png", "A 47485-2025")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 47485-2025 georefererad karta.tif", "A 47485-2025")</f>
         <v/>
       </c>
-      <c r="Z11">
+      <c r="Z12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/knärot/A 47485-2025 karta knärot.png", "A 47485-2025")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 47485-2025 FSC-klagomål.docx", "A 47485-2025")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 47485-2025 FSC-klagomål mail.docx", "A 47485-2025")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 47485-2025 tillsynsbegäran.docx", "A 47485-2025")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 47485-2025 tillsynsbegäran mail.docx", "A 47485-2025")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/fåglar/A 47485-2025 prioriterade fågelarter.docx", "A 47485-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 18695-2025</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>45763</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46284</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTERNORRLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HÄRNÖSAND</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="E13" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HÄRNÖSAND</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I13" t="n">
         <v>2.2</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>5</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L13" t="n">
         <v>3</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M13" t="n">
         <v>1</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>5</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R13" t="n">
         <v>1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S13" t="n">
         <v>10</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T13" t="n">
         <v>10</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Rynkskinn
@@ -1959,154 +2086,32 @@
 Vedticka</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 18695-2025 artfynd.xlsx", "A 18695-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 18695-2025 karta.png", "A 18695-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 18695-2025 georefererad karta.tif", "A 18695-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 18695-2025 FSC-klagomål.docx", "A 18695-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 18695-2025 FSC-klagomål mail.docx", "A 18695-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 18695-2025 tillsynsbegäran.docx", "A 18695-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 18695-2025 tillsynsbegäran mail.docx", "A 18695-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 47711-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45588</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46284</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTERNORRLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HÄRNÖSAND</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>7</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>8</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="n">
-        <v>27</v>
-      </c>
-      <c r="U13" t="n">
-        <v>13</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Dropptaggsvamp
-Kötticka
-Motaggsvamp
-Tallticka
-Tretåig hackspett
-Ullticka
-Violettgrå tagellav
-Nästlav
-Vedticka</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 47711-2024 artfynd.xlsx", "A 47711-2024")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 47711-2024 karta.png", "A 47711-2024")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 47711-2024 georefererad karta.tif", "A 47711-2024")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/knärot/A 47711-2024 karta knärot.png", "A 47711-2024")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 47711-2024 FSC-klagomål.docx", "A 47711-2024")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 47711-2024 FSC-klagomål mail.docx", "A 47711-2024")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 47711-2024 tillsynsbegäran.docx", "A 47711-2024")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 47711-2024 tillsynsbegäran mail.docx", "A 47711-2024")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/fåglar/A 47711-2024 prioriterade fågelarter.docx", "A 47711-2024")</f>
         <v/>
       </c>
     </row>
@@ -2130,7 +2135,7 @@
         <v>45805</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2252,7 +2257,7 @@
         <v>45484</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2374,7 +2379,7 @@
         <v>45139</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2487,7 +2492,7 @@
         <v>45335</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2603,7 +2608,7 @@
         <v>45826</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2715,7 +2720,7 @@
         <v>45616</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2832,7 +2837,7 @@
         <v>45082</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2948,7 +2953,7 @@
         <v>45027</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3063,7 +3068,7 @@
         <v>44874</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3178,7 +3183,7 @@
         <v>46183</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3288,7 +3293,7 @@
         <v>45352</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3406,7 +3411,7 @@
         <v>45957</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3520,7 +3525,7 @@
         <v>45188</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3638,7 +3643,7 @@
         <v>45593</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3752,7 +3757,7 @@
         <v>45593</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3866,7 +3871,7 @@
         <v>45548</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3975,7 +3980,7 @@
         <v>45567</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4089,7 +4094,7 @@
         <v>44979</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4207,7 +4212,7 @@
         <v>45477</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4315,7 +4320,7 @@
         <v>45314</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4428,7 +4433,7 @@
         <v>45971</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4541,7 +4546,7 @@
         <v>45513</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4654,7 +4659,7 @@
         <v>46176</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4767,7 +4772,7 @@
         <v>45560</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4880,7 +4885,7 @@
         <v>46251</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4993,7 +4998,7 @@
         <v>45848</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5106,7 +5111,7 @@
         <v>45323</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5223,7 +5228,7 @@
         <v>45790</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5336,7 +5341,7 @@
         <v>44686</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5452,7 +5457,7 @@
         <v>44755</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5559,7 +5564,7 @@
         <v>45617</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5671,7 +5676,7 @@
         <v>45526</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5783,7 +5788,7 @@
         <v>45930</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5895,7 +5900,7 @@
         <v>46003</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6011,7 +6016,7 @@
         <v>45182</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6123,7 +6128,7 @@
         <v>46244</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6239,7 +6244,7 @@
         <v>45596</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6351,7 +6356,7 @@
         <v>45322</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6458,7 +6463,7 @@
         <v>44664</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6564,7 +6569,7 @@
         <v>45618</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6675,7 +6680,7 @@
         <v>45376</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6786,7 +6791,7 @@
         <v>45930</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6901,7 +6906,7 @@
         <v>45910</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7012,7 +7017,7 @@
         <v>45575</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7118,7 +7123,7 @@
         <v>45967</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7229,7 +7234,7 @@
         <v>46141</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7335,7 +7340,7 @@
         <v>44874</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7446,7 +7451,7 @@
         <v>45513</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7557,7 +7562,7 @@
         <v>45267</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7668,7 +7673,7 @@
         <v>46244</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7779,7 +7784,7 @@
         <v>45847</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7894,7 +7899,7 @@
         <v>45996</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8005,7 +8010,7 @@
         <v>44676</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8110,7 +8115,7 @@
         <v>44585</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8215,7 +8220,7 @@
         <v>44655</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8320,7 +8325,7 @@
         <v>45554</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8425,7 +8430,7 @@
         <v>45456</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8535,7 +8540,7 @@
         <v>45008</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8640,7 +8645,7 @@
         <v>45583</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8749,7 +8754,7 @@
         <v>45355</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8854,7 +8859,7 @@
         <v>45350</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8964,7 +8969,7 @@
         <v>45649</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9069,7 +9074,7 @@
         <v>45919</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9179,7 +9184,7 @@
         <v>45352</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9289,7 +9294,7 @@
         <v>46031</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9398,7 +9403,7 @@
         <v>46176</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9508,7 +9513,7 @@
         <v>45276</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9613,7 +9618,7 @@
         <v>46189</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9718,7 +9723,7 @@
         <v>46191</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9828,7 +9833,7 @@
         <v>44559</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9933,7 +9938,7 @@
         <v>46184</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10042,7 +10047,7 @@
         <v>45372</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10152,7 +10157,7 @@
         <v>46127</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10257,7 +10262,7 @@
         <v>44837</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10362,7 +10367,7 @@
         <v>45428</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10472,7 +10477,7 @@
         <v>45805</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10586,7 +10591,7 @@
         <v>45805</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10691,7 +10696,7 @@
         <v>45811</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10796,7 +10801,7 @@
         <v>44874</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10869,7 +10874,7 @@
         <v>44664</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10942,7 +10947,7 @@
         <v>44806</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11015,7 +11020,7 @@
         <v>44846</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11093,7 +11098,7 @@
         <v>44532</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11166,7 +11171,7 @@
         <v>44875</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11239,7 +11244,7 @@
         <v>44477</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11312,7 +11317,7 @@
         <v>44608</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11385,7 +11390,7 @@
         <v>44720</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11458,7 +11463,7 @@
         <v>44600</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11536,7 +11541,7 @@
         <v>44824</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11609,7 +11614,7 @@
         <v>44487</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11682,7 +11687,7 @@
         <v>44734</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11755,7 +11760,7 @@
         <v>44512</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11828,7 +11833,7 @@
         <v>44517</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11906,7 +11911,7 @@
         <v>44728</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11984,7 +11989,7 @@
         <v>44477</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12057,7 +12062,7 @@
         <v>44475</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12130,7 +12135,7 @@
         <v>44476</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12203,7 +12208,7 @@
         <v>44664</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12276,7 +12281,7 @@
         <v>44804</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12349,7 +12354,7 @@
         <v>44512</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12422,7 +12427,7 @@
         <v>44503</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12495,7 +12500,7 @@
         <v>44735</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12568,7 +12573,7 @@
         <v>44581</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12641,7 +12646,7 @@
         <v>44848</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12714,7 +12719,7 @@
         <v>44469</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12787,7 +12792,7 @@
         <v>44672</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12860,7 +12865,7 @@
         <v>44652</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12933,7 +12938,7 @@
         <v>44515</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13006,7 +13011,7 @@
         <v>44664</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13079,7 +13084,7 @@
         <v>44616</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13152,7 +13157,7 @@
         <v>44496</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13225,7 +13230,7 @@
         <v>44532</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13298,7 +13303,7 @@
         <v>44571</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13371,7 +13376,7 @@
         <v>44512</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13444,7 +13449,7 @@
         <v>44664</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13517,7 +13522,7 @@
         <v>44536</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13590,7 +13595,7 @@
         <v>44522</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13663,7 +13668,7 @@
         <v>44585</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13736,7 +13741,7 @@
         <v>44792</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13809,7 +13814,7 @@
         <v>44641</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13882,7 +13887,7 @@
         <v>44747</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13955,7 +13960,7 @@
         <v>44858</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14028,7 +14033,7 @@
         <v>44881</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14106,7 +14111,7 @@
         <v>45334</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14179,7 +14184,7 @@
         <v>45209</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14257,7 +14262,7 @@
         <v>45667</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14330,7 +14335,7 @@
         <v>44617</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14403,7 +14408,7 @@
         <v>45576</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14481,7 +14486,7 @@
         <v>45314</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14554,7 +14559,7 @@
         <v>45462</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14627,7 +14632,7 @@
         <v>45762</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14700,7 +14705,7 @@
         <v>45293</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14773,7 +14778,7 @@
         <v>45496</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14846,7 +14851,7 @@
         <v>45231</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14919,7 +14924,7 @@
         <v>45281</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14992,7 +14997,7 @@
         <v>45405</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15065,7 +15070,7 @@
         <v>45126</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15138,7 +15143,7 @@
         <v>45352</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15216,7 +15221,7 @@
         <v>44853</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15289,7 +15294,7 @@
         <v>45558</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15362,7 +15367,7 @@
         <v>44809</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15435,7 +15440,7 @@
         <v>45757</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15508,7 +15513,7 @@
         <v>45228</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15581,7 +15586,7 @@
         <v>45300</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15654,7 +15659,7 @@
         <v>45350</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15732,7 +15737,7 @@
         <v>45628</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15805,7 +15810,7 @@
         <v>45482</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15883,7 +15888,7 @@
         <v>45106</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15961,7 +15966,7 @@
         <v>45531</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16034,7 +16039,7 @@
         <v>44853</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16107,7 +16112,7 @@
         <v>45289</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16180,7 +16185,7 @@
         <v>45281</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16253,7 +16258,7 @@
         <v>45278</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16331,7 +16336,7 @@
         <v>45289</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16404,7 +16409,7 @@
         <v>45181</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16477,7 +16482,7 @@
         <v>45578</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16550,7 +16555,7 @@
         <v>45578</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16623,7 +16628,7 @@
         <v>44728</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16696,7 +16701,7 @@
         <v>45749</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16769,7 +16774,7 @@
         <v>45757</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16842,7 +16847,7 @@
         <v>45496</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16915,7 +16920,7 @@
         <v>45764</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16993,7 +16998,7 @@
         <v>45483</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17066,7 +17071,7 @@
         <v>45769</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17144,7 +17149,7 @@
         <v>44603</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17217,7 +17222,7 @@
         <v>45173</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17295,7 +17300,7 @@
         <v>45168</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17368,7 +17373,7 @@
         <v>45203</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17441,7 +17446,7 @@
         <v>45701</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17519,7 +17524,7 @@
         <v>44980</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17592,7 +17597,7 @@
         <v>45097</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17665,7 +17670,7 @@
         <v>45562</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17738,7 +17743,7 @@
         <v>45617</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17811,7 +17816,7 @@
         <v>45729</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17884,7 +17889,7 @@
         <v>45352</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17962,7 +17967,7 @@
         <v>45769</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18040,7 +18045,7 @@
         <v>45730</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18113,7 +18118,7 @@
         <v>45761</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18186,7 +18191,7 @@
         <v>45342</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18259,7 +18264,7 @@
         <v>45531</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18332,7 +18337,7 @@
         <v>45638</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18405,7 +18410,7 @@
         <v>45887</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18483,7 +18488,7 @@
         <v>45293</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18556,7 +18561,7 @@
         <v>45180</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18629,7 +18634,7 @@
         <v>44853</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18702,7 +18707,7 @@
         <v>45147</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18775,7 +18780,7 @@
         <v>45887</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18848,7 +18853,7 @@
         <v>45320</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18921,7 +18926,7 @@
         <v>45888</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18994,7 +18999,7 @@
         <v>45168</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19067,7 +19072,7 @@
         <v>45293</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19140,7 +19145,7 @@
         <v>45884</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19213,7 +19218,7 @@
         <v>45890</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19291,7 +19296,7 @@
         <v>45890</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19369,7 +19374,7 @@
         <v>45891</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19447,7 +19452,7 @@
         <v>45897</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19520,7 +19525,7 @@
         <v>45168</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19593,7 +19598,7 @@
         <v>45072</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19666,7 +19671,7 @@
         <v>44936</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19739,7 +19744,7 @@
         <v>45901</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19812,7 +19817,7 @@
         <v>45511</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19885,7 +19890,7 @@
         <v>46065</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19963,7 +19968,7 @@
         <v>45771</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20036,7 +20041,7 @@
         <v>45749</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20109,7 +20114,7 @@
         <v>45803</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20182,7 +20187,7 @@
         <v>45904</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20255,7 +20260,7 @@
         <v>46024</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20328,7 +20333,7 @@
         <v>44728</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20401,7 +20406,7 @@
         <v>45825</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20474,7 +20479,7 @@
         <v>44971</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20552,7 +20557,7 @@
         <v>45526</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20625,7 +20630,7 @@
         <v>45915</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20703,7 +20708,7 @@
         <v>45915</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20781,7 +20786,7 @@
         <v>45489</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20859,7 +20864,7 @@
         <v>45523</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20932,7 +20937,7 @@
         <v>45917</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21005,7 +21010,7 @@
         <v>45887</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21078,7 +21083,7 @@
         <v>44791</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21151,7 +21156,7 @@
         <v>45273</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21224,7 +21229,7 @@
         <v>45126</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21297,7 +21302,7 @@
         <v>45840</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21370,7 +21375,7 @@
         <v>45919</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21448,7 +21453,7 @@
         <v>45923</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21526,7 +21531,7 @@
         <v>45922</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21599,7 +21604,7 @@
         <v>45685</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21672,7 +21677,7 @@
         <v>45922</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21745,7 +21750,7 @@
         <v>44987</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21823,7 +21828,7 @@
         <v>45924</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21896,7 +21901,7 @@
         <v>45189</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21969,7 +21974,7 @@
         <v>45924</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22042,7 +22047,7 @@
         <v>45924</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22115,7 +22120,7 @@
         <v>45924</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22188,7 +22193,7 @@
         <v>46072</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22261,7 +22266,7 @@
         <v>45376</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22334,7 +22339,7 @@
         <v>45924</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22407,7 +22412,7 @@
         <v>44869</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22480,7 +22485,7 @@
         <v>45006</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22553,7 +22558,7 @@
         <v>46142</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22626,7 +22631,7 @@
         <v>45428</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22699,7 +22704,7 @@
         <v>45562</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22777,7 +22782,7 @@
         <v>46142</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22850,7 +22855,7 @@
         <v>45409</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22923,7 +22928,7 @@
         <v>45645</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22996,7 +23001,7 @@
         <v>45919</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23074,7 +23079,7 @@
         <v>45936</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23147,7 +23152,7 @@
         <v>45936</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23220,7 +23225,7 @@
         <v>45936</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23293,7 +23298,7 @@
         <v>45409</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23366,7 +23371,7 @@
         <v>45937</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23444,7 +23449,7 @@
         <v>45939</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23522,7 +23527,7 @@
         <v>45147</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23595,7 +23600,7 @@
         <v>46150</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23668,7 +23673,7 @@
         <v>46153</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23741,7 +23746,7 @@
         <v>45462</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23814,7 +23819,7 @@
         <v>45161</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23892,7 +23897,7 @@
         <v>45418</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23965,7 +23970,7 @@
         <v>45091</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24038,7 +24043,7 @@
         <v>44937</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24111,7 +24116,7 @@
         <v>46153</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24184,7 +24189,7 @@
         <v>45959</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24257,7 +24262,7 @@
         <v>45959</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24330,7 +24335,7 @@
         <v>45723</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24403,7 +24408,7 @@
         <v>45733</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24476,7 +24481,7 @@
         <v>45293</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24549,7 +24554,7 @@
         <v>46155</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24622,7 +24627,7 @@
         <v>45930</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24695,7 +24700,7 @@
         <v>45392</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24768,7 +24773,7 @@
         <v>45044</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24841,7 +24846,7 @@
         <v>45793</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24919,7 +24924,7 @@
         <v>44951</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24997,7 +25002,7 @@
         <v>45972</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25075,7 +25080,7 @@
         <v>45972</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25153,7 +25158,7 @@
         <v>44897</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25226,7 +25231,7 @@
         <v>45044</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25304,7 +25309,7 @@
         <v>45975</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25382,7 +25387,7 @@
         <v>45975</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25460,7 +25465,7 @@
         <v>45978</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25538,7 +25543,7 @@
         <v>44732</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25611,7 +25616,7 @@
         <v>45979</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25689,7 +25694,7 @@
         <v>45979</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25762,7 +25767,7 @@
         <v>46107</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25835,7 +25840,7 @@
         <v>45979</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25908,7 +25913,7 @@
         <v>45979</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25981,7 +25986,7 @@
         <v>44596</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26059,7 +26064,7 @@
         <v>45979</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26137,7 +26142,7 @@
         <v>45979</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26215,7 +26220,7 @@
         <v>44706</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26288,7 +26293,7 @@
         <v>45979</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26366,7 +26371,7 @@
         <v>45512</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26439,7 +26444,7 @@
         <v>45981</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26517,7 +26522,7 @@
         <v>45981</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26595,7 +26600,7 @@
         <v>45987</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26668,7 +26673,7 @@
         <v>46161</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26741,7 +26746,7 @@
         <v>46161</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26814,7 +26819,7 @@
         <v>46161</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26887,7 +26892,7 @@
         <v>45786</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26965,7 +26970,7 @@
         <v>45790</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27043,7 +27048,7 @@
         <v>45646</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27116,7 +27121,7 @@
         <v>45329</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27189,7 +27194,7 @@
         <v>46160</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27262,7 +27267,7 @@
         <v>45813</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27335,7 +27340,7 @@
         <v>45992</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27408,7 +27413,7 @@
         <v>46161</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27481,7 +27486,7 @@
         <v>46161</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27554,7 +27559,7 @@
         <v>46161</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27627,7 +27632,7 @@
         <v>46161</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27700,7 +27705,7 @@
         <v>46161</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27773,7 +27778,7 @@
         <v>45616</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27851,7 +27856,7 @@
         <v>45320</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27924,7 +27929,7 @@
         <v>46162</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27997,7 +28002,7 @@
         <v>46162</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28070,7 +28075,7 @@
         <v>45832</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28143,7 +28148,7 @@
         <v>45035</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28216,7 +28221,7 @@
         <v>45126</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28289,7 +28294,7 @@
         <v>45163</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28362,7 +28367,7 @@
         <v>45999</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28435,7 +28440,7 @@
         <v>45999</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28508,7 +28513,7 @@
         <v>44853</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28581,7 +28586,7 @@
         <v>45999</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28654,7 +28659,7 @@
         <v>45138</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28727,7 +28732,7 @@
         <v>46000</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28800,7 +28805,7 @@
         <v>46000</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28873,7 +28878,7 @@
         <v>46167</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28946,7 +28951,7 @@
         <v>46167</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29019,7 +29024,7 @@
         <v>45531</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29097,7 +29102,7 @@
         <v>44867</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29170,7 +29175,7 @@
         <v>45638</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29243,7 +29248,7 @@
         <v>45390</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29316,7 +29321,7 @@
         <v>45678</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29394,7 +29399,7 @@
         <v>46149</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29467,7 +29472,7 @@
         <v>46013</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29540,7 +29545,7 @@
         <v>45072</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29618,7 +29623,7 @@
         <v>44676</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29691,7 +29696,7 @@
         <v>46168</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29764,7 +29769,7 @@
         <v>45985</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29837,7 +29842,7 @@
         <v>46170</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29910,7 +29915,7 @@
         <v>46023</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29983,7 +29988,7 @@
         <v>46023</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30056,7 +30061,7 @@
         <v>46023</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30129,7 +30134,7 @@
         <v>45015</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30207,7 +30212,7 @@
         <v>46024</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30280,7 +30285,7 @@
         <v>46024</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30353,7 +30358,7 @@
         <v>46024</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30426,7 +30431,7 @@
         <v>46026</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30499,7 +30504,7 @@
         <v>46024</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30572,7 +30577,7 @@
         <v>46029</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30645,7 +30650,7 @@
         <v>46029</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30718,7 +30723,7 @@
         <v>45749</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30791,7 +30796,7 @@
         <v>46030</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30864,7 +30869,7 @@
         <v>46029</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30937,7 +30942,7 @@
         <v>46029</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31010,7 +31015,7 @@
         <v>46030</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31083,7 +31088,7 @@
         <v>46034</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31156,7 +31161,7 @@
         <v>46170</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31229,7 +31234,7 @@
         <v>46035</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31302,7 +31307,7 @@
         <v>46174</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31375,7 +31380,7 @@
         <v>45313</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31448,7 +31453,7 @@
         <v>45622</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31521,7 +31526,7 @@
         <v>46038</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31594,7 +31599,7 @@
         <v>46038</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31667,7 +31672,7 @@
         <v>46042</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31740,7 +31745,7 @@
         <v>44971</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31818,7 +31823,7 @@
         <v>45910</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31891,7 +31896,7 @@
         <v>46094</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31964,7 +31969,7 @@
         <v>45148</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32037,7 +32042,7 @@
         <v>45243</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32110,7 +32115,7 @@
         <v>44845</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32183,7 +32188,7 @@
         <v>45409</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32256,7 +32261,7 @@
         <v>46045</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32329,7 +32334,7 @@
         <v>46165</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32402,7 +32407,7 @@
         <v>44580</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32475,7 +32480,7 @@
         <v>46175</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32548,7 +32553,7 @@
         <v>46049</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32621,7 +32626,7 @@
         <v>44894</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32694,7 +32699,7 @@
         <v>46175</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32767,7 +32772,7 @@
         <v>45366</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32840,7 +32845,7 @@
         <v>46055</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32913,7 +32918,7 @@
         <v>46175</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32986,7 +32991,7 @@
         <v>46054</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33059,7 +33064,7 @@
         <v>46178</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33132,7 +33137,7 @@
         <v>46052</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33205,7 +33210,7 @@
         <v>46052</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33278,7 +33283,7 @@
         <v>46177</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33351,7 +33356,7 @@
         <v>46177</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33424,7 +33429,7 @@
         <v>46177</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33497,7 +33502,7 @@
         <v>46177</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33575,7 +33580,7 @@
         <v>46177</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33648,7 +33653,7 @@
         <v>46178</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33721,7 +33726,7 @@
         <v>46052</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33799,7 +33804,7 @@
         <v>46056</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33872,7 +33877,7 @@
         <v>45251</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33945,7 +33950,7 @@
         <v>44498</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34018,7 +34023,7 @@
         <v>45376</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34091,7 +34096,7 @@
         <v>46177</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34164,7 +34169,7 @@
         <v>46063</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34237,7 +34242,7 @@
         <v>46065</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34310,7 +34315,7 @@
         <v>46065</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34388,7 +34393,7 @@
         <v>46065</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34466,7 +34471,7 @@
         <v>44865</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34544,7 +34549,7 @@
         <v>45699</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34617,7 +34622,7 @@
         <v>46065</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34695,7 +34700,7 @@
         <v>46065</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34768,7 +34773,7 @@
         <v>46181</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34841,7 +34846,7 @@
         <v>46182</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34914,7 +34919,7 @@
         <v>46069</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34987,7 +34992,7 @@
         <v>46070</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35060,7 +35065,7 @@
         <v>46070</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35133,7 +35138,7 @@
         <v>46070</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35206,7 +35211,7 @@
         <v>46071</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35279,7 +35284,7 @@
         <v>46071</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35352,7 +35357,7 @@
         <v>45044</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35430,7 +35435,7 @@
         <v>45502</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35503,7 +35508,7 @@
         <v>44726</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35576,7 +35581,7 @@
         <v>46072</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35649,7 +35654,7 @@
         <v>46072</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35722,7 +35727,7 @@
         <v>46181</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35795,7 +35800,7 @@
         <v>46077</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35868,7 +35873,7 @@
         <v>46184</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35941,7 +35946,7 @@
         <v>46080</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36014,7 +36019,7 @@
         <v>44889</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36092,7 +36097,7 @@
         <v>46085</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36165,7 +36170,7 @@
         <v>44755</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36238,7 +36243,7 @@
         <v>44881</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36316,7 +36321,7 @@
         <v>46064</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36389,7 +36394,7 @@
         <v>45194</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36462,7 +36467,7 @@
         <v>46087</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36540,7 +36545,7 @@
         <v>46188</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36613,7 +36618,7 @@
         <v>45505</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36691,7 +36696,7 @@
         <v>45800</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36764,7 +36769,7 @@
         <v>44847</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36842,7 +36847,7 @@
         <v>46189</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36915,7 +36920,7 @@
         <v>46091</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36988,7 +36993,7 @@
         <v>44847</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37066,7 +37071,7 @@
         <v>46091</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37139,7 +37144,7 @@
         <v>46091</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37212,7 +37217,7 @@
         <v>46091</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37285,7 +37290,7 @@
         <v>46091</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37358,7 +37363,7 @@
         <v>46189</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37431,7 +37436,7 @@
         <v>46189</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37504,7 +37509,7 @@
         <v>46189</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37577,7 +37582,7 @@
         <v>46094</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37655,7 +37660,7 @@
         <v>45723</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37728,7 +37733,7 @@
         <v>45482</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37806,7 +37811,7 @@
         <v>46189</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37879,7 +37884,7 @@
         <v>46094</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37952,7 +37957,7 @@
         <v>46190</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38025,7 +38030,7 @@
         <v>46189</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38098,7 +38103,7 @@
         <v>46191</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38176,7 +38181,7 @@
         <v>46195</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38249,7 +38254,7 @@
         <v>46195</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38322,7 +38327,7 @@
         <v>45328</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38400,7 +38405,7 @@
         <v>45328</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38478,7 +38483,7 @@
         <v>46195</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38551,7 +38556,7 @@
         <v>46195</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38624,7 +38629,7 @@
         <v>46195</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38697,7 +38702,7 @@
         <v>46104</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38770,7 +38775,7 @@
         <v>45390</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38843,7 +38848,7 @@
         <v>46195</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38916,7 +38921,7 @@
         <v>46101</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38994,7 +38999,7 @@
         <v>46105</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39067,7 +39072,7 @@
         <v>44496</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39140,7 +39145,7 @@
         <v>44875</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39213,7 +39218,7 @@
         <v>46105</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39286,7 +39291,7 @@
         <v>44531</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39359,7 +39364,7 @@
         <v>45729</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39432,7 +39437,7 @@
         <v>45545</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39505,7 +39510,7 @@
         <v>46106</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39578,7 +39583,7 @@
         <v>46105</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39651,7 +39656,7 @@
         <v>46105</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39724,7 +39729,7 @@
         <v>45595</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39797,7 +39802,7 @@
         <v>45595</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39870,7 +39875,7 @@
         <v>46107</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39943,7 +39948,7 @@
         <v>46107</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40016,7 +40021,7 @@
         <v>45280</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40089,7 +40094,7 @@
         <v>44694</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40167,7 +40172,7 @@
         <v>46107</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40240,7 +40245,7 @@
         <v>44743</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40313,7 +40318,7 @@
         <v>44806</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40386,7 +40391,7 @@
         <v>44806</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40459,7 +40464,7 @@
         <v>46113</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40537,7 +40542,7 @@
         <v>46120</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40610,7 +40615,7 @@
         <v>45714</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40683,7 +40688,7 @@
         <v>45229</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40756,7 +40761,7 @@
         <v>46122</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40829,7 +40834,7 @@
         <v>46126</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40907,7 +40912,7 @@
         <v>46244</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40985,7 +40990,7 @@
         <v>44991</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41063,7 +41068,7 @@
         <v>46127</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41136,7 +41141,7 @@
         <v>45250</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41209,7 +41214,7 @@
         <v>46133</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41282,7 +41287,7 @@
         <v>45580</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41355,7 +41360,7 @@
         <v>46132</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41428,7 +41433,7 @@
         <v>46133</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41501,7 +41506,7 @@
         <v>45281</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41574,7 +41579,7 @@
         <v>46203</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41652,7 +41657,7 @@
         <v>44957</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41725,7 +41730,7 @@
         <v>45265</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41803,7 +41808,7 @@
         <v>45476</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41876,7 +41881,7 @@
         <v>45476</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41949,7 +41954,7 @@
         <v>45166</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42027,7 +42032,7 @@
         <v>46204</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42100,7 +42105,7 @@
         <v>46204</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42173,7 +42178,7 @@
         <v>44855</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42246,7 +42251,7 @@
         <v>44890</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42324,7 +42329,7 @@
         <v>46204</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42397,7 +42402,7 @@
         <v>46204</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42470,7 +42475,7 @@
         <v>46205</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42543,7 +42548,7 @@
         <v>46205</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42616,7 +42621,7 @@
         <v>46205</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42689,7 +42694,7 @@
         <v>46251</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42767,7 +42772,7 @@
         <v>44945</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42845,7 +42850,7 @@
         <v>46206</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42918,7 +42923,7 @@
         <v>46206</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42991,7 +42996,7 @@
         <v>46206</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43064,7 +43069,7 @@
         <v>45800</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43137,7 +43142,7 @@
         <v>46206</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43210,7 +43215,7 @@
         <v>46206</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43283,7 +43288,7 @@
         <v>46248</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43356,7 +43361,7 @@
         <v>44903</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43434,7 +43439,7 @@
         <v>46252</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43507,7 +43512,7 @@
         <v>45251</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43580,7 +43585,7 @@
         <v>46209</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43653,7 +43658,7 @@
         <v>45512</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43726,7 +43731,7 @@
         <v>45723</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43799,7 +43804,7 @@
         <v>44497</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43872,7 +43877,7 @@
         <v>44502</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43945,7 +43950,7 @@
         <v>46211</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44018,7 +44023,7 @@
         <v>45323</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44091,7 +44096,7 @@
         <v>45639</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44164,7 +44169,7 @@
         <v>44609</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44242,7 +44247,7 @@
         <v>46211</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44315,7 +44320,7 @@
         <v>46213</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44388,7 +44393,7 @@
         <v>44952</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44461,7 +44466,7 @@
         <v>46258</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44534,7 +44539,7 @@
         <v>46215</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44607,7 +44612,7 @@
         <v>46215</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44680,7 +44685,7 @@
         <v>45348</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44753,7 +44758,7 @@
         <v>44747</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44826,7 +44831,7 @@
         <v>46213</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44899,7 +44904,7 @@
         <v>46213</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44972,7 +44977,7 @@
         <v>45152</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45045,7 +45050,7 @@
         <v>45099</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45123,7 +45128,7 @@
         <v>46260</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45196,7 +45201,7 @@
         <v>46219</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45269,7 +45274,7 @@
         <v>46219</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45342,7 +45347,7 @@
         <v>46219</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45415,7 +45420,7 @@
         <v>45629</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45488,7 +45493,7 @@
         <v>45000</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45566,7 +45571,7 @@
         <v>45000</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45644,7 +45649,7 @@
         <v>46213</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45717,7 +45722,7 @@
         <v>46203</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45790,7 +45795,7 @@
         <v>44819</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45868,7 +45873,7 @@
         <v>45762</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45941,7 +45946,7 @@
         <v>46161</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46014,7 +46019,7 @@
         <v>46262</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46087,7 +46092,7 @@
         <v>46265</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46165,7 +46170,7 @@
         <v>45163</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46238,7 +46243,7 @@
         <v>45107</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46311,7 +46316,7 @@
         <v>45685</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46384,7 +46389,7 @@
         <v>45776</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46457,7 +46462,7 @@
         <v>45776</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46530,7 +46535,7 @@
         <v>45782</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46608,7 +46613,7 @@
         <v>45782</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46686,7 +46691,7 @@
         <v>46275</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46759,7 +46764,7 @@
         <v>45562</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46832,7 +46837,7 @@
         <v>46274</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46905,7 +46910,7 @@
         <v>46232</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46978,7 +46983,7 @@
         <v>45578</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47051,7 +47056,7 @@
         <v>45574</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47124,7 +47129,7 @@
         <v>46237</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47202,7 +47207,7 @@
         <v>45791</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47275,7 +47280,7 @@
         <v>45342</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47348,7 +47353,7 @@
         <v>45433</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47421,7 +47426,7 @@
         <v>46281</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47494,7 +47499,7 @@
         <v>45351</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47567,7 +47572,7 @@
         <v>45793</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47645,7 +47650,7 @@
         <v>46281</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47718,7 +47723,7 @@
         <v>45579</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47791,7 +47796,7 @@
         <v>44571</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47864,7 +47869,7 @@
         <v>45266</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47937,7 +47942,7 @@
         <v>46239</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48015,7 +48020,7 @@
         <v>45516</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48088,7 +48093,7 @@
         <v>45799</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48166,7 +48171,7 @@
         <v>45139</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48239,7 +48244,7 @@
         <v>46282</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48312,7 +48317,7 @@
         <v>44475</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48385,7 +48390,7 @@
         <v>45803</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48458,7 +48463,7 @@
         <v>45762</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48531,7 +48536,7 @@
         <v>45800</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48609,7 +48614,7 @@
         <v>45805</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48682,7 +48687,7 @@
         <v>45630</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48755,7 +48760,7 @@
         <v>45205</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48828,7 +48833,7 @@
         <v>45811</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48901,7 +48906,7 @@
         <v>45812</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48974,7 +48979,7 @@
         <v>45812</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49047,7 +49052,7 @@
         <v>45825</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49120,7 +49125,7 @@
         <v>45825</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49193,7 +49198,7 @@
         <v>45825</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49266,7 +49271,7 @@
         <v>45825</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49339,7 +49344,7 @@
         <v>45824</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49417,7 +49422,7 @@
         <v>45826</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49495,7 +49500,7 @@
         <v>45833</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49573,7 +49578,7 @@
         <v>45833</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49651,7 +49656,7 @@
         <v>45833</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49729,7 +49734,7 @@
         <v>45833</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49807,7 +49812,7 @@
         <v>45833</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49885,7 +49890,7 @@
         <v>45834</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49958,7 +49963,7 @@
         <v>45811</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50031,7 +50036,7 @@
         <v>45834</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50104,7 +50109,7 @@
         <v>45837</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50182,7 +50187,7 @@
         <v>45837</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50260,7 +50265,7 @@
         <v>45840</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50333,7 +50338,7 @@
         <v>45840</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50406,7 +50411,7 @@
         <v>45749</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50479,7 +50484,7 @@
         <v>45848</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50552,7 +50557,7 @@
         <v>45848</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50625,7 +50630,7 @@
         <v>45853</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50703,7 +50708,7 @@
         <v>44973</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50776,7 +50781,7 @@
         <v>45741</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50849,7 +50854,7 @@
         <v>45793</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50922,7 +50927,7 @@
         <v>45729</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50995,7 +51000,7 @@
         <v>45574</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51068,7 +51073,7 @@
         <v>45741</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51141,7 +51146,7 @@
         <v>45874</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51214,7 +51219,7 @@
         <v>45874</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51287,7 +51292,7 @@
         <v>45874</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51360,7 +51365,7 @@
         <v>45874</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51433,7 +51438,7 @@
         <v>45880</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51506,7 +51511,7 @@
         <v>44393</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51579,7 +51584,7 @@
         <v>45323</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51657,7 +51662,7 @@
         <v>45733</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51735,7 +51740,7 @@
         <v>45755</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51808,7 +51813,7 @@
         <v>45793</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51886,7 +51891,7 @@
         <v>46078</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51964,7 +51969,7 @@
         <v>46073</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52037,7 +52042,7 @@
         <v>46093</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52115,7 +52120,7 @@
         <v>46156</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52188,7 +52193,7 @@
         <v>46267</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>

--- a/Översikt HÄRNÖSAND.xlsx
+++ b/Översikt HÄRNÖSAND.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45328</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>46288</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>46044</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>45763</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>45588</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>45938</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>46189</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>44686</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>45546</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>45394</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45930</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>45763</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>45805</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>45484</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>45139</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>45826</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45335</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>45027</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>45082</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>44874</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>46183</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>45352</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>45593</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>45957</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>45567</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>45188</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>45593</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>45548</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>44979</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>45477</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>45560</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>45971</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>45314</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>45848</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>46176</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>46251</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>45513</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>45323</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>45790</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>44686</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>45930</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>45617</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>45182</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>46003</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>45355</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>45596</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>45526</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>45322</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>46244</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>44755</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>44664</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>45376</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>45267</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44874</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>45513</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>45930</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>45910</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>45967</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45618</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>45575</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>46141</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>45847</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>46244</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>45996</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>44676</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>44585</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>44655</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>46031</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>45919</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>45805</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>45805</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         <v>45583</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>45811</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>46127</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>45008</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>44837</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>45649</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         <v>45276</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>46176</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44559</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>46189</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>46191</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>46184</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>45350</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>45372</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         <v>45456</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>45554</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>45428</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>45352</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         <v>44874</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>44664</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>44806</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         <v>44846</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>44532</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>44875</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>44477</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         <v>44608</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>44720</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>44600</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         <v>44824</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
         <v>44487</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>44734</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>44512</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>44517</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>44728</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         <v>44477</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>44475</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>44476</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12332,7 +12332,7 @@
         <v>44664</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>44804</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>44512</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12551,7 +12551,7 @@
         <v>44503</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12624,7 +12624,7 @@
         <v>44735</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
         <v>44581</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>44848</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>44469</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         <v>44672</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12989,7 +12989,7 @@
         <v>44652</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>44515</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13135,7 +13135,7 @@
         <v>44664</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>44616</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         <v>44496</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>44532</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>44571</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>44512</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>44664</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>44536</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>44522</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>44585</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>45483</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>45044</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>45328</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>45328</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>45531</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>45409</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>44806</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44806</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>44809</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>44853</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>45281</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>45281</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         <v>45462</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>45489</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         <v>45273</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14980,7 +14980,7 @@
         <v>44952</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>46024</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>46024</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>46023</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>46024</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>46023</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>46024</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>46026</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>44571</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15637,7 +15637,7 @@
         <v>46029</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15710,7 +15710,7 @@
         <v>46029</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>46029</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15856,7 +15856,7 @@
         <v>46030</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         <v>46029</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>45579</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         <v>45793</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>45511</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>45266</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>45243</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>44881</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>44865</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>45516</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>45139</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>44475</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>45476</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>46030</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>44937</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>45531</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>46034</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>45888</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>45887</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>45799</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>45761</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>45887</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>45890</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>46035</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17638,7 +17638,7 @@
         <v>45890</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>44498</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>44853</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>46038</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>45729</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>46038</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>46042</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>45891</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>45293</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>45800</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>45562</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>45897</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>44531</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>45901</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>46045</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>46049</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18821,7 +18821,7 @@
         <v>46052</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>45803</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>46052</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>46052</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>45209</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19196,7 +19196,7 @@
         <v>46055</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>46056</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>44897</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>45558</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>45803</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>45915</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>45915</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45917</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>46063</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>44881</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>46065</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
         <v>46065</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>45919</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>45922</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>46065</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>45922</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>46065</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>46065</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>45923</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>46070</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>45762</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>46069</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>45924</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>45924</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>45924</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         <v>45924</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>45924</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>46072</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>44894</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>46071</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>46071</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>46072</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>44609</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21650,7 +21650,7 @@
         <v>45805</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21723,7 +21723,7 @@
         <v>45576</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>46077</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>45320</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21947,7 +21947,7 @@
         <v>46080</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>45630</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>46085</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>45919</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>46064</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>45205</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
         <v>45936</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>46087</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
         <v>46091</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22614,7 +22614,7 @@
         <v>45936</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>45936</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22760,7 +22760,7 @@
         <v>46091</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         <v>46091</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>46091</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22979,7 +22979,7 @@
         <v>46091</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>45701</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>45937</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23208,7 +23208,7 @@
         <v>45757</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>45390</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>45939</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         <v>45505</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23510,7 +23510,7 @@
         <v>46094</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>46094</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>44755</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>46101</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>46104</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>46105</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23958,7 +23958,7 @@
         <v>46105</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24031,7 +24031,7 @@
         <v>44747</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>46105</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         <v>46105</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24250,7 +24250,7 @@
         <v>46107</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24323,7 +24323,7 @@
         <v>46107</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>46107</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>46106</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>45622</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>45811</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>46113</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24766,7 +24766,7 @@
         <v>44732</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>45812</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>45293</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>44890</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>45812</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25136,7 +25136,7 @@
         <v>45959</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>45959</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>45015</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
         <v>45314</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>46120</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>46122</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25579,7 +25579,7 @@
         <v>46127</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>45793</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>45972</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>46126</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25886,7 +25886,7 @@
         <v>45972</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>44971</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>45638</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26115,7 +26115,7 @@
         <v>45975</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>45978</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         <v>46132</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>45975</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>45979</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>45979</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         <v>45979</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>45979</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>45979</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26802,7 +26802,7 @@
         <v>45979</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>45979</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>45981</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27031,7 +27031,7 @@
         <v>45981</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27109,7 +27109,7 @@
         <v>46133</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27182,7 +27182,7 @@
         <v>44743</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27255,7 +27255,7 @@
         <v>46133</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>44847</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>45987</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27479,7 +27479,7 @@
         <v>45667</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27552,7 +27552,7 @@
         <v>45992</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27625,7 +27625,7 @@
         <v>45645</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27698,7 +27698,7 @@
         <v>45904</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27771,7 +27771,7 @@
         <v>45168</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>45126</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27917,7 +27917,7 @@
         <v>44853</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>45138</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28063,7 +28063,7 @@
         <v>45999</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>45999</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>45999</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>46000</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>45526</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>46065</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>45545</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>44980</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>45678</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>45764</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>44971</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28886,7 +28886,7 @@
         <v>46013</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>44936</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>45824</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>45771</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>45769</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>45685</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29334,7 +29334,7 @@
         <v>45825</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29407,7 +29407,7 @@
         <v>45825</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>45825</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>45825</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>45825</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>45523</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29772,7 +29772,7 @@
         <v>45826</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>45749</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29923,7 +29923,7 @@
         <v>45840</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>45749</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
         <v>45887</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>44603</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30215,7 +30215,7 @@
         <v>45044</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30293,7 +30293,7 @@
         <v>46072</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30366,7 +30366,7 @@
         <v>46024</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30439,7 +30439,7 @@
         <v>45203</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>45106</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30590,7 +30590,7 @@
         <v>46142</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30663,7 +30663,7 @@
         <v>46142</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>45714</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>44596</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>46150</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>46107</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>46153</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>45833</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31184,7 +31184,7 @@
         <v>45833</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>45834</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31335,7 +31335,7 @@
         <v>46153</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>45833</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31486,7 +31486,7 @@
         <v>45833</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31564,7 +31564,7 @@
         <v>45833</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31642,7 +31642,7 @@
         <v>45099</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31720,7 +31720,7 @@
         <v>45834</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31793,7 +31793,7 @@
         <v>46155</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31866,7 +31866,7 @@
         <v>45837</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31944,7 +31944,7 @@
         <v>45930</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>46160</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>45811</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32163,7 +32163,7 @@
         <v>45723</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32236,7 +32236,7 @@
         <v>46161</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>45832</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32382,7 +32382,7 @@
         <v>46161</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32455,7 +32455,7 @@
         <v>45837</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32533,7 +32533,7 @@
         <v>46161</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         <v>45562</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32684,7 +32684,7 @@
         <v>45840</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32757,7 +32757,7 @@
         <v>45840</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32830,7 +32830,7 @@
         <v>44991</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>46161</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>46161</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33054,7 +33054,7 @@
         <v>46162</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>46161</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33200,7 +33200,7 @@
         <v>45786</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>45813</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33351,7 +33351,7 @@
         <v>46162</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33424,7 +33424,7 @@
         <v>45790</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>46161</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33575,7 +33575,7 @@
         <v>46161</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33648,7 +33648,7 @@
         <v>45293</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33721,7 +33721,7 @@
         <v>44497</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         <v>45329</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33867,7 +33867,7 @@
         <v>45848</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>45848</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>46168</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34086,7 +34086,7 @@
         <v>45985</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>46167</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34232,7 +34232,7 @@
         <v>44847</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34310,7 +34310,7 @@
         <v>45749</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>45638</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34456,7 +34456,7 @@
         <v>46167</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34529,7 +34529,7 @@
         <v>46149</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>45853</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34680,7 +34680,7 @@
         <v>45352</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34758,7 +34758,7 @@
         <v>45793</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34831,7 +34831,7 @@
         <v>45265</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34909,7 +34909,7 @@
         <v>46165</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34982,7 +34982,7 @@
         <v>46170</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35055,7 +35055,7 @@
         <v>45729</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35128,7 +35128,7 @@
         <v>45741</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>45281</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>44973</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45910</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>46170</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>45574</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>46175</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>46175</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>46094</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35785,7 +35785,7 @@
         <v>45741</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>46175</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35931,7 +35931,7 @@
         <v>45409</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36004,7 +36004,7 @@
         <v>44819</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>45278</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>46174</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36233,7 +36233,7 @@
         <v>46177</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36306,7 +36306,7 @@
         <v>45502</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>46177</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36452,7 +36452,7 @@
         <v>46177</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>46177</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36603,7 +36603,7 @@
         <v>46177</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36676,7 +36676,7 @@
         <v>46177</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>46178</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36822,7 +36822,7 @@
         <v>44791</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36895,7 +36895,7 @@
         <v>45418</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36968,7 +36968,7 @@
         <v>46181</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37041,7 +37041,7 @@
         <v>46178</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37114,7 +37114,7 @@
         <v>44502</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>45126</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37260,7 +37260,7 @@
         <v>45874</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>45228</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>46182</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37479,7 +37479,7 @@
         <v>46184</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37552,7 +37552,7 @@
         <v>45161</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37630,7 +37630,7 @@
         <v>45390</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37703,7 +37703,7 @@
         <v>45148</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>45173</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37854,7 +37854,7 @@
         <v>45342</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>44496</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38000,7 +38000,7 @@
         <v>46189</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38073,7 +38073,7 @@
         <v>45800</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>45874</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38219,7 +38219,7 @@
         <v>46188</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38292,7 +38292,7 @@
         <v>45405</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>46189</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>46189</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38511,7 +38511,7 @@
         <v>46189</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38584,7 +38584,7 @@
         <v>46189</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>45874</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>45874</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>46191</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38881,7 +38881,7 @@
         <v>45409</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>45334</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>46190</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>46195</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>46195</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39246,7 +39246,7 @@
         <v>46195</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39319,7 +39319,7 @@
         <v>45628</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39392,7 +39392,7 @@
         <v>46195</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>46195</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39538,7 +39538,7 @@
         <v>46195</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39611,7 +39611,7 @@
         <v>45880</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39684,7 +39684,7 @@
         <v>44641</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39757,7 +39757,7 @@
         <v>45168</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39830,7 +39830,7 @@
         <v>45512</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>45639</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39976,7 +39976,7 @@
         <v>45147</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40049,7 +40049,7 @@
         <v>46203</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40127,7 +40127,7 @@
         <v>45595</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40200,7 +40200,7 @@
         <v>45595</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40273,7 +40273,7 @@
         <v>45616</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>46204</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>46204</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40497,7 +40497,7 @@
         <v>45884</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40570,7 +40570,7 @@
         <v>46205</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40643,7 +40643,7 @@
         <v>46204</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>46204</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40789,7 +40789,7 @@
         <v>46205</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40862,7 +40862,7 @@
         <v>46205</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>45800</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>44676</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>46206</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41154,7 +41154,7 @@
         <v>46206</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41227,7 +41227,7 @@
         <v>46206</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41300,7 +41300,7 @@
         <v>46206</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41373,7 +41373,7 @@
         <v>46252</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41446,7 +41446,7 @@
         <v>46251</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41524,7 +41524,7 @@
         <v>44694</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41602,7 +41602,7 @@
         <v>46209</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>46211</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41748,7 +41748,7 @@
         <v>45617</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41821,7 +41821,7 @@
         <v>45762</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41894,7 +41894,7 @@
         <v>46211</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41967,7 +41967,7 @@
         <v>44617</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>45428</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>45163</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>45152</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42259,7 +42259,7 @@
         <v>44858</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>46213</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>46258</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42478,7 +42478,7 @@
         <v>45348</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42551,7 +42551,7 @@
         <v>46213</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42624,7 +42624,7 @@
         <v>46213</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42697,7 +42697,7 @@
         <v>45163</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>46215</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42843,7 +42843,7 @@
         <v>46215</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>44706</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>44728</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43062,7 +43062,7 @@
         <v>46260</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43135,7 +43135,7 @@
         <v>46262</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>45181</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43281,7 +43281,7 @@
         <v>44728</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43354,7 +43354,7 @@
         <v>45189</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43427,7 +43427,7 @@
         <v>46219</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43500,7 +43500,7 @@
         <v>46219</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43573,7 +43573,7 @@
         <v>46219</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43646,7 +43646,7 @@
         <v>45699</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>45168</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43792,7 +43792,7 @@
         <v>44726</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43865,7 +43865,7 @@
         <v>45723</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>46265</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44016,7 +44016,7 @@
         <v>46161</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44089,7 +44089,7 @@
         <v>45166</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44167,7 +44167,7 @@
         <v>46203</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44240,7 +44240,7 @@
         <v>46213</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45251</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44386,7 +44386,7 @@
         <v>45350</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44464,7 +44464,7 @@
         <v>45293</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44537,7 +44537,7 @@
         <v>45320</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44610,7 +44610,7 @@
         <v>45231</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44683,7 +44683,7 @@
         <v>44747</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44756,7 +44756,7 @@
         <v>45072</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44829,7 +44829,7 @@
         <v>45313</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44902,7 +44902,7 @@
         <v>45366</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44975,7 +44975,7 @@
         <v>46274</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45048,7 +45048,7 @@
         <v>44853</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45121,7 +45121,7 @@
         <v>45749</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45194,7 +45194,7 @@
         <v>45757</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45267,7 +45267,7 @@
         <v>44792</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45340,7 +45340,7 @@
         <v>46232</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45413,7 +45413,7 @@
         <v>45733</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45486,7 +45486,7 @@
         <v>45496</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45559,7 +45559,7 @@
         <v>46275</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>45352</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45710,7 +45710,7 @@
         <v>45091</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45783,7 +45783,7 @@
         <v>45280</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45856,7 +45856,7 @@
         <v>46237</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45934,7 +45934,7 @@
         <v>45462</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46007,7 +46007,7 @@
         <v>46282</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46080,7 +46080,7 @@
         <v>46281</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46153,7 +46153,7 @@
         <v>44875</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46226,7 +46226,7 @@
         <v>46239</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46304,7 +46304,7 @@
         <v>46281</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46377,7 +46377,7 @@
         <v>45482</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46455,7 +46455,7 @@
         <v>45496</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46528,7 +46528,7 @@
         <v>44957</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46601,7 +46601,7 @@
         <v>46286</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46679,7 +46679,7 @@
         <v>44903</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46757,7 +46757,7 @@
         <v>44945</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46835,7 +46835,7 @@
         <v>46181</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46908,7 +46908,7 @@
         <v>46286</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46986,7 +46986,7 @@
         <v>46070</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47059,7 +47059,7 @@
         <v>46288</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47132,7 +47132,7 @@
         <v>46286</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47205,7 +47205,7 @@
         <v>45376</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47278,7 +47278,7 @@
         <v>46288</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47351,7 +47351,7 @@
         <v>46288</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47424,7 +47424,7 @@
         <v>46244</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47502,7 +47502,7 @@
         <v>46287</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47580,7 +47580,7 @@
         <v>46189</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47653,7 +47653,7 @@
         <v>46288</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47726,7 +47726,7 @@
         <v>44889</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>46248</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47877,7 +47877,7 @@
         <v>45289</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47950,7 +47950,7 @@
         <v>44845</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45072</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48101,7 +48101,7 @@
         <v>45194</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>45289</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>44580</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45476</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>45006</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48466,7 +48466,7 @@
         <v>45300</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48539,7 +48539,7 @@
         <v>45035</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>44987</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48690,7 +48690,7 @@
         <v>44869</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48763,7 +48763,7 @@
         <v>45392</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48836,7 +48836,7 @@
         <v>45000</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48914,7 +48914,7 @@
         <v>45000</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48992,7 +48992,7 @@
         <v>45250</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
         <v>45044</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49143,7 +49143,7 @@
         <v>45126</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49216,7 +49216,7 @@
         <v>45762</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45180</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49362,7 +49362,7 @@
         <v>45580</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49435,7 +49435,7 @@
         <v>45147</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49508,7 +49508,7 @@
         <v>45251</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>45482</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49659,7 +49659,7 @@
         <v>45769</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49737,7 +49737,7 @@
         <v>45646</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49810,7 +49810,7 @@
         <v>45107</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49883,7 +49883,7 @@
         <v>45723</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49956,7 +49956,7 @@
         <v>45097</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>44855</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50102,7 +50102,7 @@
         <v>45629</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50175,7 +50175,7 @@
         <v>45323</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50248,7 +50248,7 @@
         <v>45578</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50321,7 +50321,7 @@
         <v>45578</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>44951</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50472,7 +50472,7 @@
         <v>45531</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50545,7 +50545,7 @@
         <v>45512</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50618,7 +50618,7 @@
         <v>44867</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50691,7 +50691,7 @@
         <v>45729</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50764,7 +50764,7 @@
         <v>45376</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50837,7 +50837,7 @@
         <v>45730</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50910,7 +50910,7 @@
         <v>45685</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50983,7 +50983,7 @@
         <v>45776</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51056,7 +51056,7 @@
         <v>45776</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51129,7 +51129,7 @@
         <v>45782</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>45782</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51285,7 +51285,7 @@
         <v>45562</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51358,7 +51358,7 @@
         <v>45578</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>45791</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51504,7 +51504,7 @@
         <v>45342</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51577,7 +51577,7 @@
         <v>45574</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>45433</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51723,7 +51723,7 @@
         <v>45351</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51796,7 +51796,7 @@
         <v>44393</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>45323</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51947,7 +51947,7 @@
         <v>45733</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52025,7 +52025,7 @@
         <v>45755</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52098,7 +52098,7 @@
         <v>45793</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52176,7 +52176,7 @@
         <v>46078</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52254,7 +52254,7 @@
         <v>46073</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52327,7 +52327,7 @@
         <v>46093</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52405,7 +52405,7 @@
         <v>46156</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52478,7 +52478,7 @@
         <v>46267</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>

--- a/Översikt HÄRNÖSAND.xlsx
+++ b/Översikt HÄRNÖSAND.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45328</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>46288</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>46044</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>45763</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>45588</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>45938</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>46189</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>44686</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>45546</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>45394</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45930</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>45763</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>45805</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>45484</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>45139</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>45826</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45335</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>45027</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>45082</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>44874</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>46183</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>45352</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>45593</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>45957</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>45567</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>45188</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>45593</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>45548</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>44979</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>45477</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>45560</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>45971</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>45314</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>45848</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>46176</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>46251</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>45513</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>45323</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>45790</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>44686</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>45930</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>45617</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>45182</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>46003</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>45355</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>45596</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>45526</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>45322</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>46244</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>44755</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>44664</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>45376</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>45267</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44874</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>45513</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>45930</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>45910</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>45967</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45618</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>45575</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>46141</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>45847</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>46244</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>45996</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>44676</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>44585</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>44655</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>46031</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>45919</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>45805</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>45805</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         <v>45583</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>45811</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>46127</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>45008</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>44837</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>45649</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         <v>45276</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>46176</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44559</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>46189</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>46191</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>46184</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>45350</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>45372</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         <v>45456</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>45554</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>45428</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>45352</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         <v>44874</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>44664</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>44806</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         <v>44846</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>44532</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>44875</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>44477</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         <v>44608</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>44720</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>44600</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         <v>44824</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
         <v>44487</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>44734</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>44512</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>44517</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>44728</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         <v>44477</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>44475</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>44476</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12332,7 +12332,7 @@
         <v>44664</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>44804</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>44512</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12551,7 +12551,7 @@
         <v>44503</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12624,7 +12624,7 @@
         <v>44735</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
         <v>44581</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>44848</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>44469</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         <v>44672</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12989,7 +12989,7 @@
         <v>44652</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>44515</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13135,7 +13135,7 @@
         <v>44664</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>44616</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         <v>44496</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>44532</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>44571</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>44512</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>44664</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>44536</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>44522</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>44585</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>45483</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>45044</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>45328</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>45328</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>45531</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>45409</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>44806</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44806</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>44809</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>44853</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>45281</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>45281</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         <v>45462</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>45489</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         <v>45273</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14980,7 +14980,7 @@
         <v>44952</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>46024</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>46024</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>46023</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>46024</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>46023</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>46024</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>46026</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>44571</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15637,7 +15637,7 @@
         <v>46029</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15710,7 +15710,7 @@
         <v>46029</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>46029</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15856,7 +15856,7 @@
         <v>46030</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         <v>46029</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>45579</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         <v>45793</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>45511</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>45266</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>45243</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>44881</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>44865</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>45516</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>45139</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>44475</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>45476</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>46030</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>44937</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>45531</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>46034</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>45888</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>45887</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>45799</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>45761</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>45887</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>45890</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>46035</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17638,7 +17638,7 @@
         <v>45890</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>44498</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>44853</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>46038</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>45729</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>46038</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>46042</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>45891</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>45293</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>45800</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>45562</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>45897</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>44531</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>45901</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>46045</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>46049</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18821,7 +18821,7 @@
         <v>46052</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>45803</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>46052</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>46052</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>45209</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19196,7 +19196,7 @@
         <v>46055</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>46056</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>44897</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>45558</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>45803</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>45915</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>45915</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45917</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>46063</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>44881</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>46065</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
         <v>46065</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>45919</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>45922</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>46065</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>45922</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>46065</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>46065</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>45923</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>46070</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>45762</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>46069</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>45924</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>45924</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>45924</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         <v>45924</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>45924</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>46072</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>44894</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>46071</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>46071</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>46072</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>44609</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21650,7 +21650,7 @@
         <v>45805</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21723,7 +21723,7 @@
         <v>45576</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>46077</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>45320</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21947,7 +21947,7 @@
         <v>46080</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>45630</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>46085</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>45919</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>46064</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>45205</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
         <v>45936</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>46087</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
         <v>46091</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22614,7 +22614,7 @@
         <v>45936</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>45936</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22760,7 +22760,7 @@
         <v>46091</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         <v>46091</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>46091</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22979,7 +22979,7 @@
         <v>46091</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>45701</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>45937</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23208,7 +23208,7 @@
         <v>45757</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>45390</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>45939</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         <v>45505</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23510,7 +23510,7 @@
         <v>46094</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>46094</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>44755</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>46101</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>46104</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>46105</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23958,7 +23958,7 @@
         <v>46105</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24031,7 +24031,7 @@
         <v>44747</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>46105</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         <v>46105</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24250,7 +24250,7 @@
         <v>46107</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24323,7 +24323,7 @@
         <v>46107</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>46107</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>46106</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>45622</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>45811</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>46113</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24766,7 +24766,7 @@
         <v>44732</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>45812</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>45293</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>44890</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>45812</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25136,7 +25136,7 @@
         <v>45959</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>45959</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>45015</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
         <v>45314</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>46120</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>46122</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25579,7 +25579,7 @@
         <v>46127</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>45793</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>45972</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>46126</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25886,7 +25886,7 @@
         <v>45972</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>44971</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>45638</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26115,7 +26115,7 @@
         <v>45975</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>45978</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         <v>46132</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>45975</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>45979</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>45979</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         <v>45979</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>45979</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>45979</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26802,7 +26802,7 @@
         <v>45979</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>45979</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>45981</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27031,7 +27031,7 @@
         <v>45981</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27109,7 +27109,7 @@
         <v>46133</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27182,7 +27182,7 @@
         <v>44743</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27255,7 +27255,7 @@
         <v>46133</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>44847</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>45987</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27479,7 +27479,7 @@
         <v>45667</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27552,7 +27552,7 @@
         <v>45992</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27625,7 +27625,7 @@
         <v>45645</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27698,7 +27698,7 @@
         <v>45904</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27771,7 +27771,7 @@
         <v>45168</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>45126</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27917,7 +27917,7 @@
         <v>44853</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>45138</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28063,7 +28063,7 @@
         <v>45999</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>45999</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>45999</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>46000</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>45526</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>46065</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>45545</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>44980</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>45678</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>45764</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>44971</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28886,7 +28886,7 @@
         <v>46013</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>44936</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>45824</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>45771</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>45769</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>45685</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29334,7 +29334,7 @@
         <v>45825</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29407,7 +29407,7 @@
         <v>45825</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>45825</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>45825</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>45825</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>45523</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29772,7 +29772,7 @@
         <v>45826</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>45749</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29923,7 +29923,7 @@
         <v>45840</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>45749</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
         <v>45887</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>44603</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30215,7 +30215,7 @@
         <v>45044</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30293,7 +30293,7 @@
         <v>46072</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30366,7 +30366,7 @@
         <v>46024</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30439,7 +30439,7 @@
         <v>45203</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>45106</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30590,7 +30590,7 @@
         <v>46142</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30663,7 +30663,7 @@
         <v>46142</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>45714</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>44596</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>46150</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>46107</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>46153</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>45833</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31184,7 +31184,7 @@
         <v>45833</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>45834</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31335,7 +31335,7 @@
         <v>46153</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>45833</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31486,7 +31486,7 @@
         <v>45833</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31564,7 +31564,7 @@
         <v>45833</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31642,7 +31642,7 @@
         <v>45099</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31720,7 +31720,7 @@
         <v>45834</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31793,7 +31793,7 @@
         <v>46155</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31866,7 +31866,7 @@
         <v>45837</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31944,7 +31944,7 @@
         <v>45930</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>46160</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>45811</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32163,7 +32163,7 @@
         <v>45723</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32236,7 +32236,7 @@
         <v>46161</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>45832</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32382,7 +32382,7 @@
         <v>46161</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32455,7 +32455,7 @@
         <v>45837</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32533,7 +32533,7 @@
         <v>46161</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         <v>45562</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32684,7 +32684,7 @@
         <v>45840</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32757,7 +32757,7 @@
         <v>45840</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32830,7 +32830,7 @@
         <v>44991</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>46161</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>46161</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33054,7 +33054,7 @@
         <v>46162</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>46161</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33200,7 +33200,7 @@
         <v>45786</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>45813</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33351,7 +33351,7 @@
         <v>46162</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33424,7 +33424,7 @@
         <v>45790</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>46161</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33575,7 +33575,7 @@
         <v>46161</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33648,7 +33648,7 @@
         <v>45293</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33721,7 +33721,7 @@
         <v>44497</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         <v>45329</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33867,7 +33867,7 @@
         <v>45848</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>45848</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>46168</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34086,7 +34086,7 @@
         <v>45985</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>46167</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34232,7 +34232,7 @@
         <v>44847</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34310,7 +34310,7 @@
         <v>45749</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>45638</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34456,7 +34456,7 @@
         <v>46167</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34529,7 +34529,7 @@
         <v>46149</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>45853</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34680,7 +34680,7 @@
         <v>45352</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34758,7 +34758,7 @@
         <v>45793</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34831,7 +34831,7 @@
         <v>45265</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34909,7 +34909,7 @@
         <v>46165</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34982,7 +34982,7 @@
         <v>46170</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35055,7 +35055,7 @@
         <v>45729</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35128,7 +35128,7 @@
         <v>45741</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>45281</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>44973</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45910</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>46170</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>45574</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>46175</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>46175</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>46094</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35785,7 +35785,7 @@
         <v>45741</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>46175</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35931,7 +35931,7 @@
         <v>45409</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36004,7 +36004,7 @@
         <v>44819</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>45278</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>46174</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36233,7 +36233,7 @@
         <v>46177</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36306,7 +36306,7 @@
         <v>45502</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>46177</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36452,7 +36452,7 @@
         <v>46177</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>46177</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36603,7 +36603,7 @@
         <v>46177</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36676,7 +36676,7 @@
         <v>46177</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>46178</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36822,7 +36822,7 @@
         <v>44791</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36895,7 +36895,7 @@
         <v>45418</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36968,7 +36968,7 @@
         <v>46181</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37041,7 +37041,7 @@
         <v>46178</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37114,7 +37114,7 @@
         <v>44502</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>45126</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37260,7 +37260,7 @@
         <v>45874</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>45228</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>46182</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37479,7 +37479,7 @@
         <v>46184</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37552,7 +37552,7 @@
         <v>45161</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37630,7 +37630,7 @@
         <v>45390</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37703,7 +37703,7 @@
         <v>45148</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>45173</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37854,7 +37854,7 @@
         <v>45342</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>44496</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38000,7 +38000,7 @@
         <v>46189</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38073,7 +38073,7 @@
         <v>45800</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>45874</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38219,7 +38219,7 @@
         <v>46188</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38292,7 +38292,7 @@
         <v>45405</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>46189</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>46189</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38511,7 +38511,7 @@
         <v>46189</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38584,7 +38584,7 @@
         <v>46189</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>45874</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>45874</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>46191</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38881,7 +38881,7 @@
         <v>45409</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>45334</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>46190</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>46195</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>46195</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39246,7 +39246,7 @@
         <v>46195</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39319,7 +39319,7 @@
         <v>45628</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39392,7 +39392,7 @@
         <v>46195</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>46195</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39538,7 +39538,7 @@
         <v>46195</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39611,7 +39611,7 @@
         <v>45880</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39684,7 +39684,7 @@
         <v>44641</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39757,7 +39757,7 @@
         <v>45168</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39830,7 +39830,7 @@
         <v>45512</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>45639</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39976,7 +39976,7 @@
         <v>45147</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40049,7 +40049,7 @@
         <v>46203</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40127,7 +40127,7 @@
         <v>45595</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40200,7 +40200,7 @@
         <v>45595</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40273,7 +40273,7 @@
         <v>45616</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>46204</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>46204</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40497,7 +40497,7 @@
         <v>45884</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40570,7 +40570,7 @@
         <v>46205</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40643,7 +40643,7 @@
         <v>46204</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>46204</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40789,7 +40789,7 @@
         <v>46205</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40862,7 +40862,7 @@
         <v>46205</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>45800</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>44676</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>46206</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41154,7 +41154,7 @@
         <v>46206</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41227,7 +41227,7 @@
         <v>46206</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41300,7 +41300,7 @@
         <v>46206</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41373,7 +41373,7 @@
         <v>46252</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41446,7 +41446,7 @@
         <v>46251</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41524,7 +41524,7 @@
         <v>44694</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41602,7 +41602,7 @@
         <v>46209</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>46211</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41748,7 +41748,7 @@
         <v>45617</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41821,7 +41821,7 @@
         <v>45762</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41894,7 +41894,7 @@
         <v>46211</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41967,7 +41967,7 @@
         <v>44617</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>45428</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>45163</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>45152</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42259,7 +42259,7 @@
         <v>44858</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>46213</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>46258</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42478,7 +42478,7 @@
         <v>45348</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42551,7 +42551,7 @@
         <v>46213</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42624,7 +42624,7 @@
         <v>46213</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42697,7 +42697,7 @@
         <v>45163</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>46215</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42843,7 +42843,7 @@
         <v>46215</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>44706</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>44728</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43062,7 +43062,7 @@
         <v>46260</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43135,7 +43135,7 @@
         <v>46262</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>45181</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43281,7 +43281,7 @@
         <v>44728</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43354,7 +43354,7 @@
         <v>45189</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43427,7 +43427,7 @@
         <v>46219</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43500,7 +43500,7 @@
         <v>46219</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43573,7 +43573,7 @@
         <v>46219</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43646,7 +43646,7 @@
         <v>45699</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>45168</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43792,7 +43792,7 @@
         <v>44726</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43865,7 +43865,7 @@
         <v>45723</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>46265</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44016,7 +44016,7 @@
         <v>46161</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44089,7 +44089,7 @@
         <v>45166</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44167,7 +44167,7 @@
         <v>46203</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44240,7 +44240,7 @@
         <v>46213</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45251</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44386,7 +44386,7 @@
         <v>45350</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44464,7 +44464,7 @@
         <v>45293</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44537,7 +44537,7 @@
         <v>45320</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44610,7 +44610,7 @@
         <v>45231</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44683,7 +44683,7 @@
         <v>44747</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44756,7 +44756,7 @@
         <v>45072</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44829,7 +44829,7 @@
         <v>45313</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44902,7 +44902,7 @@
         <v>45366</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44975,7 +44975,7 @@
         <v>46274</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45048,7 +45048,7 @@
         <v>44853</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45121,7 +45121,7 @@
         <v>45749</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45194,7 +45194,7 @@
         <v>45757</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45267,7 +45267,7 @@
         <v>44792</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45340,7 +45340,7 @@
         <v>46232</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45413,7 +45413,7 @@
         <v>45733</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45486,7 +45486,7 @@
         <v>45496</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45559,7 +45559,7 @@
         <v>46275</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>45352</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45710,7 +45710,7 @@
         <v>45091</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45783,7 +45783,7 @@
         <v>45280</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45856,7 +45856,7 @@
         <v>46237</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45934,7 +45934,7 @@
         <v>45462</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46007,7 +46007,7 @@
         <v>46282</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46080,7 +46080,7 @@
         <v>46281</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46153,7 +46153,7 @@
         <v>44875</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46226,7 +46226,7 @@
         <v>46239</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46304,7 +46304,7 @@
         <v>46281</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46377,7 +46377,7 @@
         <v>45482</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46455,7 +46455,7 @@
         <v>45496</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46528,7 +46528,7 @@
         <v>44957</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46601,7 +46601,7 @@
         <v>46286</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46679,7 +46679,7 @@
         <v>44903</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46757,7 +46757,7 @@
         <v>44945</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46835,7 +46835,7 @@
         <v>46181</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46908,7 +46908,7 @@
         <v>46286</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46986,7 +46986,7 @@
         <v>46070</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47059,7 +47059,7 @@
         <v>46288</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47132,7 +47132,7 @@
         <v>46286</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47205,7 +47205,7 @@
         <v>45376</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47278,7 +47278,7 @@
         <v>46288</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47351,7 +47351,7 @@
         <v>46288</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47424,7 +47424,7 @@
         <v>46244</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47502,7 +47502,7 @@
         <v>46287</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47580,7 +47580,7 @@
         <v>46189</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47653,7 +47653,7 @@
         <v>46288</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47726,7 +47726,7 @@
         <v>44889</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>46248</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47877,7 +47877,7 @@
         <v>45289</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47950,7 +47950,7 @@
         <v>44845</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45072</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48101,7 +48101,7 @@
         <v>45194</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>45289</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>44580</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45476</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>45006</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48466,7 +48466,7 @@
         <v>45300</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48539,7 +48539,7 @@
         <v>45035</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>44987</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48690,7 +48690,7 @@
         <v>44869</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48763,7 +48763,7 @@
         <v>45392</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48836,7 +48836,7 @@
         <v>45000</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48914,7 +48914,7 @@
         <v>45000</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48992,7 +48992,7 @@
         <v>45250</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
         <v>45044</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49143,7 +49143,7 @@
         <v>45126</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49216,7 +49216,7 @@
         <v>45762</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45180</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49362,7 +49362,7 @@
         <v>45580</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49435,7 +49435,7 @@
         <v>45147</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49508,7 +49508,7 @@
         <v>45251</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>45482</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49659,7 +49659,7 @@
         <v>45769</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49737,7 +49737,7 @@
         <v>45646</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49810,7 +49810,7 @@
         <v>45107</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49883,7 +49883,7 @@
         <v>45723</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49956,7 +49956,7 @@
         <v>45097</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>44855</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50102,7 +50102,7 @@
         <v>45629</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50175,7 +50175,7 @@
         <v>45323</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50248,7 +50248,7 @@
         <v>45578</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50321,7 +50321,7 @@
         <v>45578</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>44951</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50472,7 +50472,7 @@
         <v>45531</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50545,7 +50545,7 @@
         <v>45512</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50618,7 +50618,7 @@
         <v>44867</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50691,7 +50691,7 @@
         <v>45729</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50764,7 +50764,7 @@
         <v>45376</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50837,7 +50837,7 @@
         <v>45730</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50910,7 +50910,7 @@
         <v>45685</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50983,7 +50983,7 @@
         <v>45776</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51056,7 +51056,7 @@
         <v>45776</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51129,7 +51129,7 @@
         <v>45782</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>45782</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51285,7 +51285,7 @@
         <v>45562</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51358,7 +51358,7 @@
         <v>45578</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>45791</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51504,7 +51504,7 @@
         <v>45342</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51577,7 +51577,7 @@
         <v>45574</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>45433</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51723,7 +51723,7 @@
         <v>45351</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51796,7 +51796,7 @@
         <v>44393</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>45323</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51947,7 +51947,7 @@
         <v>45733</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52025,7 +52025,7 @@
         <v>45755</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52098,7 +52098,7 @@
         <v>45793</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52176,7 +52176,7 @@
         <v>46078</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52254,7 +52254,7 @@
         <v>46073</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52327,7 +52327,7 @@
         <v>46093</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52405,7 +52405,7 @@
         <v>46156</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52478,7 +52478,7 @@
         <v>46267</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>

--- a/Översikt HÄRNÖSAND.xlsx
+++ b/Översikt HÄRNÖSAND.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45328</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>46288</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>46044</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>45588</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>45763</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>44686</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>45938</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>46189</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>45546</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>45394</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45930</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>45763</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>45484</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>45139</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>45805</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>45826</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45335</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>45082</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45027</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>44874</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>46183</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>45548</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45957</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>45352</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45188</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>45567</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>45593</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>45593</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>44979</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>45971</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>45477</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>45848</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>45314</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>46176</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>45513</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>45560</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>46251</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>45323</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>45790</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>44686</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>46003</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>45355</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>44755</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>45930</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>45617</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>45526</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>45182</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         <v>45322</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>46244</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
         <v>45596</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>44664</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>45618</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>45376</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>45930</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>45910</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>45967</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>45847</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>45575</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>46141</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>44874</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>45513</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>45267</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>46244</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>45996</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>44676</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>44585</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>44655</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>45554</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>45456</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>45008</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>45583</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>45350</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>46031</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>45805</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>45919</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>45805</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>45649</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>45811</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>46127</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>45352</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>46176</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>45276</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>46189</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10276,7 +10276,7 @@
         <v>46191</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>46184</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>46213</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
         <v>44559</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>45372</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>44837</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>45428</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>44874</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>44664</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11180,7 +11180,7 @@
         <v>44806</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>44846</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>44875</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>44532</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>44477</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>44608</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>44720</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>44600</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>44824</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>44487</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>44734</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>44512</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>44517</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>44728</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>44477</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
         <v>44475</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>44476</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         <v>44664</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>44804</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>44512</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>44503</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>44735</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12806,7 +12806,7 @@
         <v>44848</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>44581</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>44672</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
         <v>44652</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>44515</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>44664</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>44616</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>44496</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>44532</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>44571</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44512</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>44664</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>44536</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>44522</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>44585</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
         <v>44792</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>45334</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>45462</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>45293</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>44747</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14266,7 +14266,7 @@
         <v>44858</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
         <v>44881</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>44641</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>45209</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>45667</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>44617</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>45314</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>45576</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
         <v>45762</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>45281</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>45405</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>45496</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>45761</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>45574</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>45231</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>45887</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>46013</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>45126</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>45791</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>44853</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>45352</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>44809</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>45757</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>45888</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>45558</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>45890</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
         <v>46023</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>46023</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16340,7 +16340,7 @@
         <v>45890</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>46024</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>46024</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>45891</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16642,7 +16642,7 @@
         <v>45300</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>46024</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16788,7 +16788,7 @@
         <v>45228</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16861,7 +16861,7 @@
         <v>46026</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>46024</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         <v>45350</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17085,7 +17085,7 @@
         <v>45342</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17158,7 +17158,7 @@
         <v>45433</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17231,7 +17231,7 @@
         <v>46029</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>45628</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>45897</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>46029</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>46030</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>46029</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>46029</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17742,7 +17742,7 @@
         <v>46030</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>45351</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>46034</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17961,7 +17961,7 @@
         <v>46035</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>45901</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18107,7 +18107,7 @@
         <v>45793</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>45482</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
         <v>45803</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18336,7 +18336,7 @@
         <v>46038</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18409,7 +18409,7 @@
         <v>46038</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>46042</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>45106</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18633,7 +18633,7 @@
         <v>45579</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>44571</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>45266</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>45915</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>45915</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>46045</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>46049</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>45531</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>45516</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
         <v>45917</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>45799</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>45139</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>44475</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>45803</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>45762</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19743,7 +19743,7 @@
         <v>45919</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>45800</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>45805</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>45630</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>46055</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>46052</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>45923</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20269,7 +20269,7 @@
         <v>45922</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>46052</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         <v>45922</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20488,7 +20488,7 @@
         <v>46052</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>44853</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>45924</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20712,7 +20712,7 @@
         <v>45289</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20785,7 +20785,7 @@
         <v>46056</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>45924</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20931,7 +20931,7 @@
         <v>45924</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21004,7 +21004,7 @@
         <v>45924</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21077,7 +21077,7 @@
         <v>45924</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>45281</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21223,7 +21223,7 @@
         <v>45289</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21296,7 +21296,7 @@
         <v>46063</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>45278</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>46065</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>46065</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>46065</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>46065</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>46065</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21827,7 +21827,7 @@
         <v>45919</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21905,7 +21905,7 @@
         <v>45936</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         <v>45936</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>45936</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22124,7 +22124,7 @@
         <v>45181</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22197,7 +22197,7 @@
         <v>45937</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>46069</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45205</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>46070</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>46071</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>46071</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>45939</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>45578</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>45578</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22864,7 +22864,7 @@
         <v>46072</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22937,7 +22937,7 @@
         <v>46072</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23010,7 +23010,7 @@
         <v>45749</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23083,7 +23083,7 @@
         <v>46077</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>45811</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>44728</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>45757</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>46080</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>46085</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>46064</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>45496</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>45959</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>45959</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>46087</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>45812</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>45812</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>45764</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>46091</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>46091</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>46091</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>46091</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>46091</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>45483</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24553,7 +24553,7 @@
         <v>46094</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>46094</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
         <v>44603</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>45793</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24855,7 +24855,7 @@
         <v>45173</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>45203</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>45769</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>45168</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25157,7 +25157,7 @@
         <v>45972</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         <v>45972</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25313,7 +25313,7 @@
         <v>46104</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25386,7 +25386,7 @@
         <v>45975</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25464,7 +25464,7 @@
         <v>46101</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>45975</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>46105</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25693,7 +25693,7 @@
         <v>45978</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>44980</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>45979</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>45979</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>45097</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>46105</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>45979</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26214,7 +26214,7 @@
         <v>45979</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>46106</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>45979</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>45701</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>46105</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>46105</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>45979</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>45979</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>45981</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>46107</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>45981</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>46107</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>46107</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27193,7 +27193,7 @@
         <v>45729</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>45562</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>45987</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>46113</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         <v>45825</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>45825</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
         <v>45825</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>45825</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27782,7 +27782,7 @@
         <v>45617</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>45352</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27933,7 +27933,7 @@
         <v>46120</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28006,7 +28006,7 @@
         <v>45769</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>45824</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28162,7 +28162,7 @@
         <v>45730</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         <v>46122</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>45992</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28381,7 +28381,7 @@
         <v>45342</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28454,7 +28454,7 @@
         <v>45531</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
         <v>45126</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28600,7 +28600,7 @@
         <v>45826</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
         <v>45638</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28751,7 +28751,7 @@
         <v>45999</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>45999</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>45999</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>45293</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>45180</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>46127</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29189,7 +29189,7 @@
         <v>44853</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29262,7 +29262,7 @@
         <v>46000</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>45147</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29408,7 +29408,7 @@
         <v>46133</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29481,7 +29481,7 @@
         <v>45833</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29559,7 +29559,7 @@
         <v>46132</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29632,7 +29632,7 @@
         <v>46133</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29705,7 +29705,7 @@
         <v>45833</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>45320</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29856,7 +29856,7 @@
         <v>45833</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>45168</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30007,7 +30007,7 @@
         <v>45833</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>45293</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>45833</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30236,7 +30236,7 @@
         <v>45834</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30309,7 +30309,7 @@
         <v>45811</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
         <v>45834</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         <v>45837</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30533,7 +30533,7 @@
         <v>45837</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>45840</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30684,7 +30684,7 @@
         <v>45168</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30757,7 +30757,7 @@
         <v>45840</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30830,7 +30830,7 @@
         <v>45072</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30903,7 +30903,7 @@
         <v>44936</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>45511</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31049,7 +31049,7 @@
         <v>45749</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31122,7 +31122,7 @@
         <v>44728</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31195,7 +31195,7 @@
         <v>45749</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>45848</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31341,7 +31341,7 @@
         <v>45848</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31414,7 +31414,7 @@
         <v>44971</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31492,7 +31492,7 @@
         <v>45489</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>45853</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31648,7 +31648,7 @@
         <v>44791</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31721,7 +31721,7 @@
         <v>45273</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31794,7 +31794,7 @@
         <v>45126</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>45685</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>44973</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>44987</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>45189</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>45376</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32237,7 +32237,7 @@
         <v>44869</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32310,7 +32310,7 @@
         <v>46065</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>45771</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32461,7 +32461,7 @@
         <v>45006</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>45741</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32607,7 +32607,7 @@
         <v>45428</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>45562</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32758,7 +32758,7 @@
         <v>45904</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32831,7 +32831,7 @@
         <v>45793</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32904,7 +32904,7 @@
         <v>46024</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>45409</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33050,7 +33050,7 @@
         <v>45729</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33123,7 +33123,7 @@
         <v>45645</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33196,7 +33196,7 @@
         <v>45825</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33269,7 +33269,7 @@
         <v>45409</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33342,7 +33342,7 @@
         <v>45526</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33415,7 +33415,7 @@
         <v>45574</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33488,7 +33488,7 @@
         <v>45741</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33561,7 +33561,7 @@
         <v>45523</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33634,7 +33634,7 @@
         <v>45887</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>45840</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33780,7 +33780,7 @@
         <v>46072</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33853,7 +33853,7 @@
         <v>46142</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33926,7 +33926,7 @@
         <v>46142</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33999,7 +33999,7 @@
         <v>45147</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34072,7 +34072,7 @@
         <v>45462</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34145,7 +34145,7 @@
         <v>45161</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34223,7 +34223,7 @@
         <v>45418</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34296,7 +34296,7 @@
         <v>45091</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34369,7 +34369,7 @@
         <v>44937</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34442,7 +34442,7 @@
         <v>46150</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>46153</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34588,7 +34588,7 @@
         <v>46153</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34661,7 +34661,7 @@
         <v>45723</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34734,7 +34734,7 @@
         <v>45733</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>45874</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34880,7 +34880,7 @@
         <v>45874</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>46155</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35026,7 +35026,7 @@
         <v>45930</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>45293</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>46107</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35245,7 +35245,7 @@
         <v>45392</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35318,7 +35318,7 @@
         <v>45044</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35391,7 +35391,7 @@
         <v>44951</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35469,7 +35469,7 @@
         <v>46161</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35542,7 +35542,7 @@
         <v>46161</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>46161</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35688,7 +35688,7 @@
         <v>45786</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35766,7 +35766,7 @@
         <v>45790</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>45874</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         <v>46160</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>45813</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36063,7 +36063,7 @@
         <v>46161</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36136,7 +36136,7 @@
         <v>46161</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36209,7 +36209,7 @@
         <v>46161</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36282,7 +36282,7 @@
         <v>44897</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36355,7 +36355,7 @@
         <v>46161</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36428,7 +36428,7 @@
         <v>46161</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36501,7 +36501,7 @@
         <v>45044</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36579,7 +36579,7 @@
         <v>45874</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36652,7 +36652,7 @@
         <v>46162</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>46162</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36798,7 +36798,7 @@
         <v>45832</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>44732</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36944,7 +36944,7 @@
         <v>44596</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37022,7 +37022,7 @@
         <v>44706</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>45512</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>46167</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>46167</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37314,7 +37314,7 @@
         <v>45880</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>45638</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37460,7 +37460,7 @@
         <v>46149</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>46168</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37606,7 +37606,7 @@
         <v>45985</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>46170</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37752,7 +37752,7 @@
         <v>46170</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37825,7 +37825,7 @@
         <v>46174</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37898,7 +37898,7 @@
         <v>45646</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>45329</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>45910</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38117,7 +38117,7 @@
         <v>46094</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
         <v>46165</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38263,7 +38263,7 @@
         <v>46175</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>46175</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>46175</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38482,7 +38482,7 @@
         <v>46178</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38555,7 +38555,7 @@
         <v>46177</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38628,7 +38628,7 @@
         <v>46177</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>46177</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38774,7 +38774,7 @@
         <v>46177</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38847,7 +38847,7 @@
         <v>46178</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38920,7 +38920,7 @@
         <v>45887</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38993,7 +38993,7 @@
         <v>45616</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39071,7 +39071,7 @@
         <v>45884</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39144,7 +39144,7 @@
         <v>45320</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39217,7 +39217,7 @@
         <v>46177</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>46181</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39363,7 +39363,7 @@
         <v>46182</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39436,7 +39436,7 @@
         <v>45035</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39509,7 +39509,7 @@
         <v>45163</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>46184</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39655,7 +39655,7 @@
         <v>44853</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39728,7 +39728,7 @@
         <v>46188</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39801,7 +39801,7 @@
         <v>45138</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39874,7 +39874,7 @@
         <v>45800</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39947,7 +39947,7 @@
         <v>46189</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40020,7 +40020,7 @@
         <v>46189</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40093,7 +40093,7 @@
         <v>46189</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40166,7 +40166,7 @@
         <v>45531</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40244,7 +40244,7 @@
         <v>44867</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40317,7 +40317,7 @@
         <v>46189</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40390,7 +40390,7 @@
         <v>46190</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40463,7 +40463,7 @@
         <v>46189</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40536,7 +40536,7 @@
         <v>46191</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40614,7 +40614,7 @@
         <v>45390</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40687,7 +40687,7 @@
         <v>45678</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40765,7 +40765,7 @@
         <v>46195</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40838,7 +40838,7 @@
         <v>46195</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40911,7 +40911,7 @@
         <v>46195</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40984,7 +40984,7 @@
         <v>46195</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41057,7 +41057,7 @@
         <v>46195</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41130,7 +41130,7 @@
         <v>46195</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41203,7 +41203,7 @@
         <v>45072</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41281,7 +41281,7 @@
         <v>44676</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41354,7 +41354,7 @@
         <v>45015</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
         <v>45749</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41505,7 +41505,7 @@
         <v>46203</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41583,7 +41583,7 @@
         <v>46204</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41656,7 +41656,7 @@
         <v>46204</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41729,7 +41729,7 @@
         <v>46204</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41802,7 +41802,7 @@
         <v>46204</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41875,7 +41875,7 @@
         <v>46205</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41948,7 +41948,7 @@
         <v>46205</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42021,7 +42021,7 @@
         <v>46205</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42094,7 +42094,7 @@
         <v>45313</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42167,7 +42167,7 @@
         <v>46206</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42240,7 +42240,7 @@
         <v>46206</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42313,7 +42313,7 @@
         <v>46206</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42386,7 +42386,7 @@
         <v>45800</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>46206</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>45622</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42605,7 +42605,7 @@
         <v>46209</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>46211</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42751,7 +42751,7 @@
         <v>44971</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42829,7 +42829,7 @@
         <v>46211</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42902,7 +42902,7 @@
         <v>45148</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>45243</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43048,7 +43048,7 @@
         <v>44845</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43121,7 +43121,7 @@
         <v>45409</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>46258</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43267,7 +43267,7 @@
         <v>44580</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>46215</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43413,7 +43413,7 @@
         <v>46215</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>45348</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43559,7 +43559,7 @@
         <v>46213</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43632,7 +43632,7 @@
         <v>46213</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43705,7 +43705,7 @@
         <v>44894</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>46260</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43851,7 +43851,7 @@
         <v>45366</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43924,7 +43924,7 @@
         <v>46219</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43997,7 +43997,7 @@
         <v>46219</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44070,7 +44070,7 @@
         <v>46219</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44143,7 +44143,7 @@
         <v>46213</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44216,7 +44216,7 @@
         <v>46203</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>45251</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44362,7 +44362,7 @@
         <v>44498</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44435,7 +44435,7 @@
         <v>45376</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>46161</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>46262</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44654,7 +44654,7 @@
         <v>46265</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44732,7 +44732,7 @@
         <v>44865</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44810,7 +44810,7 @@
         <v>45699</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44883,7 +44883,7 @@
         <v>45044</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>45502</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45034,7 +45034,7 @@
         <v>44726</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>44889</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45185,7 +45185,7 @@
         <v>46275</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>46274</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45331,7 +45331,7 @@
         <v>46232</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45404,7 +45404,7 @@
         <v>44755</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>44881</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45555,7 +45555,7 @@
         <v>45194</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45628,7 +45628,7 @@
         <v>46237</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45706,7 +45706,7 @@
         <v>45505</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45784,7 +45784,7 @@
         <v>46281</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45857,7 +45857,7 @@
         <v>44847</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45935,7 +45935,7 @@
         <v>46281</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46008,7 +46008,7 @@
         <v>44847</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46086,7 +46086,7 @@
         <v>45723</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>45482</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>46239</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46315,7 +46315,7 @@
         <v>45328</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46393,7 +46393,7 @@
         <v>45328</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46471,7 +46471,7 @@
         <v>46282</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46544,7 +46544,7 @@
         <v>45390</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46617,7 +46617,7 @@
         <v>44496</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46690,7 +46690,7 @@
         <v>44875</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46763,7 +46763,7 @@
         <v>44531</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46836,7 +46836,7 @@
         <v>45729</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46909,7 +46909,7 @@
         <v>45545</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
         <v>46189</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47055,7 +47055,7 @@
         <v>45595</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47128,7 +47128,7 @@
         <v>45595</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47201,7 +47201,7 @@
         <v>46070</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47274,7 +47274,7 @@
         <v>46286</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47352,7 +47352,7 @@
         <v>46286</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47430,7 +47430,7 @@
         <v>45280</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47503,7 +47503,7 @@
         <v>46244</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47581,7 +47581,7 @@
         <v>46287</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47659,7 +47659,7 @@
         <v>44694</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47737,7 +47737,7 @@
         <v>46181</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47810,7 +47810,7 @@
         <v>46288</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47883,7 +47883,7 @@
         <v>46288</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47956,7 +47956,7 @@
         <v>46286</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48029,7 +48029,7 @@
         <v>44743</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48102,7 +48102,7 @@
         <v>44806</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48175,7 +48175,7 @@
         <v>44806</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48248,7 +48248,7 @@
         <v>46288</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48321,7 +48321,7 @@
         <v>45714</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48394,7 +48394,7 @@
         <v>46248</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48467,7 +48467,7 @@
         <v>44991</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48545,7 +48545,7 @@
         <v>45250</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48618,7 +48618,7 @@
         <v>45580</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48691,7 +48691,7 @@
         <v>45281</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48764,7 +48764,7 @@
         <v>44957</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48837,7 +48837,7 @@
         <v>45265</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48915,7 +48915,7 @@
         <v>46252</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45476</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45476</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49134,7 +49134,7 @@
         <v>46251</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45166</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49290,7 +49290,7 @@
         <v>44855</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49363,7 +49363,7 @@
         <v>46296</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49441,7 +49441,7 @@
         <v>44890</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49519,7 +49519,7 @@
         <v>46296</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49597,7 +49597,7 @@
         <v>46296</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49675,7 +49675,7 @@
         <v>46296</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49753,7 +49753,7 @@
         <v>46297</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49826,7 +49826,7 @@
         <v>46288</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49899,7 +49899,7 @@
         <v>44945</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49977,7 +49977,7 @@
         <v>46297</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50055,7 +50055,7 @@
         <v>44903</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50133,7 +50133,7 @@
         <v>45251</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>45512</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50279,7 +50279,7 @@
         <v>45723</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>44497</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50425,7 +50425,7 @@
         <v>44502</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50498,7 +50498,7 @@
         <v>45323</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50571,7 +50571,7 @@
         <v>45639</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>44609</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50722,7 +50722,7 @@
         <v>44952</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50795,7 +50795,7 @@
         <v>44747</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50868,7 +50868,7 @@
         <v>45152</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50941,7 +50941,7 @@
         <v>45099</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>45629</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51092,7 +51092,7 @@
         <v>45000</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51170,7 +51170,7 @@
         <v>45000</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51248,7 +51248,7 @@
         <v>44819</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51326,7 +51326,7 @@
         <v>45762</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51399,7 +51399,7 @@
         <v>45163</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51472,7 +51472,7 @@
         <v>45107</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51545,7 +51545,7 @@
         <v>45685</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51618,7 +51618,7 @@
         <v>45776</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51691,7 +51691,7 @@
         <v>45776</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51764,7 +51764,7 @@
         <v>45782</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51842,7 +51842,7 @@
         <v>45782</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51920,7 +51920,7 @@
         <v>45562</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51993,7 +51993,7 @@
         <v>45578</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52066,7 +52066,7 @@
         <v>44393</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52139,7 +52139,7 @@
         <v>45323</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52217,7 +52217,7 @@
         <v>45733</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52295,7 +52295,7 @@
         <v>45755</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52368,7 +52368,7 @@
         <v>45793</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>46078</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52524,7 +52524,7 @@
         <v>46073</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52597,7 +52597,7 @@
         <v>46093</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52675,7 +52675,7 @@
         <v>46156</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52748,7 +52748,7 @@
         <v>46267</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>

--- a/Översikt HÄRNÖSAND.xlsx
+++ b/Översikt HÄRNÖSAND.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45328</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>46288</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>46044</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>45588</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>45763</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>44686</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>46189</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>45938</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>45546</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>45394</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45763</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>45930</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>45139</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>45484</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>45805</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>45826</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45335</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>45027</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>45082</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>44874</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>46183</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>45188</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>45593</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>45548</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45352</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>45593</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>45957</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>45567</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>44979</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>45477</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>45513</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>45560</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>45971</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>45848</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>45314</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>46176</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>46251</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>45323</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>45790</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>44686</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>45355</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>45930</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>45617</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>45182</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>45596</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>45526</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         <v>46003</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44755</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>46244</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>45322</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>44664</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>45376</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>45267</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44874</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>45513</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>45930</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>45910</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>45618</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45967</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>45847</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>45575</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>46141</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>46244</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>46303</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>45996</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>44676</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         <v>44585</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>44655</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>44837</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>45649</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         <v>45428</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>45352</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9099,7 +9099,7 @@
         <v>44559</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>45919</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>45583</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>45805</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>45805</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>45811</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         <v>45350</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>45372</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>45008</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>46127</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>45456</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>46031</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>45554</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         <v>45276</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>46176</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>46189</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>46184</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>46213</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>46191</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>44874</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>44664</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>44806</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>44846</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
         <v>44532</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         <v>44875</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         <v>44608</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         <v>44720</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
         <v>44600</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>44824</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11889,7 +11889,7 @@
         <v>44487</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>44734</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>44512</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>44517</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>44728</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>44848</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         <v>44581</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>44571</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>44512</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>44672</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>44652</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>44512</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
         <v>44503</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>44515</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>44664</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>44664</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>44664</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13140,7 +13140,7 @@
         <v>44616</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>44804</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>44496</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         <v>44532</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>44536</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>44735</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>44522</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>44585</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13724,7 +13724,7 @@
         <v>45531</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         <v>45409</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>45762</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         <v>45180</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         <v>44596</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>45580</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>45147</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>45483</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>45044</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44806</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>44806</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>45099</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>45251</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>45482</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>45723</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>45769</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         <v>45328</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>45328</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         <v>44809</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>45646</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>45107</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>45562</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>44991</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>44853</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>45293</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>44497</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>45329</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15740,7 +15740,7 @@
         <v>45723</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
         <v>45884</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>44847</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>45281</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>45097</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>45352</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>45281</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>45489</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>44855</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45462</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>45629</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45323</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>45578</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>45578</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>45273</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>44951</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>44952</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>45531</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>45265</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>45888</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>45512</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>45281</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>44867</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17444,7 +17444,7 @@
         <v>45887</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>45761</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>45511</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         <v>45887</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>45243</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17814,7 +17814,7 @@
         <v>44881</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>44865</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>45890</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>45729</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>45890</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>45476</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>45409</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>44937</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>45531</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
         <v>45891</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>45897</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>45376</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45901</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>44498</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>45730</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>44853</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>44819</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>45278</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19163,7 +19163,7 @@
         <v>45729</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>45502</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>45293</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>45803</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>45562</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>44531</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>45685</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>45776</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>45776</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19820,7 +19820,7 @@
         <v>44791</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45782</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19971,7 +19971,7 @@
         <v>45782</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>45418</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20122,7 +20122,7 @@
         <v>44502</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>45126</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>45915</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
         <v>45228</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20419,7 +20419,7 @@
         <v>45161</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20497,7 +20497,7 @@
         <v>45562</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20570,7 +20570,7 @@
         <v>45209</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>45915</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         <v>45390</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20799,7 +20799,7 @@
         <v>45148</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>44897</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20945,7 +20945,7 @@
         <v>45917</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21018,7 +21018,7 @@
         <v>45558</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21091,7 +21091,7 @@
         <v>45173</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>45342</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>44496</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>45405</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21388,7 +21388,7 @@
         <v>45919</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>45922</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>45578</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         <v>45922</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>44881</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>45923</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>45924</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
         <v>45924</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>45924</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22060,7 +22060,7 @@
         <v>45924</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22133,7 +22133,7 @@
         <v>45924</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22206,7 +22206,7 @@
         <v>45409</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>45334</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22352,7 +22352,7 @@
         <v>44894</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
         <v>45791</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>45342</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22571,7 +22571,7 @@
         <v>44609</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>45628</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22722,7 +22722,7 @@
         <v>45574</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>45576</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>45433</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>45351</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>45320</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>44571</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>44641</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>45168</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23311,7 +23311,7 @@
         <v>45579</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>45512</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>45639</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>45793</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>45266</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>45516</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>45139</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>45147</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>45919</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>45799</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>45701</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24134,7 +24134,7 @@
         <v>45936</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24207,7 +24207,7 @@
         <v>45595</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>45595</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24353,7 +24353,7 @@
         <v>45800</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>45616</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>45757</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>45936</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>45936</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>45390</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>45505</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>45803</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         <v>44676</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>45762</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>44755</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>45805</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>45630</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>44694</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>44747</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>45937</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>45205</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>45939</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25697,7 +25697,7 @@
         <v>45617</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>45811</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>45762</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>45812</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25989,7 +25989,7 @@
         <v>45812</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26062,7 +26062,7 @@
         <v>44617</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>45428</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26208,7 +26208,7 @@
         <v>45163</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>45622</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26354,7 +26354,7 @@
         <v>45152</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>44732</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>44858</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>45293</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26646,7 +26646,7 @@
         <v>44890</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>45015</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26802,7 +26802,7 @@
         <v>45314</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26875,7 +26875,7 @@
         <v>45824</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>45163</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>45825</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>45825</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>45825</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>45825</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27318,7 +27318,7 @@
         <v>44706</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>45826</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>44728</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>45959</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>45959</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>44971</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27766,7 +27766,7 @@
         <v>45833</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>45833</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27922,7 +27922,7 @@
         <v>45834</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27995,7 +27995,7 @@
         <v>45833</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28073,7 +28073,7 @@
         <v>45638</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>45833</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>45833</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>45834</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>45181</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>45837</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>44728</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>45189</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>45811</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28745,7 +28745,7 @@
         <v>45837</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28823,7 +28823,7 @@
         <v>45699</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28896,7 +28896,7 @@
         <v>45840</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>44743</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>45840</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29115,7 +29115,7 @@
         <v>45168</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29188,7 +29188,7 @@
         <v>44847</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29266,7 +29266,7 @@
         <v>45793</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29344,7 +29344,7 @@
         <v>44726</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29417,7 +29417,7 @@
         <v>45667</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>45723</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29563,7 +29563,7 @@
         <v>45848</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29636,7 +29636,7 @@
         <v>45972</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>45848</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29787,7 +29787,7 @@
         <v>45972</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29865,7 +29865,7 @@
         <v>45166</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29943,7 +29943,7 @@
         <v>45749</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>45645</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30089,7 +30089,7 @@
         <v>45975</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30167,7 +30167,7 @@
         <v>45853</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>45251</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>45168</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>44853</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30464,7 +30464,7 @@
         <v>45350</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>45793</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30615,7 +30615,7 @@
         <v>45293</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30688,7 +30688,7 @@
         <v>45729</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>45741</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>45138</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>45978</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>45320</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>44973</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31131,7 +31131,7 @@
         <v>45231</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>45574</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31277,7 +31277,7 @@
         <v>44747</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31350,7 +31350,7 @@
         <v>45741</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31423,7 +31423,7 @@
         <v>45072</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31496,7 +31496,7 @@
         <v>45975</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>45979</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31652,7 +31652,7 @@
         <v>45313</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>45366</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>45979</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>45545</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>45979</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32022,7 +32022,7 @@
         <v>45874</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>44980</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>44853</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>45874</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>45979</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32387,7 +32387,7 @@
         <v>45979</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>45678</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>45874</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>45874</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32689,7 +32689,7 @@
         <v>45979</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32767,7 +32767,7 @@
         <v>45764</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32845,7 +32845,7 @@
         <v>45979</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32918,7 +32918,7 @@
         <v>44971</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32996,7 +32996,7 @@
         <v>45981</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>44936</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>45880</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>45749</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>45757</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>45981</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>44792</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33517,7 +33517,7 @@
         <v>45769</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33595,7 +33595,7 @@
         <v>45733</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>45496</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>45352</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33819,7 +33819,7 @@
         <v>46094</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>46094</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>45685</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>45091</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34116,7 +34116,7 @@
         <v>45280</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>46101</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34267,7 +34267,7 @@
         <v>45749</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34340,7 +34340,7 @@
         <v>46104</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>45462</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34486,7 +34486,7 @@
         <v>45749</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34559,7 +34559,7 @@
         <v>46105</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34632,7 +34632,7 @@
         <v>46105</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34705,7 +34705,7 @@
         <v>46105</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>44603</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>46105</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>46107</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34997,7 +34997,7 @@
         <v>44875</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>45482</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>45044</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35226,7 +35226,7 @@
         <v>46107</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35299,7 +35299,7 @@
         <v>46107</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35372,7 +35372,7 @@
         <v>46106</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>45203</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>45106</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>45987</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>45714</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>46113</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35820,7 +35820,7 @@
         <v>45496</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>44957</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35966,7 +35966,7 @@
         <v>45992</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36039,7 +36039,7 @@
         <v>44903</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36117,7 +36117,7 @@
         <v>46120</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>44945</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>46122</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36341,7 +36341,7 @@
         <v>46127</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36414,7 +36414,7 @@
         <v>45126</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36487,7 +36487,7 @@
         <v>45999</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>45999</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36633,7 +36633,7 @@
         <v>45999</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36706,7 +36706,7 @@
         <v>46000</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>45376</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36852,7 +36852,7 @@
         <v>46132</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36925,7 +36925,7 @@
         <v>46133</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>46133</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>44889</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37149,7 +37149,7 @@
         <v>45289</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>44845</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>45072</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45194</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37446,7 +37446,7 @@
         <v>45289</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>44580</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37592,7 +37592,7 @@
         <v>45476</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37665,7 +37665,7 @@
         <v>45904</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37738,7 +37738,7 @@
         <v>46013</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>45006</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>46024</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>46024</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38030,7 +38030,7 @@
         <v>46023</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>46024</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38176,7 +38176,7 @@
         <v>46023</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38249,7 +38249,7 @@
         <v>46024</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38322,7 +38322,7 @@
         <v>45300</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>46026</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38468,7 +38468,7 @@
         <v>45035</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>44987</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>46029</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>46029</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38765,7 +38765,7 @@
         <v>46029</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38838,7 +38838,7 @@
         <v>45526</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>46030</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38984,7 +38984,7 @@
         <v>46029</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>46030</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39130,7 +39130,7 @@
         <v>46065</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39208,7 +39208,7 @@
         <v>44869</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39281,7 +39281,7 @@
         <v>46034</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39354,7 +39354,7 @@
         <v>45392</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39427,7 +39427,7 @@
         <v>46035</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39500,7 +39500,7 @@
         <v>46038</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39573,7 +39573,7 @@
         <v>46038</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39646,7 +39646,7 @@
         <v>46042</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>45000</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>45000</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>45250</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39948,7 +39948,7 @@
         <v>45771</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40021,7 +40021,7 @@
         <v>45044</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40099,7 +40099,7 @@
         <v>45126</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40172,7 +40172,7 @@
         <v>45825</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40245,7 +40245,7 @@
         <v>45523</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40318,7 +40318,7 @@
         <v>46045</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40391,7 +40391,7 @@
         <v>45840</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40464,7 +40464,7 @@
         <v>45887</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>46052</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40610,7 +40610,7 @@
         <v>46052</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40683,7 +40683,7 @@
         <v>46052</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40761,7 +40761,7 @@
         <v>46055</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40834,7 +40834,7 @@
         <v>46056</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40907,7 +40907,7 @@
         <v>46072</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>46024</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41053,7 +41053,7 @@
         <v>46142</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>46142</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>46063</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41272,7 +41272,7 @@
         <v>46065</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41350,7 +41350,7 @@
         <v>46065</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41428,7 +41428,7 @@
         <v>46065</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>46065</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>46065</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>46070</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41725,7 +41725,7 @@
         <v>46150</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41798,7 +41798,7 @@
         <v>46069</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>46072</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41944,7 +41944,7 @@
         <v>46071</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42017,7 +42017,7 @@
         <v>46071</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42090,7 +42090,7 @@
         <v>46072</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42163,7 +42163,7 @@
         <v>46107</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42236,7 +42236,7 @@
         <v>46153</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>46077</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42382,7 +42382,7 @@
         <v>46153</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42455,7 +42455,7 @@
         <v>46080</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42528,7 +42528,7 @@
         <v>46085</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42601,7 +42601,7 @@
         <v>46064</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42674,7 +42674,7 @@
         <v>46155</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>45930</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42820,7 +42820,7 @@
         <v>46087</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42898,7 +42898,7 @@
         <v>46091</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42971,7 +42971,7 @@
         <v>46160</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43044,7 +43044,7 @@
         <v>46091</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>46091</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>46091</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43263,7 +43263,7 @@
         <v>46091</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>46161</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43409,7 +43409,7 @@
         <v>45832</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>46161</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43555,7 +43555,7 @@
         <v>46161</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43628,7 +43628,7 @@
         <v>46161</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43701,7 +43701,7 @@
         <v>46161</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>46162</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43847,7 +43847,7 @@
         <v>46161</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45786</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>45813</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>46162</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>45790</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44222,7 +44222,7 @@
         <v>46161</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44295,7 +44295,7 @@
         <v>46161</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44368,7 +44368,7 @@
         <v>46168</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44441,7 +44441,7 @@
         <v>45985</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>46167</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44587,7 +44587,7 @@
         <v>45638</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>46167</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>46149</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44806,7 +44806,7 @@
         <v>46165</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>46170</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>45910</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45025,7 +45025,7 @@
         <v>46170</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>46175</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>46175</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>46094</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>46175</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45390,7 +45390,7 @@
         <v>46174</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45463,7 +45463,7 @@
         <v>46177</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>46177</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45609,7 +45609,7 @@
         <v>46177</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45682,7 +45682,7 @@
         <v>46177</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45755,7 +45755,7 @@
         <v>46177</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>46178</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>46181</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>46178</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>46182</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46120,7 +46120,7 @@
         <v>46184</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>46189</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>45800</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46339,7 +46339,7 @@
         <v>46188</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>46189</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>46189</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         <v>46189</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46631,7 +46631,7 @@
         <v>46189</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>46191</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46782,7 +46782,7 @@
         <v>46190</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46855,7 +46855,7 @@
         <v>46195</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>46195</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47001,7 +47001,7 @@
         <v>46195</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47074,7 +47074,7 @@
         <v>46195</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47147,7 +47147,7 @@
         <v>46195</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47220,7 +47220,7 @@
         <v>46195</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47293,7 +47293,7 @@
         <v>46203</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47371,7 +47371,7 @@
         <v>46204</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47444,7 +47444,7 @@
         <v>46204</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47517,7 +47517,7 @@
         <v>46205</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47590,7 +47590,7 @@
         <v>46204</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47663,7 +47663,7 @@
         <v>46204</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47736,7 +47736,7 @@
         <v>46205</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47809,7 +47809,7 @@
         <v>46205</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47882,7 +47882,7 @@
         <v>45800</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47955,7 +47955,7 @@
         <v>46206</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48028,7 +48028,7 @@
         <v>46206</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48101,7 +48101,7 @@
         <v>46206</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>46206</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>46209</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>46211</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>46211</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48466,7 +48466,7 @@
         <v>46213</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48539,7 +48539,7 @@
         <v>45348</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>46213</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48685,7 +48685,7 @@
         <v>46215</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48758,7 +48758,7 @@
         <v>46215</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48831,7 +48831,7 @@
         <v>46219</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48904,7 +48904,7 @@
         <v>46219</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48977,7 +48977,7 @@
         <v>46219</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>46265</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49128,7 +49128,7 @@
         <v>46161</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49201,7 +49201,7 @@
         <v>46203</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49274,7 +49274,7 @@
         <v>46213</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49347,7 +49347,7 @@
         <v>46274</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49420,7 +49420,7 @@
         <v>46232</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49493,7 +49493,7 @@
         <v>46275</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         <v>46237</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49644,7 +49644,7 @@
         <v>46282</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>46281</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>46239</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49868,7 +49868,7 @@
         <v>46281</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49941,7 +49941,7 @@
         <v>46286</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50019,7 +50019,7 @@
         <v>46181</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50092,7 +50092,7 @@
         <v>46286</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50170,7 +50170,7 @@
         <v>46070</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50243,7 +50243,7 @@
         <v>46288</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50316,7 +50316,7 @@
         <v>46286</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50389,7 +50389,7 @@
         <v>46288</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50462,7 +50462,7 @@
         <v>46244</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50540,7 +50540,7 @@
         <v>46287</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50618,7 +50618,7 @@
         <v>46189</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50691,7 +50691,7 @@
         <v>46288</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50764,7 +50764,7 @@
         <v>46248</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50837,7 +50837,7 @@
         <v>46296</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50915,7 +50915,7 @@
         <v>46252</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>46296</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51066,7 +51066,7 @@
         <v>46296</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51144,7 +51144,7 @@
         <v>46296</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51222,7 +51222,7 @@
         <v>46297</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51300,7 +51300,7 @@
         <v>46251</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51378,7 +51378,7 @@
         <v>46297</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51451,7 +51451,7 @@
         <v>46288</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51524,7 +51524,7 @@
         <v>46301</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51597,7 +51597,7 @@
         <v>46258</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51670,7 +51670,7 @@
         <v>46303</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51748,7 +51748,7 @@
         <v>46262</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51821,7 +51821,7 @@
         <v>46260</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51894,7 +51894,7 @@
         <v>46304</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51967,7 +51967,7 @@
         <v>46049</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>44393</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52113,7 +52113,7 @@
         <v>45323</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         <v>45733</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52269,7 +52269,7 @@
         <v>45755</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52342,7 +52342,7 @@
         <v>45793</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52420,7 +52420,7 @@
         <v>46078</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52498,7 +52498,7 @@
         <v>46073</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52571,7 +52571,7 @@
         <v>46093</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52649,7 +52649,7 @@
         <v>46156</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52722,7 +52722,7 @@
         <v>46267</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>

--- a/Översikt HÄRNÖSAND.xlsx
+++ b/Översikt HÄRNÖSAND.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45328</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>46288</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>46044</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>45588</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>45763</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>44686</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>46189</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>45938</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>45546</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>45394</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45763</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>45930</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>45139</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>45484</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>45805</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>45826</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45335</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>45027</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>45082</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>44874</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>46183</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>45188</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>45593</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>45548</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45352</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>45593</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>45957</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>45567</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>44979</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>45477</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>45513</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>45560</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>45971</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>45848</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>45314</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>46176</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>46251</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>45323</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>45790</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>44686</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>45355</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>45930</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>45617</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>45182</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>45596</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>45526</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         <v>46003</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44755</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>46244</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>45322</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>44664</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>45376</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>45267</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44874</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>45513</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>45930</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>45910</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>45618</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45967</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>45847</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>45575</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>46141</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>46244</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>46303</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>45996</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>44676</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         <v>44585</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>44655</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>44837</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>45649</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         <v>45428</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>45352</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9099,7 +9099,7 @@
         <v>44559</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>45919</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>45583</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>45805</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>45805</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>45811</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         <v>45350</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>45372</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>45008</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>46127</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>45456</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>46031</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>45554</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         <v>45276</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>46176</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>46189</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>46184</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>46213</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>46191</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>44874</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>44664</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>44806</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>44846</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
         <v>44532</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         <v>44875</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         <v>44608</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         <v>44720</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
         <v>44600</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>44824</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11889,7 +11889,7 @@
         <v>44487</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>44734</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>44512</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>44517</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>44728</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>44848</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         <v>44581</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>44571</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>44512</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>44672</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>44652</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>44512</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
         <v>44503</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>44515</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>44664</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>44664</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>44664</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13140,7 +13140,7 @@
         <v>44616</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>44804</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>44496</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         <v>44532</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>44536</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>44735</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>44522</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>44585</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13724,7 +13724,7 @@
         <v>45531</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         <v>45409</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>45762</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         <v>45180</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         <v>44596</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>45580</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>45147</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>45483</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>45044</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44806</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>44806</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>45099</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>45251</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>45482</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>45723</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>45769</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         <v>45328</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>45328</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         <v>44809</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>45646</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>45107</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>45562</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>44991</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>44853</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>45293</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>44497</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>45329</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15740,7 +15740,7 @@
         <v>45723</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
         <v>45884</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>44847</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>45281</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>45097</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>45352</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>45281</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>45489</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>44855</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45462</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>45629</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45323</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>45578</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>45578</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>45273</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>44951</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>44952</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>45531</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>45265</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>45888</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>45512</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>45281</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>44867</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17444,7 +17444,7 @@
         <v>45887</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>45761</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>45511</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         <v>45887</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>45243</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17814,7 +17814,7 @@
         <v>44881</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>44865</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>45890</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>45729</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>45890</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>45476</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>45409</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>44937</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>45531</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
         <v>45891</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>45897</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>45376</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45901</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>44498</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>45730</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>44853</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>44819</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>45278</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19163,7 +19163,7 @@
         <v>45729</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>45502</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>45293</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>45803</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>45562</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>44531</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>45685</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>45776</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>45776</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19820,7 +19820,7 @@
         <v>44791</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45782</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19971,7 +19971,7 @@
         <v>45782</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>45418</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20122,7 +20122,7 @@
         <v>44502</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>45126</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>45915</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
         <v>45228</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20419,7 +20419,7 @@
         <v>45161</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20497,7 +20497,7 @@
         <v>45562</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20570,7 +20570,7 @@
         <v>45209</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>45915</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         <v>45390</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20799,7 +20799,7 @@
         <v>45148</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>44897</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20945,7 +20945,7 @@
         <v>45917</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21018,7 +21018,7 @@
         <v>45558</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21091,7 +21091,7 @@
         <v>45173</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>45342</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>44496</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>45405</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21388,7 +21388,7 @@
         <v>45919</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>45922</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>45578</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         <v>45922</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>44881</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>45923</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>45924</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
         <v>45924</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>45924</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22060,7 +22060,7 @@
         <v>45924</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22133,7 +22133,7 @@
         <v>45924</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22206,7 +22206,7 @@
         <v>45409</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>45334</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22352,7 +22352,7 @@
         <v>44894</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
         <v>45791</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>45342</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22571,7 +22571,7 @@
         <v>44609</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>45628</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22722,7 +22722,7 @@
         <v>45574</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>45576</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>45433</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>45351</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>45320</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>44571</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>44641</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>45168</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23311,7 +23311,7 @@
         <v>45579</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>45512</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>45639</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>45793</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>45266</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>45516</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>45139</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>45147</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>45919</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>45799</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>45701</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24134,7 +24134,7 @@
         <v>45936</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24207,7 +24207,7 @@
         <v>45595</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>45595</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24353,7 +24353,7 @@
         <v>45800</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>45616</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>45757</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>45936</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>45936</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>45390</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>45505</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>45803</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         <v>44676</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>45762</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>44755</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>45805</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>45630</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>44694</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>44747</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>45937</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>45205</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>45939</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25697,7 +25697,7 @@
         <v>45617</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>45811</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>45762</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>45812</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25989,7 +25989,7 @@
         <v>45812</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26062,7 +26062,7 @@
         <v>44617</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>45428</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26208,7 +26208,7 @@
         <v>45163</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>45622</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26354,7 +26354,7 @@
         <v>45152</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>44732</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>44858</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>45293</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26646,7 +26646,7 @@
         <v>44890</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>45015</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26802,7 +26802,7 @@
         <v>45314</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26875,7 +26875,7 @@
         <v>45824</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>45163</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>45825</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>45825</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>45825</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>45825</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27318,7 +27318,7 @@
         <v>44706</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>45826</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>44728</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>45959</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>45959</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>44971</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27766,7 +27766,7 @@
         <v>45833</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>45833</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27922,7 +27922,7 @@
         <v>45834</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27995,7 +27995,7 @@
         <v>45833</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28073,7 +28073,7 @@
         <v>45638</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>45833</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>45833</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>45834</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>45181</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>45837</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>44728</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>45189</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>45811</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28745,7 +28745,7 @@
         <v>45837</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28823,7 +28823,7 @@
         <v>45699</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28896,7 +28896,7 @@
         <v>45840</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>44743</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>45840</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29115,7 +29115,7 @@
         <v>45168</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29188,7 +29188,7 @@
         <v>44847</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29266,7 +29266,7 @@
         <v>45793</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29344,7 +29344,7 @@
         <v>44726</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29417,7 +29417,7 @@
         <v>45667</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>45723</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29563,7 +29563,7 @@
         <v>45848</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29636,7 +29636,7 @@
         <v>45972</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>45848</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29787,7 +29787,7 @@
         <v>45972</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29865,7 +29865,7 @@
         <v>45166</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29943,7 +29943,7 @@
         <v>45749</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>45645</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30089,7 +30089,7 @@
         <v>45975</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30167,7 +30167,7 @@
         <v>45853</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>45251</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>45168</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>44853</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30464,7 +30464,7 @@
         <v>45350</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>45793</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30615,7 +30615,7 @@
         <v>45293</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30688,7 +30688,7 @@
         <v>45729</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>45741</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>45138</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>45978</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>45320</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>44973</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31131,7 +31131,7 @@
         <v>45231</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>45574</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31277,7 +31277,7 @@
         <v>44747</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31350,7 +31350,7 @@
         <v>45741</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31423,7 +31423,7 @@
         <v>45072</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31496,7 +31496,7 @@
         <v>45975</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>45979</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31652,7 +31652,7 @@
         <v>45313</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>45366</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>45979</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>45545</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>45979</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32022,7 +32022,7 @@
         <v>45874</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>44980</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>44853</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>45874</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>45979</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32387,7 +32387,7 @@
         <v>45979</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>45678</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>45874</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>45874</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32689,7 +32689,7 @@
         <v>45979</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32767,7 +32767,7 @@
         <v>45764</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32845,7 +32845,7 @@
         <v>45979</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32918,7 +32918,7 @@
         <v>44971</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32996,7 +32996,7 @@
         <v>45981</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>44936</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>45880</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>45749</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>45757</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>45981</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>44792</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33517,7 +33517,7 @@
         <v>45769</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33595,7 +33595,7 @@
         <v>45733</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>45496</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>45352</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33819,7 +33819,7 @@
         <v>46094</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>46094</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>45685</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>45091</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34116,7 +34116,7 @@
         <v>45280</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>46101</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34267,7 +34267,7 @@
         <v>45749</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34340,7 +34340,7 @@
         <v>46104</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>45462</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34486,7 +34486,7 @@
         <v>45749</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34559,7 +34559,7 @@
         <v>46105</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34632,7 +34632,7 @@
         <v>46105</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34705,7 +34705,7 @@
         <v>46105</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>44603</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>46105</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>46107</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34997,7 +34997,7 @@
         <v>44875</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>45482</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>45044</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35226,7 +35226,7 @@
         <v>46107</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35299,7 +35299,7 @@
         <v>46107</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35372,7 +35372,7 @@
         <v>46106</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>45203</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>45106</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>45987</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>45714</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>46113</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35820,7 +35820,7 @@
         <v>45496</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>44957</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35966,7 +35966,7 @@
         <v>45992</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36039,7 +36039,7 @@
         <v>44903</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36117,7 +36117,7 @@
         <v>46120</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>44945</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>46122</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36341,7 +36341,7 @@
         <v>46127</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36414,7 +36414,7 @@
         <v>45126</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36487,7 +36487,7 @@
         <v>45999</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>45999</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36633,7 +36633,7 @@
         <v>45999</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36706,7 +36706,7 @@
         <v>46000</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>45376</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36852,7 +36852,7 @@
         <v>46132</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36925,7 +36925,7 @@
         <v>46133</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>46133</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>44889</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37149,7 +37149,7 @@
         <v>45289</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>44845</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>45072</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45194</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37446,7 +37446,7 @@
         <v>45289</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>44580</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37592,7 +37592,7 @@
         <v>45476</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37665,7 +37665,7 @@
         <v>45904</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37738,7 +37738,7 @@
         <v>46013</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>45006</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>46024</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>46024</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38030,7 +38030,7 @@
         <v>46023</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>46024</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38176,7 +38176,7 @@
         <v>46023</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38249,7 +38249,7 @@
         <v>46024</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38322,7 +38322,7 @@
         <v>45300</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>46026</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38468,7 +38468,7 @@
         <v>45035</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>44987</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>46029</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>46029</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38765,7 +38765,7 @@
         <v>46029</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38838,7 +38838,7 @@
         <v>45526</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>46030</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38984,7 +38984,7 @@
         <v>46029</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>46030</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39130,7 +39130,7 @@
         <v>46065</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39208,7 +39208,7 @@
         <v>44869</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39281,7 +39281,7 @@
         <v>46034</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39354,7 +39354,7 @@
         <v>45392</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39427,7 +39427,7 @@
         <v>46035</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39500,7 +39500,7 @@
         <v>46038</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39573,7 +39573,7 @@
         <v>46038</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39646,7 +39646,7 @@
         <v>46042</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>45000</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>45000</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>45250</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39948,7 +39948,7 @@
         <v>45771</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40021,7 +40021,7 @@
         <v>45044</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40099,7 +40099,7 @@
         <v>45126</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40172,7 +40172,7 @@
         <v>45825</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40245,7 +40245,7 @@
         <v>45523</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40318,7 +40318,7 @@
         <v>46045</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40391,7 +40391,7 @@
         <v>45840</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40464,7 +40464,7 @@
         <v>45887</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>46052</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40610,7 +40610,7 @@
         <v>46052</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40683,7 +40683,7 @@
         <v>46052</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40761,7 +40761,7 @@
         <v>46055</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40834,7 +40834,7 @@
         <v>46056</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40907,7 +40907,7 @@
         <v>46072</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>46024</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41053,7 +41053,7 @@
         <v>46142</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>46142</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>46063</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41272,7 +41272,7 @@
         <v>46065</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41350,7 +41350,7 @@
         <v>46065</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41428,7 +41428,7 @@
         <v>46065</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>46065</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>46065</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>46070</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41725,7 +41725,7 @@
         <v>46150</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41798,7 +41798,7 @@
         <v>46069</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>46072</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41944,7 +41944,7 @@
         <v>46071</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42017,7 +42017,7 @@
         <v>46071</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42090,7 +42090,7 @@
         <v>46072</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42163,7 +42163,7 @@
         <v>46107</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42236,7 +42236,7 @@
         <v>46153</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>46077</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42382,7 +42382,7 @@
         <v>46153</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42455,7 +42455,7 @@
         <v>46080</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42528,7 +42528,7 @@
         <v>46085</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42601,7 +42601,7 @@
         <v>46064</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42674,7 +42674,7 @@
         <v>46155</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>45930</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42820,7 +42820,7 @@
         <v>46087</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42898,7 +42898,7 @@
         <v>46091</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42971,7 +42971,7 @@
         <v>46160</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43044,7 +43044,7 @@
         <v>46091</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>46091</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>46091</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43263,7 +43263,7 @@
         <v>46091</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>46161</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43409,7 +43409,7 @@
         <v>45832</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>46161</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43555,7 +43555,7 @@
         <v>46161</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43628,7 +43628,7 @@
         <v>46161</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43701,7 +43701,7 @@
         <v>46161</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>46162</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43847,7 +43847,7 @@
         <v>46161</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45786</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>45813</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>46162</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>45790</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44222,7 +44222,7 @@
         <v>46161</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44295,7 +44295,7 @@
         <v>46161</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44368,7 +44368,7 @@
         <v>46168</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44441,7 +44441,7 @@
         <v>45985</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>46167</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44587,7 +44587,7 @@
         <v>45638</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>46167</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>46149</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44806,7 +44806,7 @@
         <v>46165</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>46170</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>45910</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45025,7 +45025,7 @@
         <v>46170</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>46175</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>46175</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>46094</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>46175</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45390,7 +45390,7 @@
         <v>46174</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45463,7 +45463,7 @@
         <v>46177</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>46177</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45609,7 +45609,7 @@
         <v>46177</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45682,7 +45682,7 @@
         <v>46177</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45755,7 +45755,7 @@
         <v>46177</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>46178</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>46181</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>46178</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>46182</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46120,7 +46120,7 @@
         <v>46184</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>46189</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>45800</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46339,7 +46339,7 @@
         <v>46188</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>46189</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>46189</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         <v>46189</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46631,7 +46631,7 @@
         <v>46189</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>46191</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46782,7 +46782,7 @@
         <v>46190</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46855,7 +46855,7 @@
         <v>46195</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>46195</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47001,7 +47001,7 @@
         <v>46195</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47074,7 +47074,7 @@
         <v>46195</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47147,7 +47147,7 @@
         <v>46195</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47220,7 +47220,7 @@
         <v>46195</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47293,7 +47293,7 @@
         <v>46203</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47371,7 +47371,7 @@
         <v>46204</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47444,7 +47444,7 @@
         <v>46204</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47517,7 +47517,7 @@
         <v>46205</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47590,7 +47590,7 @@
         <v>46204</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47663,7 +47663,7 @@
         <v>46204</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47736,7 +47736,7 @@
         <v>46205</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47809,7 +47809,7 @@
         <v>46205</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47882,7 +47882,7 @@
         <v>45800</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47955,7 +47955,7 @@
         <v>46206</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48028,7 +48028,7 @@
         <v>46206</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48101,7 +48101,7 @@
         <v>46206</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>46206</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>46209</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>46211</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>46211</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48466,7 +48466,7 @@
         <v>46213</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48539,7 +48539,7 @@
         <v>45348</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>46213</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48685,7 +48685,7 @@
         <v>46215</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48758,7 +48758,7 @@
         <v>46215</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48831,7 +48831,7 @@
         <v>46219</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48904,7 +48904,7 @@
         <v>46219</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48977,7 +48977,7 @@
         <v>46219</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>46265</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49128,7 +49128,7 @@
         <v>46161</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49201,7 +49201,7 @@
         <v>46203</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49274,7 +49274,7 @@
         <v>46213</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49347,7 +49347,7 @@
         <v>46274</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49420,7 +49420,7 @@
         <v>46232</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49493,7 +49493,7 @@
         <v>46275</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         <v>46237</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49644,7 +49644,7 @@
         <v>46282</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>46281</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>46239</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49868,7 +49868,7 @@
         <v>46281</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49941,7 +49941,7 @@
         <v>46286</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50019,7 +50019,7 @@
         <v>46181</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50092,7 +50092,7 @@
         <v>46286</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50170,7 +50170,7 @@
         <v>46070</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50243,7 +50243,7 @@
         <v>46288</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50316,7 +50316,7 @@
         <v>46286</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50389,7 +50389,7 @@
         <v>46288</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50462,7 +50462,7 @@
         <v>46244</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50540,7 +50540,7 @@
         <v>46287</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50618,7 +50618,7 @@
         <v>46189</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50691,7 +50691,7 @@
         <v>46288</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50764,7 +50764,7 @@
         <v>46248</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50837,7 +50837,7 @@
         <v>46296</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50915,7 +50915,7 @@
         <v>46252</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>46296</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51066,7 +51066,7 @@
         <v>46296</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51144,7 +51144,7 @@
         <v>46296</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51222,7 +51222,7 @@
         <v>46297</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51300,7 +51300,7 @@
         <v>46251</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51378,7 +51378,7 @@
         <v>46297</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51451,7 +51451,7 @@
         <v>46288</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51524,7 +51524,7 @@
         <v>46301</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51597,7 +51597,7 @@
         <v>46258</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51670,7 +51670,7 @@
         <v>46303</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51748,7 +51748,7 @@
         <v>46262</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51821,7 +51821,7 @@
         <v>46260</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51894,7 +51894,7 @@
         <v>46304</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51967,7 +51967,7 @@
         <v>46049</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>44393</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52113,7 +52113,7 @@
         <v>45323</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         <v>45733</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52269,7 +52269,7 @@
         <v>45755</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52342,7 +52342,7 @@
         <v>45793</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52420,7 +52420,7 @@
         <v>46078</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52498,7 +52498,7 @@
         <v>46073</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52571,7 +52571,7 @@
         <v>46093</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52649,7 +52649,7 @@
         <v>46156</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52722,7 +52722,7 @@
         <v>46267</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>

--- a/Översikt HÄRNÖSAND.xlsx
+++ b/Översikt HÄRNÖSAND.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45328</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>46288</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,24 +970,24 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S 174-2026</t>
+          <t>A 5881-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46044</v>
+        <v>45335</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -999,25 +999,20 @@
           <t>HÄRNÖSAND</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I5" t="n">
-        <v>5.4</v>
+        <v>22.9</v>
       </c>
       <c r="J5" t="n">
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
         <v>9</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1029,21 +1024,156 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
         <v>18</v>
       </c>
       <c r="T5" t="n">
+        <v>60</v>
+      </c>
+      <c r="U5" t="n">
+        <v>46</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Knärot
+Ringlav
+Dropptaggsvamp
+Gammelgransskål
+Motaggsvamp
+Rosenticka
+Tallkötticka
+Talltita
+Tretåig hackspett
+Ullticka
+Violettgrå tagellav
+Nästlav
+Rävticka
+Vedticka
+Linnea
+Spillkråka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 5881-2024 artfynd.xlsx", "A 5881-2024")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 5881-2024 karta.png", "A 5881-2024")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 5881-2024 georefererad karta.tif", "A 5881-2024")</f>
+        <v/>
+      </c>
+      <c r="Z5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/knärot/A 5881-2024 karta knärot.png", "A 5881-2024")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 5881-2024 FSC-klagomål.docx", "A 5881-2024")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 5881-2024 FSC-klagomål mail.docx", "A 5881-2024")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 5881-2024 tillsynsbegäran.docx", "A 5881-2024")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 5881-2024 tillsynsbegäran mail.docx", "A 5881-2024")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/fåglar/A 5881-2024 prioriterade fågelarter.docx", "A 5881-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S 174-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>46044</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HÄRNÖSAND</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>10</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>18</v>
+      </c>
+      <c r="T6" t="n">
         <v>34</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Blågrå svartspik
@@ -1065,116 +1195,244 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/S 174-2026 artfynd.xlsx", "S 174-2026")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/S 174-2026 karta.png", "S 174-2026")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/S 174-2026 georefererad karta.tif", "S 174-2026")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/S 174-2026 FSC-klagomål.docx", "S 174-2026")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/S 174-2026 FSC-klagomål mail.docx", "S 174-2026")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/S 174-2026 tillsynsbegäran.docx", "S 174-2026")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/S 174-2026 tillsynsbegäran mail.docx", "S 174-2026")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/fåglar/S 174-2026 prioriterade fågelarter.docx", "S 174-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 47711-2024</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45588</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HÄRNÖSAND</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>9</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>11</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>16</v>
+      </c>
+      <c r="T7" t="n">
+        <v>57</v>
+      </c>
+      <c r="U7" t="n">
+        <v>43</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Ringlav
+Dropptaggsvamp
+Motaggsvamp
+Orange taggsvamp
+Rosenticka
+Svartvit taggsvamp
+Tallticka
+Tretåig hackspett
+Ullticka
+Violettgrå tagellav
+Bronshjon
+Nästlav
+Vedticka
+Kötticka
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 47711-2024 artfynd.xlsx", "A 47711-2024")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 47711-2024 karta.png", "A 47711-2024")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 47711-2024 georefererad karta.tif", "A 47711-2024")</f>
+        <v/>
+      </c>
+      <c r="Z7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/knärot/A 47711-2024 karta knärot.png", "A 47711-2024")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 47711-2024 FSC-klagomål.docx", "A 47711-2024")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 47711-2024 FSC-klagomål mail.docx", "A 47711-2024")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 47711-2024 tillsynsbegäran.docx", "A 47711-2024")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 47711-2024 tillsynsbegäran mail.docx", "A 47711-2024")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/fåglar/A 47711-2024 prioriterade fågelarter.docx", "A 47711-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>A 18689-2025</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
         <v>45763</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTERNORRLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>HÄRNÖSAND</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="E8" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HÄRNÖSAND</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I8" t="n">
         <v>12.2</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J8" t="n">
         <v>5</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K8" t="n">
         <v>5</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L8" t="n">
         <v>5</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M8" t="n">
         <v>3</v>
       </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>8</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S8" t="n">
         <v>15</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T8" t="n">
         <v>28</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U8" t="n">
         <v>20</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -1193,247 +1451,120 @@
 Nattviol</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 18689-2025 artfynd.xlsx", "A 18689-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 18689-2025 karta.png", "A 18689-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 18689-2025 georefererad karta.tif", "A 18689-2025")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/knärot/A 18689-2025 karta knärot.png", "A 18689-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 18689-2025 FSC-klagomål.docx", "A 18689-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 18689-2025 FSC-klagomål mail.docx", "A 18689-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 18689-2025 tillsynsbegäran.docx", "A 18689-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 18689-2025 tillsynsbegäran mail.docx", "A 18689-2025")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/fåglar/A 18689-2025 prioriterade fågelarter.docx", "A 18689-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 47711-2024</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45588</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTERNORRLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HÄRNÖSAND</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" t="n">
-        <v>9</v>
-      </c>
-      <c r="M7" t="n">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 18563-2022</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>44686</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HÄRNÖSAND</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>10</v>
-      </c>
-      <c r="R7" t="n">
+      <c r="K9" t="n">
+        <v>7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M9" t="n">
         <v>1</v>
       </c>
-      <c r="S7" t="n">
-        <v>15</v>
-      </c>
-      <c r="T7" t="n">
-        <v>49</v>
-      </c>
-      <c r="U7" t="n">
-        <v>35</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Dropptaggsvamp
-Motaggsvamp
-Orange taggsvamp
-Rosenticka
-Svartvit taggsvamp
-Tallticka
-Tretåig hackspett
-Ullticka
-Violettgrå tagellav
-Bronshjon
-Nästlav
-Vedticka
-Kötticka
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 47711-2024 artfynd.xlsx", "A 47711-2024")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 47711-2024 karta.png", "A 47711-2024")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 47711-2024 georefererad karta.tif", "A 47711-2024")</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/knärot/A 47711-2024 karta knärot.png", "A 47711-2024")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 47711-2024 FSC-klagomål.docx", "A 47711-2024")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 47711-2024 FSC-klagomål mail.docx", "A 47711-2024")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 47711-2024 tillsynsbegäran.docx", "A 47711-2024")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 47711-2024 tillsynsbegäran mail.docx", "A 47711-2024")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/fåglar/A 47711-2024 prioriterade fågelarter.docx", "A 47711-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 18563-2022</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44686</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTERNORRLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HÄRNÖSAND</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="J8" t="n">
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>7</v>
+      </c>
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>7</v>
-      </c>
-      <c r="L8" t="n">
-        <v>6</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>7</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="S9" t="n">
         <v>14</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>73</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>4</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Lunglav
@@ -1451,112 +1582,112 @@
 Vedticka</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 18563-2022 artfynd.xlsx", "A 18563-2022")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 18563-2022 karta.png", "A 18563-2022")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 18563-2022 georefererad karta.tif", "A 18563-2022")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 18563-2022 FSC-klagomål.docx", "A 18563-2022")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 18563-2022 FSC-klagomål mail.docx", "A 18563-2022")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 18563-2022 tillsynsbegäran.docx", "A 18563-2022")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 18563-2022 tillsynsbegäran mail.docx", "A 18563-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 27496-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>46189</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTERNORRLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>HÄRNÖSAND</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="E10" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÄRNÖSAND</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="I10" t="n">
         <v>4.2</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J10" t="n">
         <v>3</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K10" t="n">
         <v>4</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L10" t="n">
         <v>5</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M10" t="n">
         <v>2</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>7</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S10" t="n">
         <v>14</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>17</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Aspfjädermossa
 Lappticka
@@ -1574,116 +1705,116 @@
 Utter</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 27496-2026 artfynd.xlsx", "A 27496-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 27496-2026 karta.png", "A 27496-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 27496-2026 georefererad karta.tif", "A 27496-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 27496-2026 FSC-klagomål.docx", "A 27496-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 27496-2026 FSC-klagomål mail.docx", "A 27496-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 27496-2026 tillsynsbegäran.docx", "A 27496-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 27496-2026 tillsynsbegäran mail.docx", "A 27496-2026")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/fåglar/A 27496-2026 prioriterade fågelarter.docx", "A 27496-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 49355-2025</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>45938</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTERNORRLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÄRNÖSAND</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="E11" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÄRNÖSAND</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="I11" t="n">
         <v>10.3</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>3</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K11" t="n">
         <v>3</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L11" t="n">
         <v>6</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M11" t="n">
         <v>4</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>10</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R11" t="n">
         <v>4</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S11" t="n">
         <v>14</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>59</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>38</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -1701,120 +1832,120 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 49355-2025 artfynd.xlsx", "A 49355-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 49355-2025 karta.png", "A 49355-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 49355-2025 georefererad karta.tif", "A 49355-2025")</f>
         <v/>
       </c>
-      <c r="Z10">
+      <c r="Z11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/knärot/A 49355-2025 karta knärot.png", "A 49355-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 49355-2025 FSC-klagomål.docx", "A 49355-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 49355-2025 FSC-klagomål mail.docx", "A 49355-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 49355-2025 tillsynsbegäran.docx", "A 49355-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 49355-2025 tillsynsbegäran mail.docx", "A 49355-2025")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/fåglar/A 49355-2025 prioriterade fågelarter.docx", "A 49355-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 38409-2024</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D12" s="1" t="n">
         <v>45546</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTERNORRLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÄRNÖSAND</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="E12" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HÄRNÖSAND</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I12" t="n">
         <v>7.7</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" t="n">
         <v>3</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K12" t="n">
         <v>2</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L12" t="n">
         <v>7</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M12" t="n">
         <v>3</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>10</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>3</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S12" t="n">
         <v>12</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T12" t="n">
         <v>40</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>40</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -1830,120 +1961,120 @@
 Mörk husmossa</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 38409-2024 artfynd.xlsx", "A 38409-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 38409-2024 karta.png", "A 38409-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 38409-2024 georefererad karta.tif", "A 38409-2024")</f>
         <v/>
       </c>
-      <c r="Z11">
+      <c r="Z12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/knärot/A 38409-2024 karta knärot.png", "A 38409-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 38409-2024 FSC-klagomål.docx", "A 38409-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 38409-2024 FSC-klagomål mail.docx", "A 38409-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 38409-2024 tillsynsbegäran.docx", "A 38409-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 38409-2024 tillsynsbegäran mail.docx", "A 38409-2024")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/fåglar/A 38409-2024 prioriterade fågelarter.docx", "A 38409-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 14582-2024</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>45394</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTERNORRLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HÄRNÖSAND</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="E13" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HÄRNÖSAND</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I13" t="n">
         <v>4.1</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>10</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M13" t="n">
         <v>1</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>11</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R13" t="n">
         <v>1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S13" t="n">
         <v>11</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T13" t="n">
         <v>19</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U13" t="n">
         <v>18</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Dvärgbägarlav
@@ -1958,116 +2089,116 @@
 Vedskivlav</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 14582-2024 artfynd.xlsx", "A 14582-2024")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 14582-2024 karta.png", "A 14582-2024")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 14582-2024 georefererad karta.tif", "A 14582-2024")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 14582-2024 FSC-klagomål.docx", "A 14582-2024")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 14582-2024 FSC-klagomål mail.docx", "A 14582-2024")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 14582-2024 tillsynsbegäran.docx", "A 14582-2024")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 14582-2024 tillsynsbegäran mail.docx", "A 14582-2024")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/fåglar/A 14582-2024 prioriterade fågelarter.docx", "A 14582-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 47485-2025</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTERNORRLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HÄRNÖSAND</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="E14" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HÄRNÖSAND</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I14" t="n">
         <v>10.6</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J14" t="n">
         <v>2</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K14" t="n">
         <v>2</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>7</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R14" t="n">
         <v>1</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S14" t="n">
         <v>10</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>15</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Lunglav
@@ -2081,120 +2212,120 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 47485-2025 artfynd.xlsx", "A 47485-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 47485-2025 karta.png", "A 47485-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 47485-2025 georefererad karta.tif", "A 47485-2025")</f>
         <v/>
       </c>
-      <c r="Z13">
+      <c r="Z14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/knärot/A 47485-2025 karta knärot.png", "A 47485-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 47485-2025 FSC-klagomål.docx", "A 47485-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 47485-2025 FSC-klagomål mail.docx", "A 47485-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 47485-2025 tillsynsbegäran.docx", "A 47485-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 47485-2025 tillsynsbegäran mail.docx", "A 47485-2025")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/fåglar/A 47485-2025 prioriterade fågelarter.docx", "A 47485-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 18695-2025</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
         <v>45763</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTERNORRLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HÄRNÖSAND</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="E15" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>HÄRNÖSAND</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I15" t="n">
         <v>2.2</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>5</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M15" t="n">
         <v>1</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>5</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R15" t="n">
         <v>1</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S15" t="n">
         <v>10</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T15" t="n">
         <v>10</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Rynkskinn
@@ -2208,112 +2339,112 @@
 Vedticka</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 18695-2025 artfynd.xlsx", "A 18695-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 18695-2025 karta.png", "A 18695-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 18695-2025 georefererad karta.tif", "A 18695-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 18695-2025 FSC-klagomål.docx", "A 18695-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 18695-2025 FSC-klagomål mail.docx", "A 18695-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 18695-2025 tillsynsbegäran.docx", "A 18695-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 18695-2025 tillsynsbegäran mail.docx", "A 18695-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 29686-2024</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="D16" s="1" t="n">
         <v>45484</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTERNORRLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>HÄRNÖSAND</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="E16" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>HÄRNÖSAND</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="I16" t="n">
         <v>12.8</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K16" t="n">
         <v>3</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L16" t="n">
         <v>4</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>5</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R16" t="n">
         <v>1</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S16" t="n">
         <v>9</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T16" t="n">
         <v>17</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>2</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Doftskinn
@@ -2326,111 +2457,111 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 29686-2024 artfynd.xlsx", "A 29686-2024")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 29686-2024 karta.png", "A 29686-2024")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 29686-2024 georefererad karta.tif", "A 29686-2024")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 29686-2024 FSC-klagomål.docx", "A 29686-2024")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 29686-2024 FSC-klagomål mail.docx", "A 29686-2024")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 29686-2024 tillsynsbegäran.docx", "A 29686-2024")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 29686-2024 tillsynsbegäran mail.docx", "A 29686-2024")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/fåglar/A 29686-2024 prioriterade fågelarter.docx", "A 29686-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 34711-2023</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>45139</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTERNORRLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>HÄRNÖSAND</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HÄRNÖSAND</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>11.6</v>
       </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>4</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L17" t="n">
         <v>3</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M17" t="n">
         <v>2</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>5</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R17" t="n">
         <v>2</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S17" t="n">
         <v>9</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>18</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>1</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Aspfjädermossa
 Aspgelélav
@@ -2443,112 +2574,112 @@
 Vedticka</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 34711-2023 artfynd.xlsx", "A 34711-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 34711-2023 karta.png", "A 34711-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 34711-2023 georefererad karta.tif", "A 34711-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 34711-2023 FSC-klagomål.docx", "A 34711-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 34711-2023 FSC-klagomål mail.docx", "A 34711-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 34711-2023 tillsynsbegäran.docx", "A 34711-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 34711-2023 tillsynsbegäran mail.docx", "A 34711-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 26084-2025</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>45805</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTERNORRLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>HÄRNÖSAND</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="E18" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>HÄRNÖSAND</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I18" t="n">
         <v>3.5</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K18" t="n">
         <v>2</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L18" t="n">
         <v>5</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M18" t="n">
         <v>1</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>6</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R18" t="n">
         <v>1</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S18" t="n">
         <v>9</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>16</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>14</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gammelgransskål
@@ -2561,152 +2692,36 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 26084-2025 artfynd.xlsx", "A 26084-2025")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 26084-2025 karta.png", "A 26084-2025")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 26084-2025 georefererad karta.tif", "A 26084-2025")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 26084-2025 FSC-klagomål.docx", "A 26084-2025")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 26084-2025 FSC-klagomål mail.docx", "A 26084-2025")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 26084-2025 tillsynsbegäran.docx", "A 26084-2025")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 26084-2025 tillsynsbegäran mail.docx", "A 26084-2025")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/fåglar/A 26084-2025 prioriterade fågelarter.docx", "A 26084-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 5881-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45335</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTERNORRLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>HÄRNÖSAND</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>6</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>8</v>
-      </c>
-      <c r="T18" t="n">
-        <v>22</v>
-      </c>
-      <c r="U18" t="n">
-        <v>8</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Motaggsvamp
-Rosenticka
-Talltita
-Ullticka
-Violettgrå tagellav
-Vedticka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 5881-2024 artfynd.xlsx", "A 5881-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 5881-2024 karta.png", "A 5881-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 5881-2024 georefererad karta.tif", "A 5881-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 5881-2024 FSC-klagomål.docx", "A 5881-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 5881-2024 FSC-klagomål mail.docx", "A 5881-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 5881-2024 tillsynsbegäran.docx", "A 5881-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 5881-2024 tillsynsbegäran mail.docx", "A 5881-2024")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/fåglar/A 5881-2024 prioriterade fågelarter.docx", "A 5881-2024")</f>
         <v/>
       </c>
     </row>
@@ -2730,7 +2745,7 @@
         <v>45826</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2842,7 +2857,7 @@
         <v>45616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2959,7 +2974,7 @@
         <v>45082</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3075,7 +3090,7 @@
         <v>45027</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3190,7 +3205,7 @@
         <v>44874</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3305,7 +3320,7 @@
         <v>46183</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3415,7 +3430,7 @@
         <v>45352</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3533,7 +3548,7 @@
         <v>45957</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3647,7 +3662,7 @@
         <v>45188</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3765,7 +3780,7 @@
         <v>45593</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3879,7 +3894,7 @@
         <v>45593</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3993,7 +4008,7 @@
         <v>45548</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4102,7 +4117,7 @@
         <v>45567</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4216,7 +4231,7 @@
         <v>44979</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4334,7 +4349,7 @@
         <v>45477</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4442,7 +4457,7 @@
         <v>45314</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4555,7 +4570,7 @@
         <v>45971</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4668,7 +4683,7 @@
         <v>46176</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4781,7 +4796,7 @@
         <v>45513</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4894,7 +4909,7 @@
         <v>45560</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5007,7 +5022,7 @@
         <v>46251</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5120,7 +5135,7 @@
         <v>45848</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5233,7 +5248,7 @@
         <v>45323</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5350,7 +5365,7 @@
         <v>45790</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5463,7 +5478,7 @@
         <v>44686</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5579,7 +5594,7 @@
         <v>45355</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5686,7 +5701,7 @@
         <v>44755</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5793,7 +5808,7 @@
         <v>45617</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5905,7 +5920,7 @@
         <v>45526</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6017,7 +6032,7 @@
         <v>45930</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6129,7 +6144,7 @@
         <v>46003</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6245,7 +6260,7 @@
         <v>45182</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6357,7 +6372,7 @@
         <v>45596</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6469,7 +6484,7 @@
         <v>46244</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6585,7 +6600,7 @@
         <v>45322</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6692,7 +6707,7 @@
         <v>44664</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6798,7 +6813,7 @@
         <v>45618</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6909,7 +6924,7 @@
         <v>45376</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7020,7 +7035,7 @@
         <v>45575</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7126,7 +7141,7 @@
         <v>45930</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7241,7 +7256,7 @@
         <v>45910</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7352,7 +7367,7 @@
         <v>46141</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7458,7 +7473,7 @@
         <v>45967</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7569,7 +7584,7 @@
         <v>44874</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7680,7 +7695,7 @@
         <v>45513</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7791,7 +7806,7 @@
         <v>45267</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7902,7 +7917,7 @@
         <v>46244</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8013,7 +8028,7 @@
         <v>46303</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8128,7 +8143,7 @@
         <v>45847</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8243,7 +8258,7 @@
         <v>45996</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8354,7 +8369,7 @@
         <v>44676</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8459,7 +8474,7 @@
         <v>44585</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8564,7 +8579,7 @@
         <v>44655</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8669,7 +8684,7 @@
         <v>45554</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8774,7 +8789,7 @@
         <v>45456</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8884,7 +8899,7 @@
         <v>45008</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8989,7 +9004,7 @@
         <v>45583</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9098,7 +9113,7 @@
         <v>45350</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9208,7 +9223,7 @@
         <v>45649</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9313,7 +9328,7 @@
         <v>45919</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9423,7 +9438,7 @@
         <v>45352</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9533,7 +9548,7 @@
         <v>46031</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9642,7 +9657,7 @@
         <v>46176</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9752,7 +9767,7 @@
         <v>45276</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9857,7 +9872,7 @@
         <v>46189</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9962,7 +9977,7 @@
         <v>46184</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10071,7 +10086,7 @@
         <v>46127</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10176,7 +10191,7 @@
         <v>44559</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10281,7 +10296,7 @@
         <v>46213</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10390,7 +10405,7 @@
         <v>45372</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10500,7 +10515,7 @@
         <v>44837</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10605,7 +10620,7 @@
         <v>45428</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10715,7 +10730,7 @@
         <v>46191</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10825,7 +10840,7 @@
         <v>45805</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10939,7 +10954,7 @@
         <v>45805</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11044,7 +11059,7 @@
         <v>45811</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11149,7 +11164,7 @@
         <v>44874</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11222,7 +11237,7 @@
         <v>44664</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11295,7 +11310,7 @@
         <v>44806</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11368,7 +11383,7 @@
         <v>44846</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11446,7 +11461,7 @@
         <v>44875</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11519,7 +11534,7 @@
         <v>44532</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11592,7 +11607,7 @@
         <v>44608</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11665,7 +11680,7 @@
         <v>44720</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11738,7 +11753,7 @@
         <v>44600</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11816,7 +11831,7 @@
         <v>44824</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11889,7 +11904,7 @@
         <v>44734</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11962,7 +11977,7 @@
         <v>44487</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12035,7 +12050,7 @@
         <v>44512</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12108,7 +12123,7 @@
         <v>44517</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12186,7 +12201,7 @@
         <v>44728</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12264,7 +12279,7 @@
         <v>44664</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12337,7 +12352,7 @@
         <v>44804</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12410,7 +12425,7 @@
         <v>44512</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12483,7 +12498,7 @@
         <v>44503</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12556,7 +12571,7 @@
         <v>44735</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12629,7 +12644,7 @@
         <v>44581</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12702,7 +12717,7 @@
         <v>44848</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12775,7 +12790,7 @@
         <v>44672</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12848,7 +12863,7 @@
         <v>44652</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12921,7 +12936,7 @@
         <v>44515</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12994,7 +13009,7 @@
         <v>44664</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13067,7 +13082,7 @@
         <v>44616</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13140,7 +13155,7 @@
         <v>44496</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13213,7 +13228,7 @@
         <v>44532</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13286,7 +13301,7 @@
         <v>44571</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13359,7 +13374,7 @@
         <v>44512</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13432,7 +13447,7 @@
         <v>44664</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13505,7 +13520,7 @@
         <v>44536</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13578,7 +13593,7 @@
         <v>44522</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13651,7 +13666,7 @@
         <v>44585</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13724,7 +13739,7 @@
         <v>44792</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13797,7 +13812,7 @@
         <v>45462</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13870,7 +13885,7 @@
         <v>45293</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13943,7 +13958,7 @@
         <v>44747</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14016,7 +14031,7 @@
         <v>44858</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14089,7 +14104,7 @@
         <v>44641</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14162,7 +14177,7 @@
         <v>44881</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14240,7 +14255,7 @@
         <v>45334</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14313,7 +14328,7 @@
         <v>45209</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14391,7 +14406,7 @@
         <v>45667</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14464,7 +14479,7 @@
         <v>44617</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14537,7 +14552,7 @@
         <v>45576</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14615,7 +14630,7 @@
         <v>45281</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14688,7 +14703,7 @@
         <v>45405</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14761,7 +14776,7 @@
         <v>45314</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14834,7 +14849,7 @@
         <v>45762</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14907,7 +14922,7 @@
         <v>45496</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14980,7 +14995,7 @@
         <v>45231</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15053,7 +15068,7 @@
         <v>45352</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15131,7 +15146,7 @@
         <v>44809</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15204,7 +15219,7 @@
         <v>45757</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15277,7 +15292,7 @@
         <v>44853</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15350,7 +15365,7 @@
         <v>45126</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15423,7 +15438,7 @@
         <v>45558</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15496,7 +15511,7 @@
         <v>45228</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15569,7 +15584,7 @@
         <v>45350</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15647,7 +15662,7 @@
         <v>45300</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15720,7 +15735,7 @@
         <v>45628</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15793,7 +15808,7 @@
         <v>45482</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15871,7 +15886,7 @@
         <v>45106</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15949,7 +15964,7 @@
         <v>45531</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16022,7 +16037,7 @@
         <v>44853</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16095,7 +16110,7 @@
         <v>45281</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16168,7 +16183,7 @@
         <v>45289</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16241,7 +16256,7 @@
         <v>45278</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16319,7 +16334,7 @@
         <v>45181</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16392,7 +16407,7 @@
         <v>45289</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16465,7 +16480,7 @@
         <v>45749</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16538,7 +16553,7 @@
         <v>45578</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16611,7 +16626,7 @@
         <v>45578</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16684,7 +16699,7 @@
         <v>44728</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16757,7 +16772,7 @@
         <v>45757</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16830,7 +16845,7 @@
         <v>45496</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16903,7 +16918,7 @@
         <v>45764</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16981,7 +16996,7 @@
         <v>45483</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17054,7 +17069,7 @@
         <v>44603</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17127,7 +17142,7 @@
         <v>45769</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17205,7 +17220,7 @@
         <v>45173</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17283,7 +17298,7 @@
         <v>45168</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17356,7 +17371,7 @@
         <v>45203</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17429,7 +17444,7 @@
         <v>44980</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17502,7 +17517,7 @@
         <v>45097</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17575,7 +17590,7 @@
         <v>45701</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17653,7 +17668,7 @@
         <v>45562</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17726,7 +17741,7 @@
         <v>45729</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17799,7 +17814,7 @@
         <v>45761</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17872,7 +17887,7 @@
         <v>45617</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17945,7 +17960,7 @@
         <v>45352</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18023,7 +18038,7 @@
         <v>45887</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18101,7 +18116,7 @@
         <v>45769</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18179,7 +18194,7 @@
         <v>45730</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18252,7 +18267,7 @@
         <v>45342</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18325,7 +18340,7 @@
         <v>45531</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18398,7 +18413,7 @@
         <v>45887</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18471,7 +18486,7 @@
         <v>45888</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18544,7 +18559,7 @@
         <v>45638</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18617,7 +18632,7 @@
         <v>45884</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18690,7 +18705,7 @@
         <v>45890</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18768,7 +18783,7 @@
         <v>45890</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18846,7 +18861,7 @@
         <v>45293</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18919,7 +18934,7 @@
         <v>45891</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18997,7 +19012,7 @@
         <v>45180</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19070,7 +19085,7 @@
         <v>44853</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19143,7 +19158,7 @@
         <v>45147</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19216,7 +19231,7 @@
         <v>45897</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19289,7 +19304,7 @@
         <v>46065</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19367,7 +19382,7 @@
         <v>45771</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19440,7 +19455,7 @@
         <v>45320</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19513,7 +19528,7 @@
         <v>45904</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19586,7 +19601,7 @@
         <v>46024</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19659,7 +19674,7 @@
         <v>45168</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19732,7 +19747,7 @@
         <v>45293</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19805,7 +19820,7 @@
         <v>45901</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19878,7 +19893,7 @@
         <v>45825</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19951,7 +19966,7 @@
         <v>45526</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20024,7 +20039,7 @@
         <v>45523</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20097,7 +20112,7 @@
         <v>45887</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20170,7 +20185,7 @@
         <v>45840</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20243,7 +20258,7 @@
         <v>45803</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20316,7 +20331,7 @@
         <v>46072</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20389,7 +20404,7 @@
         <v>46142</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20462,7 +20477,7 @@
         <v>45915</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20540,7 +20555,7 @@
         <v>45915</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20618,7 +20633,7 @@
         <v>45168</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20691,7 +20706,7 @@
         <v>45072</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20764,7 +20779,7 @@
         <v>44936</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20837,7 +20852,7 @@
         <v>46142</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20910,7 +20925,7 @@
         <v>45917</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20983,7 +20998,7 @@
         <v>45511</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21056,7 +21071,7 @@
         <v>45749</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21129,7 +21144,7 @@
         <v>45919</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21207,7 +21222,7 @@
         <v>44728</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21280,7 +21295,7 @@
         <v>45923</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21358,7 +21373,7 @@
         <v>45922</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21431,7 +21446,7 @@
         <v>45922</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21504,7 +21519,7 @@
         <v>45924</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21577,7 +21592,7 @@
         <v>44971</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21655,7 +21670,7 @@
         <v>45924</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21728,7 +21743,7 @@
         <v>45924</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21801,7 +21816,7 @@
         <v>45924</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21874,7 +21889,7 @@
         <v>45924</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21947,7 +21962,7 @@
         <v>45489</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22025,7 +22040,7 @@
         <v>44791</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22098,7 +22113,7 @@
         <v>45273</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22171,7 +22186,7 @@
         <v>46150</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22244,7 +22259,7 @@
         <v>46153</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22317,7 +22332,7 @@
         <v>46153</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22390,7 +22405,7 @@
         <v>45919</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22468,7 +22483,7 @@
         <v>45936</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22541,7 +22556,7 @@
         <v>45936</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22614,7 +22629,7 @@
         <v>45126</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22687,7 +22702,7 @@
         <v>45936</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22760,7 +22775,7 @@
         <v>45937</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22838,7 +22853,7 @@
         <v>45685</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22911,7 +22926,7 @@
         <v>44987</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22989,7 +23004,7 @@
         <v>45189</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23062,7 +23077,7 @@
         <v>45939</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23140,7 +23155,7 @@
         <v>45376</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23213,7 +23228,7 @@
         <v>44869</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23286,7 +23301,7 @@
         <v>45006</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23359,7 +23374,7 @@
         <v>45428</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23432,7 +23447,7 @@
         <v>46155</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23505,7 +23520,7 @@
         <v>45562</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23583,7 +23598,7 @@
         <v>45930</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23656,7 +23671,7 @@
         <v>45409</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23729,7 +23744,7 @@
         <v>45645</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23802,7 +23817,7 @@
         <v>46107</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23875,7 +23890,7 @@
         <v>45409</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23948,7 +23963,7 @@
         <v>45959</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24021,7 +24036,7 @@
         <v>45959</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24094,7 +24109,7 @@
         <v>46161</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24167,7 +24182,7 @@
         <v>46161</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24240,7 +24255,7 @@
         <v>46161</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24313,7 +24328,7 @@
         <v>45786</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24391,7 +24406,7 @@
         <v>45790</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24469,7 +24484,7 @@
         <v>46160</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24542,7 +24557,7 @@
         <v>45813</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24615,7 +24630,7 @@
         <v>46161</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24688,7 +24703,7 @@
         <v>46161</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24761,7 +24776,7 @@
         <v>46161</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24834,7 +24849,7 @@
         <v>45793</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24912,7 +24927,7 @@
         <v>46161</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24985,7 +25000,7 @@
         <v>46161</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25058,7 +25073,7 @@
         <v>45147</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25131,7 +25146,7 @@
         <v>45972</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25209,7 +25224,7 @@
         <v>45462</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25282,7 +25297,7 @@
         <v>46162</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25355,7 +25370,7 @@
         <v>45972</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25433,7 +25448,7 @@
         <v>46162</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25506,7 +25521,7 @@
         <v>45832</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25579,7 +25594,7 @@
         <v>45161</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25657,7 +25672,7 @@
         <v>45418</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25730,7 +25745,7 @@
         <v>45091</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25803,7 +25818,7 @@
         <v>45975</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25881,7 +25896,7 @@
         <v>45975</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25959,7 +25974,7 @@
         <v>45978</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26037,7 +26052,7 @@
         <v>44937</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26110,7 +26125,7 @@
         <v>45979</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26188,7 +26203,7 @@
         <v>45979</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26261,7 +26276,7 @@
         <v>45979</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26334,7 +26349,7 @@
         <v>45979</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26407,7 +26422,7 @@
         <v>45979</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26485,7 +26500,7 @@
         <v>45979</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26563,7 +26578,7 @@
         <v>45979</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26641,7 +26656,7 @@
         <v>45981</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26719,7 +26734,7 @@
         <v>45981</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26797,7 +26812,7 @@
         <v>45723</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26870,7 +26885,7 @@
         <v>45733</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26943,7 +26958,7 @@
         <v>45293</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27016,7 +27031,7 @@
         <v>46167</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27089,7 +27104,7 @@
         <v>46167</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27162,7 +27177,7 @@
         <v>45987</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27235,7 +27250,7 @@
         <v>45392</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27308,7 +27323,7 @@
         <v>45044</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27381,7 +27396,7 @@
         <v>44951</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27459,7 +27474,7 @@
         <v>45638</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27532,7 +27547,7 @@
         <v>46149</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27605,7 +27620,7 @@
         <v>45992</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27678,7 +27693,7 @@
         <v>44897</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27751,7 +27766,7 @@
         <v>45044</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27829,7 +27844,7 @@
         <v>45126</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27902,7 +27917,7 @@
         <v>46168</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27975,7 +27990,7 @@
         <v>44732</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28048,7 +28063,7 @@
         <v>45999</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28121,7 +28136,7 @@
         <v>45999</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28194,7 +28209,7 @@
         <v>44596</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28272,7 +28287,7 @@
         <v>45999</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28345,7 +28360,7 @@
         <v>45985</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28418,7 +28433,7 @@
         <v>44706</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28491,7 +28506,7 @@
         <v>45512</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28564,7 +28579,7 @@
         <v>46000</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28637,7 +28652,7 @@
         <v>46170</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28710,7 +28725,7 @@
         <v>46170</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28783,7 +28798,7 @@
         <v>46174</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28856,7 +28871,7 @@
         <v>45646</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28929,7 +28944,7 @@
         <v>46013</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29002,7 +29017,7 @@
         <v>45329</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29075,7 +29090,7 @@
         <v>45910</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29148,7 +29163,7 @@
         <v>46094</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29221,7 +29236,7 @@
         <v>45616</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29299,7 +29314,7 @@
         <v>45320</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29372,7 +29387,7 @@
         <v>46023</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29445,7 +29460,7 @@
         <v>46023</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29518,7 +29533,7 @@
         <v>46024</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29591,7 +29606,7 @@
         <v>46024</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29664,7 +29679,7 @@
         <v>46165</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29737,7 +29752,7 @@
         <v>46024</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29810,7 +29825,7 @@
         <v>46026</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29883,7 +29898,7 @@
         <v>46024</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29956,7 +29971,7 @@
         <v>45035</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30029,7 +30044,7 @@
         <v>46175</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30102,7 +30117,7 @@
         <v>46029</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30175,7 +30190,7 @@
         <v>46029</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30248,7 +30263,7 @@
         <v>46030</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30321,7 +30336,7 @@
         <v>45163</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30394,7 +30409,7 @@
         <v>46029</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30467,7 +30482,7 @@
         <v>46029</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30540,7 +30555,7 @@
         <v>46030</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30613,7 +30628,7 @@
         <v>46034</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30686,7 +30701,7 @@
         <v>44853</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30759,7 +30774,7 @@
         <v>46035</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30832,7 +30847,7 @@
         <v>45138</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30905,7 +30920,7 @@
         <v>46175</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30978,7 +30993,7 @@
         <v>46175</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31051,7 +31066,7 @@
         <v>46178</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31124,7 +31139,7 @@
         <v>46177</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31197,7 +31212,7 @@
         <v>46177</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31270,7 +31285,7 @@
         <v>46177</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31343,7 +31358,7 @@
         <v>46177</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31416,7 +31431,7 @@
         <v>46178</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31489,7 +31504,7 @@
         <v>46038</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31562,7 +31577,7 @@
         <v>46038</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31635,7 +31650,7 @@
         <v>46177</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31708,7 +31723,7 @@
         <v>46042</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31781,7 +31796,7 @@
         <v>45531</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31859,7 +31874,7 @@
         <v>44867</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31932,7 +31947,7 @@
         <v>46045</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32005,7 +32020,7 @@
         <v>46181</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32078,7 +32093,7 @@
         <v>46182</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32151,7 +32166,7 @@
         <v>45390</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32224,7 +32239,7 @@
         <v>45678</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32302,7 +32317,7 @@
         <v>46055</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32375,7 +32390,7 @@
         <v>46052</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32448,7 +32463,7 @@
         <v>46052</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32521,7 +32536,7 @@
         <v>46052</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32599,7 +32614,7 @@
         <v>46056</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32672,7 +32687,7 @@
         <v>45072</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32750,7 +32765,7 @@
         <v>44676</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32823,7 +32838,7 @@
         <v>46184</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32896,7 +32911,7 @@
         <v>46063</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32969,7 +32984,7 @@
         <v>46065</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33042,7 +33057,7 @@
         <v>46065</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33120,7 +33135,7 @@
         <v>46065</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33198,7 +33213,7 @@
         <v>46065</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33276,7 +33291,7 @@
         <v>46065</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33349,7 +33364,7 @@
         <v>45015</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33427,7 +33442,7 @@
         <v>46070</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33500,7 +33515,7 @@
         <v>46071</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33573,7 +33588,7 @@
         <v>46071</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33646,7 +33661,7 @@
         <v>46188</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33719,7 +33734,7 @@
         <v>46072</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33792,7 +33807,7 @@
         <v>46072</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33865,7 +33880,7 @@
         <v>45749</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33938,7 +33953,7 @@
         <v>46077</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34011,7 +34026,7 @@
         <v>46080</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34084,7 +34099,7 @@
         <v>45800</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34157,7 +34172,7 @@
         <v>45313</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34230,7 +34245,7 @@
         <v>46189</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34303,7 +34318,7 @@
         <v>46085</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34376,7 +34391,7 @@
         <v>46064</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34449,7 +34464,7 @@
         <v>45622</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34522,7 +34537,7 @@
         <v>46189</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34595,7 +34610,7 @@
         <v>46087</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34673,7 +34688,7 @@
         <v>46189</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34746,7 +34761,7 @@
         <v>46189</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34819,7 +34834,7 @@
         <v>46091</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34892,7 +34907,7 @@
         <v>46190</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34965,7 +34980,7 @@
         <v>46189</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35038,7 +35053,7 @@
         <v>44971</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35116,7 +35131,7 @@
         <v>46091</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35189,7 +35204,7 @@
         <v>46091</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35262,7 +35277,7 @@
         <v>46091</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35335,7 +35350,7 @@
         <v>46091</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35408,7 +35423,7 @@
         <v>46191</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35486,7 +35501,7 @@
         <v>45148</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35559,7 +35574,7 @@
         <v>45243</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35632,7 +35647,7 @@
         <v>46094</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35710,7 +35725,7 @@
         <v>44845</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35783,7 +35798,7 @@
         <v>46094</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35856,7 +35871,7 @@
         <v>45409</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35929,7 +35944,7 @@
         <v>44580</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36002,7 +36017,7 @@
         <v>46195</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36075,7 +36090,7 @@
         <v>46195</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36148,7 +36163,7 @@
         <v>46104</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36221,7 +36236,7 @@
         <v>46195</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36294,7 +36309,7 @@
         <v>46195</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36367,7 +36382,7 @@
         <v>44894</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36440,7 +36455,7 @@
         <v>46195</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36513,7 +36528,7 @@
         <v>45366</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36586,7 +36601,7 @@
         <v>46101</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36664,7 +36679,7 @@
         <v>46105</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36737,7 +36752,7 @@
         <v>46105</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36810,7 +36825,7 @@
         <v>46106</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36883,7 +36898,7 @@
         <v>46195</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36956,7 +36971,7 @@
         <v>46105</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37029,7 +37044,7 @@
         <v>45251</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37102,7 +37117,7 @@
         <v>46105</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37175,7 +37190,7 @@
         <v>44498</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37248,7 +37263,7 @@
         <v>46107</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37321,7 +37336,7 @@
         <v>46107</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37394,7 +37409,7 @@
         <v>45376</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37467,7 +37482,7 @@
         <v>46107</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37540,7 +37555,7 @@
         <v>46113</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37618,7 +37633,7 @@
         <v>46120</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37691,7 +37706,7 @@
         <v>44865</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37769,7 +37784,7 @@
         <v>45699</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37842,7 +37857,7 @@
         <v>46122</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37915,7 +37930,7 @@
         <v>45044</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37993,7 +38008,7 @@
         <v>45502</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38066,7 +38081,7 @@
         <v>44726</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38139,7 +38154,7 @@
         <v>46127</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38212,7 +38227,7 @@
         <v>46133</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38285,7 +38300,7 @@
         <v>46132</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38358,7 +38373,7 @@
         <v>46133</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38431,7 +38446,7 @@
         <v>46203</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38509,7 +38524,7 @@
         <v>44889</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38587,7 +38602,7 @@
         <v>46204</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38660,7 +38675,7 @@
         <v>46204</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38733,7 +38748,7 @@
         <v>44755</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38806,7 +38821,7 @@
         <v>46204</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38879,7 +38894,7 @@
         <v>46204</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38952,7 +38967,7 @@
         <v>44881</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39030,7 +39045,7 @@
         <v>45194</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39103,7 +39118,7 @@
         <v>46205</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39176,7 +39191,7 @@
         <v>46205</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39249,7 +39264,7 @@
         <v>46205</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39322,7 +39337,7 @@
         <v>45505</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39400,7 +39415,7 @@
         <v>44847</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39478,7 +39493,7 @@
         <v>46206</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39551,7 +39566,7 @@
         <v>46206</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39624,7 +39639,7 @@
         <v>44847</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39702,7 +39717,7 @@
         <v>46206</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39775,7 +39790,7 @@
         <v>45800</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39848,7 +39863,7 @@
         <v>46206</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39921,7 +39936,7 @@
         <v>45723</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39994,7 +40009,7 @@
         <v>45482</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40072,7 +40087,7 @@
         <v>46209</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40145,7 +40160,7 @@
         <v>45328</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40223,7 +40238,7 @@
         <v>45328</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40301,7 +40316,7 @@
         <v>46211</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40374,7 +40389,7 @@
         <v>45390</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40447,7 +40462,7 @@
         <v>44496</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40520,7 +40535,7 @@
         <v>44875</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40593,7 +40608,7 @@
         <v>44531</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40666,7 +40681,7 @@
         <v>45729</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40739,7 +40754,7 @@
         <v>46211</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40812,7 +40827,7 @@
         <v>45545</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40885,7 +40900,7 @@
         <v>45595</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40958,7 +40973,7 @@
         <v>45595</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41031,7 +41046,7 @@
         <v>46215</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41104,7 +41119,7 @@
         <v>46215</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41177,7 +41192,7 @@
         <v>45348</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41250,7 +41265,7 @@
         <v>46213</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41323,7 +41338,7 @@
         <v>46213</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41396,7 +41411,7 @@
         <v>45280</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41469,7 +41484,7 @@
         <v>44694</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41547,7 +41562,7 @@
         <v>46219</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41620,7 +41635,7 @@
         <v>46219</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41693,7 +41708,7 @@
         <v>46219</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41766,7 +41781,7 @@
         <v>46213</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41839,7 +41854,7 @@
         <v>46203</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41912,7 +41927,7 @@
         <v>46161</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41985,7 +42000,7 @@
         <v>44743</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42058,7 +42073,7 @@
         <v>44806</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42131,7 +42146,7 @@
         <v>44806</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42204,7 +42219,7 @@
         <v>45714</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42277,7 +42292,7 @@
         <v>46275</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42350,7 +42365,7 @@
         <v>44991</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42428,7 +42443,7 @@
         <v>46274</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42501,7 +42516,7 @@
         <v>45250</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42574,7 +42589,7 @@
         <v>45580</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42647,7 +42662,7 @@
         <v>46232</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42720,7 +42735,7 @@
         <v>45281</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42793,7 +42808,7 @@
         <v>44957</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42866,7 +42881,7 @@
         <v>45265</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42944,7 +42959,7 @@
         <v>45476</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43017,7 +43032,7 @@
         <v>45476</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43090,7 +43105,7 @@
         <v>46237</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43168,7 +43183,7 @@
         <v>45166</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43246,7 +43261,7 @@
         <v>46281</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43319,7 +43334,7 @@
         <v>44855</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43392,7 +43407,7 @@
         <v>44890</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43470,7 +43485,7 @@
         <v>46281</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43543,7 +43558,7 @@
         <v>46239</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43621,7 +43636,7 @@
         <v>46282</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43694,7 +43709,7 @@
         <v>44945</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43772,7 +43787,7 @@
         <v>46189</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43845,7 +43860,7 @@
         <v>44903</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43923,7 +43938,7 @@
         <v>46070</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43996,7 +44011,7 @@
         <v>46286</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44074,7 +44089,7 @@
         <v>46286</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44152,7 +44167,7 @@
         <v>45251</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44225,7 +44240,7 @@
         <v>46244</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44303,7 +44318,7 @@
         <v>46287</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44381,7 +44396,7 @@
         <v>46181</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44454,7 +44469,7 @@
         <v>46288</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44527,7 +44542,7 @@
         <v>45512</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44600,7 +44615,7 @@
         <v>45723</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44673,7 +44688,7 @@
         <v>44497</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44746,7 +44761,7 @@
         <v>44502</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44819,7 +44834,7 @@
         <v>46288</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44892,7 +44907,7 @@
         <v>46286</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44965,7 +44980,7 @@
         <v>45323</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45038,7 +45053,7 @@
         <v>46288</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45111,7 +45126,7 @@
         <v>45639</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45184,7 +45199,7 @@
         <v>44609</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45262,7 +45277,7 @@
         <v>44952</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45335,7 +45350,7 @@
         <v>46248</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45408,7 +45423,7 @@
         <v>44747</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45481,7 +45496,7 @@
         <v>45152</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45554,7 +45569,7 @@
         <v>45099</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45632,7 +45647,7 @@
         <v>45629</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45705,7 +45720,7 @@
         <v>45000</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45783,7 +45798,7 @@
         <v>45000</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45861,7 +45876,7 @@
         <v>46252</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45934,7 +45949,7 @@
         <v>44819</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46012,7 +46027,7 @@
         <v>45762</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46085,7 +46100,7 @@
         <v>46251</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46163,7 +46178,7 @@
         <v>45163</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46236,7 +46251,7 @@
         <v>46296</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46314,7 +46329,7 @@
         <v>46296</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46392,7 +46407,7 @@
         <v>46296</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46470,7 +46485,7 @@
         <v>46296</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46548,7 +46563,7 @@
         <v>46297</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46621,7 +46636,7 @@
         <v>46288</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46694,7 +46709,7 @@
         <v>46297</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46772,7 +46787,7 @@
         <v>45107</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46845,7 +46860,7 @@
         <v>45685</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46918,7 +46933,7 @@
         <v>46258</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46991,7 +47006,7 @@
         <v>45776</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47064,7 +47079,7 @@
         <v>45776</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47137,7 +47152,7 @@
         <v>45782</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47215,7 +47230,7 @@
         <v>45782</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47293,7 +47308,7 @@
         <v>45562</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47366,7 +47381,7 @@
         <v>46301</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47439,7 +47454,7 @@
         <v>45578</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47512,7 +47527,7 @@
         <v>46303</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47590,7 +47605,7 @@
         <v>46260</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47663,7 +47678,7 @@
         <v>45574</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47736,7 +47751,7 @@
         <v>45791</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47809,7 +47824,7 @@
         <v>45342</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47882,7 +47897,7 @@
         <v>45433</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47955,7 +47970,7 @@
         <v>45351</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48028,7 +48043,7 @@
         <v>45793</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48106,7 +48121,7 @@
         <v>46307</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48179,7 +48194,7 @@
         <v>45579</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48252,7 +48267,7 @@
         <v>44571</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48325,7 +48340,7 @@
         <v>45266</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48398,7 +48413,7 @@
         <v>46262</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48471,7 +48486,7 @@
         <v>45516</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48544,7 +48559,7 @@
         <v>45799</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48622,7 +48637,7 @@
         <v>45139</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48695,7 +48710,7 @@
         <v>46049</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48768,7 +48783,7 @@
         <v>46304</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48841,7 +48856,7 @@
         <v>45803</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48914,7 +48929,7 @@
         <v>45762</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48987,7 +49002,7 @@
         <v>45800</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49065,7 +49080,7 @@
         <v>46309</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49138,7 +49153,7 @@
         <v>45805</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49211,7 +49226,7 @@
         <v>45630</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49284,7 +49299,7 @@
         <v>46265</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49362,7 +49377,7 @@
         <v>45205</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49435,7 +49450,7 @@
         <v>45811</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49508,7 +49523,7 @@
         <v>46309</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49581,7 +49596,7 @@
         <v>45812</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49654,7 +49669,7 @@
         <v>46309</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49727,7 +49742,7 @@
         <v>45812</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49800,7 +49815,7 @@
         <v>46309</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49873,7 +49888,7 @@
         <v>45825</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49946,7 +49961,7 @@
         <v>45825</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50019,7 +50034,7 @@
         <v>45825</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50092,7 +50107,7 @@
         <v>45825</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50165,7 +50180,7 @@
         <v>45824</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50243,7 +50258,7 @@
         <v>45826</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50321,7 +50336,7 @@
         <v>45833</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50399,7 +50414,7 @@
         <v>45833</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50477,7 +50492,7 @@
         <v>45833</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50555,7 +50570,7 @@
         <v>45833</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50633,7 +50648,7 @@
         <v>45833</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50711,7 +50726,7 @@
         <v>45834</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50784,7 +50799,7 @@
         <v>45811</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50857,7 +50872,7 @@
         <v>45834</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50930,7 +50945,7 @@
         <v>45837</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51008,7 +51023,7 @@
         <v>45837</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51086,7 +51101,7 @@
         <v>45840</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51159,7 +51174,7 @@
         <v>45840</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51232,7 +51247,7 @@
         <v>45749</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51305,7 +51320,7 @@
         <v>45848</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51378,7 +51393,7 @@
         <v>45848</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51451,7 +51466,7 @@
         <v>45853</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51529,7 +51544,7 @@
         <v>44973</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51602,7 +51617,7 @@
         <v>45741</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51675,7 +51690,7 @@
         <v>45793</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51748,7 +51763,7 @@
         <v>45729</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51821,7 +51836,7 @@
         <v>45574</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51894,7 +51909,7 @@
         <v>45741</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51967,7 +51982,7 @@
         <v>45874</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52040,7 +52055,7 @@
         <v>45874</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52113,7 +52128,7 @@
         <v>45874</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52186,7 +52201,7 @@
         <v>45874</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52259,7 +52274,7 @@
         <v>45880</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52332,7 +52347,7 @@
         <v>44393</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52405,7 +52420,7 @@
         <v>45323</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52483,7 +52498,7 @@
         <v>45733</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52561,7 +52576,7 @@
         <v>45755</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52634,7 +52649,7 @@
         <v>45793</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52712,7 +52727,7 @@
         <v>46078</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52790,7 +52805,7 @@
         <v>46073</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52863,7 +52878,7 @@
         <v>46093</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52941,7 +52956,7 @@
         <v>46156</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53014,7 +53029,7 @@
         <v>46267</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>

--- a/Översikt HÄRNÖSAND.xlsx
+++ b/Översikt HÄRNÖSAND.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 56749-2025</t>
+          <t>A 5881-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45978</v>
+        <v>45335</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -613,22 +613,17 @@
           <t>HÄRNÖSAND</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I2" t="n">
-        <v>7.8</v>
+        <v>22.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
         <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
@@ -643,21 +638,160 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R2" t="n">
         <v>3</v>
       </c>
       <c r="S2" t="n">
+        <v>22</v>
+      </c>
+      <c r="T2" t="n">
+        <v>82</v>
+      </c>
+      <c r="U2" t="n">
+        <v>68</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Knärot
+Ringlav
+Dropptaggsvamp
+Gammelgransskål
+Motaggsvamp
+Rosenticka
+Tallkötticka
+Talltita
+Tretåig hackspett
+Ullticka
+Vedskivlav
+Violettgrå tagellav
+Bronshjon
+Nästlav
+Rävticka
+Vedticka
+Vågbandad barkbock
+Linnea
+Spillkråka
+Tjäder
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 5881-2024 artfynd.xlsx", "A 5881-2024")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 5881-2024 karta.png", "A 5881-2024")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 5881-2024 georefererad karta.tif", "A 5881-2024")</f>
+        <v/>
+      </c>
+      <c r="Z2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/knärot/A 5881-2024 karta knärot.png", "A 5881-2024")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 5881-2024 FSC-klagomål.docx", "A 5881-2024")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 5881-2024 FSC-klagomål mail.docx", "A 5881-2024")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 5881-2024 tillsynsbegäran.docx", "A 5881-2024")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 5881-2024 tillsynsbegäran mail.docx", "A 5881-2024")</f>
+        <v/>
+      </c>
+      <c r="AE2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/fåglar/A 5881-2024 prioriterade fågelarter.docx", "A 5881-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 56749-2025</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45978</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>HÄRNÖSAND</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>11</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>14</v>
+      </c>
+      <c r="R3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S3" t="n">
         <v>20</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T3" t="n">
         <v>166</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U3" t="n">
         <v>162</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -681,116 +815,248 @@
 Järpe</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 56749-2025 artfynd.xlsx", "A 56749-2025")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 56749-2025 karta.png", "A 56749-2025")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 56749-2025 georefererad karta.tif", "A 56749-2025")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 56749-2025 FSC-klagomål.docx", "A 56749-2025")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 56749-2025 FSC-klagomål mail.docx", "A 56749-2025")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 56749-2025 tillsynsbegäran.docx", "A 56749-2025")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 56749-2025 tillsynsbegäran mail.docx", "A 56749-2025")</f>
         <v/>
       </c>
-      <c r="AE2">
+      <c r="AE3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/fåglar/A 56749-2025 prioriterade fågelarter.docx", "A 56749-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 47711-2024</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45588</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>HÄRNÖSAND</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" t="n">
+        <v>9</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>12</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="n">
+        <v>65</v>
+      </c>
+      <c r="U4" t="n">
+        <v>51</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Knärot
+Ringlav
+Dropptaggsvamp
+Motaggsvamp
+Orange taggsvamp
+Rosenticka
+Svartvit taggsvamp
+Tallticka
+Tretåig hackspett
+Ullticka
+Violettgrå tagellav
+Bronshjon
+Nästlav
+Vedticka
+Vågbandad barkbock
+Kötticka
+Mattlummer
+Spillkråka
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 47711-2024 artfynd.xlsx", "A 47711-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 47711-2024 karta.png", "A 47711-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 47711-2024 georefererad karta.tif", "A 47711-2024")</f>
+        <v/>
+      </c>
+      <c r="Z4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/knärot/A 47711-2024 karta knärot.png", "A 47711-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 47711-2024 FSC-klagomål.docx", "A 47711-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 47711-2024 FSC-klagomål mail.docx", "A 47711-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 47711-2024 tillsynsbegäran.docx", "A 47711-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 47711-2024 tillsynsbegäran mail.docx", "A 47711-2024")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2280/fåglar/A 47711-2024 prioriterade fågelarter.docx", "A 47711-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>A 4816-2024</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
         <v>45328</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VÄSTERNORRLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>HÄRNÖSAND</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="E5" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>HÄRNÖSAND</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="I5" t="n">
         <v>11.6</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J5" t="n">
         <v>5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K5" t="n">
         <v>3</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L5" t="n">
         <v>7</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M5" t="n">
         <v>4</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>11</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R5" t="n">
         <v>4</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S5" t="n">
         <v>18</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T5" t="n">
         <v>78</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U5" t="n">
         <v>76</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Blackticka
 Garnlav
@@ -812,111 +1078,111 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 4816-2024 artfynd.xlsx", "A 4816-2024")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 4816-2024 karta.png", "A 4816-2024")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 4816-2024 georefererad karta.tif", "A 4816-2024")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 4816-2024 FSC-klagomål.docx", "A 4816-2024")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 4816-2024 FSC-klagomål mail.docx", "A 4816-2024")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 4816-2024 tillsynsbegäran.docx", "A 4816-2024")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 4816-2024 tillsynsbegäran mail.docx", "A 4816-2024")</f>
         <v/>
       </c>
-      <c r="AE3">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/fåglar/A 4816-2024 prioriterade fågelarter.docx", "A 4816-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A 39378-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
         <v>46288</v>
       </c>
-      <c r="E4" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTERNORRLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>HÄRNÖSAND</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
+      <c r="E6" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HÄRNÖSAND</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>2.8</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J6" t="n">
         <v>2</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K6" t="n">
         <v>5</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L6" t="n">
         <v>8</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M6" t="n">
         <v>3</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>12</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R6" t="n">
         <v>4</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S6" t="n">
         <v>18</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T6" t="n">
         <v>36</v>
       </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Trådbrosklav
 Garnlav
@@ -938,242 +1204,112 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 39378-2026 artfynd.xlsx", "A 39378-2026")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 39378-2026 karta.png", "A 39378-2026")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 39378-2026 georefererad karta.tif", "A 39378-2026")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 39378-2026 FSC-klagomål.docx", "A 39378-2026")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 39378-2026 FSC-klagomål mail.docx", "A 39378-2026")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 39378-2026 tillsynsbegäran.docx", "A 39378-2026")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 39378-2026 tillsynsbegäran mail.docx", "A 39378-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 5881-2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45335</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTERNORRLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>HÄRNÖSAND</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="J5" t="n">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S 174-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46044</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HÄRNÖSAND</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J7" t="n">
         <v>5</v>
       </c>
-      <c r="K5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="K7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L7" t="n">
         <v>9</v>
       </c>
-      <c r="M5" t="n">
-        <v>3</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>12</v>
-      </c>
-      <c r="R5" t="n">
-        <v>3</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>10</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
         <v>18</v>
       </c>
-      <c r="T5" t="n">
-        <v>60</v>
-      </c>
-      <c r="U5" t="n">
-        <v>46</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Knärot
-Ringlav
-Dropptaggsvamp
-Gammelgransskål
-Motaggsvamp
-Rosenticka
-Tallkötticka
-Talltita
-Tretåig hackspett
-Ullticka
-Violettgrå tagellav
-Nästlav
-Rävticka
-Vedticka
-Linnea
-Spillkråka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 5881-2024 artfynd.xlsx", "A 5881-2024")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 5881-2024 karta.png", "A 5881-2024")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 5881-2024 georefererad karta.tif", "A 5881-2024")</f>
-        <v/>
-      </c>
-      <c r="Z5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/knärot/A 5881-2024 karta knärot.png", "A 5881-2024")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 5881-2024 FSC-klagomål.docx", "A 5881-2024")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 5881-2024 FSC-klagomål mail.docx", "A 5881-2024")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 5881-2024 tillsynsbegäran.docx", "A 5881-2024")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 5881-2024 tillsynsbegäran mail.docx", "A 5881-2024")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/fåglar/A 5881-2024 prioriterade fågelarter.docx", "A 5881-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>S 174-2026</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>46044</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTERNORRLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>HÄRNÖSAND</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J6" t="n">
-        <v>5</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6</v>
-      </c>
-      <c r="L6" t="n">
-        <v>9</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>10</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>18</v>
-      </c>
-      <c r="T6" t="n">
+      <c r="T7" t="n">
         <v>34</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Blågrå svartspik
@@ -1195,164 +1331,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/S 174-2026 artfynd.xlsx", "S 174-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/S 174-2026 karta.png", "S 174-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/S 174-2026 georefererad karta.tif", "S 174-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/S 174-2026 FSC-klagomål.docx", "S 174-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/S 174-2026 FSC-klagomål mail.docx", "S 174-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/S 174-2026 tillsynsbegäran.docx", "S 174-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/S 174-2026 tillsynsbegäran mail.docx", "S 174-2026")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2280/fåglar/S 174-2026 prioriterade fågelarter.docx", "S 174-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 47711-2024</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45588</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTERNORRLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HÄRNÖSAND</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" t="n">
-        <v>9</v>
-      </c>
-      <c r="M7" t="n">
-        <v>2</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>11</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>16</v>
-      </c>
-      <c r="T7" t="n">
-        <v>57</v>
-      </c>
-      <c r="U7" t="n">
-        <v>43</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Ringlav
-Dropptaggsvamp
-Motaggsvamp
-Orange taggsvamp
-Rosenticka
-Svartvit taggsvamp
-Tallticka
-Tretåig hackspett
-Ullticka
-Violettgrå tagellav
-Bronshjon
-Nästlav
-Vedticka
-Kötticka
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/artfynd/A 47711-2024 artfynd.xlsx", "A 47711-2024")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor/A 47711-2024 karta.png", "A 47711-2024")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/kartor_geotiff/A 47711-2024 georefererad karta.tif", "A 47711-2024")</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/knärot/A 47711-2024 karta knärot.png", "A 47711-2024")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomål/A 47711-2024 FSC-klagomål.docx", "A 47711-2024")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/klagomålsmail/A 47711-2024 FSC-klagomål mail.docx", "A 47711-2024")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsyn/A 47711-2024 tillsynsbegäran.docx", "A 47711-2024")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/tillsynsmail/A 47711-2024 tillsynsbegäran mail.docx", "A 47711-2024")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2280/fåglar/A 47711-2024 prioriterade fågelarter.docx", "A 47711-2024")</f>
         <v/>
       </c>
     </row>
@@ -1376,7 +1384,7 @@
         <v>45763</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1508,7 +1516,7 @@
         <v>44686</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1631,7 +1639,7 @@
         <v>46189</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1758,7 +1766,7 @@
         <v>45938</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1889,7 +1897,7 @@
         <v>45546</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2018,7 +2026,7 @@
         <v>45394</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2142,7 +2150,7 @@
         <v>45930</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2269,7 +2277,7 @@
         <v>45763</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2388,7 +2396,7 @@
         <v>45484</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2510,7 +2518,7 @@
         <v>45139</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2623,7 +2631,7 @@
         <v>45805</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2745,7 +2753,7 @@
         <v>45826</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2857,7 +2865,7 @@
         <v>45616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2974,7 +2982,7 @@
         <v>45082</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3090,7 +3098,7 @@
         <v>45027</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3205,7 +3213,7 @@
         <v>44874</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3320,7 +3328,7 @@
         <v>46183</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3430,7 +3438,7 @@
         <v>45352</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3548,7 +3556,7 @@
         <v>45957</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3662,7 +3670,7 @@
         <v>45188</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3780,7 +3788,7 @@
         <v>45593</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3894,7 +3902,7 @@
         <v>45593</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4008,7 +4016,7 @@
         <v>45548</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4117,7 +4125,7 @@
         <v>45567</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4231,7 +4239,7 @@
         <v>44979</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4349,7 +4357,7 @@
         <v>45477</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4457,7 +4465,7 @@
         <v>45314</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4570,7 +4578,7 @@
         <v>45971</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4683,7 +4691,7 @@
         <v>46176</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4796,7 +4804,7 @@
         <v>45513</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4909,7 +4917,7 @@
         <v>45560</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5022,7 +5030,7 @@
         <v>46251</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5135,7 +5143,7 @@
         <v>45848</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5248,7 +5256,7 @@
         <v>45323</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5365,7 +5373,7 @@
         <v>45790</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5478,7 +5486,7 @@
         <v>44686</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5594,7 +5602,7 @@
         <v>45355</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5701,7 +5709,7 @@
         <v>44755</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5808,7 +5816,7 @@
         <v>45617</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5920,7 +5928,7 @@
         <v>45526</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6032,7 +6040,7 @@
         <v>45930</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6144,7 +6152,7 @@
         <v>46003</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6260,7 +6268,7 @@
         <v>45182</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6372,7 +6380,7 @@
         <v>45596</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6484,7 +6492,7 @@
         <v>46244</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6600,7 +6608,7 @@
         <v>45322</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6707,7 +6715,7 @@
         <v>44664</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6813,7 +6821,7 @@
         <v>45618</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6924,7 +6932,7 @@
         <v>45376</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7035,7 +7043,7 @@
         <v>45575</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7141,7 +7149,7 @@
         <v>45930</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7256,7 +7264,7 @@
         <v>45910</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7367,7 +7375,7 @@
         <v>46141</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7473,7 +7481,7 @@
         <v>45967</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7584,7 +7592,7 @@
         <v>44874</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7695,7 +7703,7 @@
         <v>45513</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7806,7 +7814,7 @@
         <v>45267</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7917,7 +7925,7 @@
         <v>46244</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8028,7 +8036,7 @@
         <v>46303</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8143,7 +8151,7 @@
         <v>45847</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8258,7 +8266,7 @@
         <v>45996</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8369,7 +8377,7 @@
         <v>44676</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8474,7 +8482,7 @@
         <v>44585</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8579,7 +8587,7 @@
         <v>44655</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8684,7 +8692,7 @@
         <v>45554</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8789,7 +8797,7 @@
         <v>45456</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8899,7 +8907,7 @@
         <v>45008</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9004,7 +9012,7 @@
         <v>45583</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9113,7 +9121,7 @@
         <v>45350</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9223,7 +9231,7 @@
         <v>45649</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9328,7 +9336,7 @@
         <v>45919</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9438,7 +9446,7 @@
         <v>45352</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9548,7 +9556,7 @@
         <v>46031</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9657,7 +9665,7 @@
         <v>46176</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9767,7 +9775,7 @@
         <v>45276</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9872,7 +9880,7 @@
         <v>46189</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9977,7 +9985,7 @@
         <v>46184</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10086,7 +10094,7 @@
         <v>46127</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10191,7 +10199,7 @@
         <v>44559</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10296,7 +10304,7 @@
         <v>46213</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10405,7 +10413,7 @@
         <v>45372</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10515,7 +10523,7 @@
         <v>44837</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10620,7 +10628,7 @@
         <v>45428</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10730,7 +10738,7 @@
         <v>46191</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10840,7 +10848,7 @@
         <v>45805</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10954,7 +10962,7 @@
         <v>45805</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11059,7 +11067,7 @@
         <v>45811</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11164,7 +11172,7 @@
         <v>44874</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11237,7 +11245,7 @@
         <v>44664</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11310,7 +11318,7 @@
         <v>44806</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11383,7 +11391,7 @@
         <v>44846</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11461,7 +11469,7 @@
         <v>44875</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11534,7 +11542,7 @@
         <v>44532</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11607,7 +11615,7 @@
         <v>44608</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11680,7 +11688,7 @@
         <v>44720</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11753,7 +11761,7 @@
         <v>44600</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11831,7 +11839,7 @@
         <v>44824</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11904,7 +11912,7 @@
         <v>44734</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11977,7 +11985,7 @@
         <v>44487</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12050,7 +12058,7 @@
         <v>44512</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12123,7 +12131,7 @@
         <v>44517</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12201,7 +12209,7 @@
         <v>44728</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12279,7 +12287,7 @@
         <v>44664</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12352,7 +12360,7 @@
         <v>44804</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12425,7 +12433,7 @@
         <v>44512</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12498,7 +12506,7 @@
         <v>44503</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12571,7 +12579,7 @@
         <v>44735</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12644,7 +12652,7 @@
         <v>44581</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12717,7 +12725,7 @@
         <v>44848</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12790,7 +12798,7 @@
         <v>44672</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12863,7 +12871,7 @@
         <v>44652</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12936,7 +12944,7 @@
         <v>44515</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13009,7 +13017,7 @@
         <v>44664</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13082,7 +13090,7 @@
         <v>44616</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13155,7 +13163,7 @@
         <v>44496</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13228,7 +13236,7 @@
         <v>44532</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13301,7 +13309,7 @@
         <v>44571</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13374,7 +13382,7 @@
         <v>44512</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13447,7 +13455,7 @@
         <v>44664</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13520,7 +13528,7 @@
         <v>44536</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13593,7 +13601,7 @@
         <v>44522</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13666,7 +13674,7 @@
         <v>44585</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13739,7 +13747,7 @@
         <v>44792</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13812,7 +13820,7 @@
         <v>45462</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13885,7 +13893,7 @@
         <v>45293</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13958,7 +13966,7 @@
         <v>44747</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14031,7 +14039,7 @@
         <v>44858</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14104,7 +14112,7 @@
         <v>44641</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14177,7 +14185,7 @@
         <v>44881</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14255,7 +14263,7 @@
         <v>45334</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14328,7 +14336,7 @@
         <v>45209</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14406,7 +14414,7 @@
         <v>45667</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14479,7 +14487,7 @@
         <v>44617</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14552,7 +14560,7 @@
         <v>45576</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14630,7 +14638,7 @@
         <v>45281</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14703,7 +14711,7 @@
         <v>45405</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14776,7 +14784,7 @@
         <v>45314</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14849,7 +14857,7 @@
         <v>45762</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14922,7 +14930,7 @@
         <v>45496</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14995,7 +15003,7 @@
         <v>45231</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15068,7 +15076,7 @@
         <v>45352</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15146,7 +15154,7 @@
         <v>44809</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15219,7 +15227,7 @@
         <v>45757</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15292,7 +15300,7 @@
         <v>44853</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15365,7 +15373,7 @@
         <v>45126</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15438,7 +15446,7 @@
         <v>45558</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15511,7 +15519,7 @@
         <v>45228</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15584,7 +15592,7 @@
         <v>45350</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15662,7 +15670,7 @@
         <v>45300</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15735,7 +15743,7 @@
         <v>45628</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15808,7 +15816,7 @@
         <v>45482</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15886,7 +15894,7 @@
         <v>45106</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15964,7 +15972,7 @@
         <v>45531</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16037,7 +16045,7 @@
         <v>44853</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16110,7 +16118,7 @@
         <v>45281</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16183,7 +16191,7 @@
         <v>45289</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16256,7 +16264,7 @@
         <v>45278</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16334,7 +16342,7 @@
         <v>45181</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16407,7 +16415,7 @@
         <v>45289</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16480,7 +16488,7 @@
         <v>45749</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16553,7 +16561,7 @@
         <v>45578</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16626,7 +16634,7 @@
         <v>45578</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16699,7 +16707,7 @@
         <v>44728</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16772,7 +16780,7 @@
         <v>45757</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16845,7 +16853,7 @@
         <v>45496</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16918,7 +16926,7 @@
         <v>45764</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16996,7 +17004,7 @@
         <v>45483</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17069,7 +17077,7 @@
         <v>44603</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17142,7 +17150,7 @@
         <v>45769</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17220,7 +17228,7 @@
         <v>45173</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17298,7 +17306,7 @@
         <v>45168</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17371,7 +17379,7 @@
         <v>45203</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17444,7 +17452,7 @@
         <v>44980</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17517,7 +17525,7 @@
         <v>45097</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17590,7 +17598,7 @@
         <v>45701</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17668,7 +17676,7 @@
         <v>45562</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17741,7 +17749,7 @@
         <v>45729</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17814,7 +17822,7 @@
         <v>45761</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17887,7 +17895,7 @@
         <v>45617</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17960,7 +17968,7 @@
         <v>45352</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18038,7 +18046,7 @@
         <v>45887</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18116,7 +18124,7 @@
         <v>45769</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18194,7 +18202,7 @@
         <v>45730</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18267,7 +18275,7 @@
         <v>45342</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18340,7 +18348,7 @@
         <v>45531</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18413,7 +18421,7 @@
         <v>45887</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18486,7 +18494,7 @@
         <v>45888</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18559,7 +18567,7 @@
         <v>45638</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18632,7 +18640,7 @@
         <v>45884</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18705,7 +18713,7 @@
         <v>45890</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18783,7 +18791,7 @@
         <v>45890</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18861,7 +18869,7 @@
         <v>45293</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18934,7 +18942,7 @@
         <v>45891</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19012,7 +19020,7 @@
         <v>45180</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19085,7 +19093,7 @@
         <v>44853</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19158,7 +19166,7 @@
         <v>45147</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19231,7 +19239,7 @@
         <v>45897</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19304,7 +19312,7 @@
         <v>46065</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19382,7 +19390,7 @@
         <v>45771</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19455,7 +19463,7 @@
         <v>45320</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19528,7 +19536,7 @@
         <v>45904</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19601,7 +19609,7 @@
         <v>46024</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19674,7 +19682,7 @@
         <v>45168</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19747,7 +19755,7 @@
         <v>45293</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19820,7 +19828,7 @@
         <v>45901</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19893,7 +19901,7 @@
         <v>45825</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19966,7 +19974,7 @@
         <v>45526</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20039,7 +20047,7 @@
         <v>45523</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20112,7 +20120,7 @@
         <v>45887</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20185,7 +20193,7 @@
         <v>45840</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20258,7 +20266,7 @@
         <v>45803</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20331,7 +20339,7 @@
         <v>46072</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20404,7 +20412,7 @@
         <v>46142</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20477,7 +20485,7 @@
         <v>45915</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20555,7 +20563,7 @@
         <v>45915</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20633,7 +20641,7 @@
         <v>45168</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20706,7 +20714,7 @@
         <v>45072</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20779,7 +20787,7 @@
         <v>44936</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20852,7 +20860,7 @@
         <v>46142</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20925,7 +20933,7 @@
         <v>45917</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20998,7 +21006,7 @@
         <v>45511</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21071,7 +21079,7 @@
         <v>45749</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21144,7 +21152,7 @@
         <v>45919</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21222,7 +21230,7 @@
         <v>44728</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21295,7 +21303,7 @@
         <v>45923</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21373,7 +21381,7 @@
         <v>45922</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21446,7 +21454,7 @@
         <v>45922</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21519,7 +21527,7 @@
         <v>45924</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21592,7 +21600,7 @@
         <v>44971</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21670,7 +21678,7 @@
         <v>45924</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21743,7 +21751,7 @@
         <v>45924</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21816,7 +21824,7 @@
         <v>45924</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21889,7 +21897,7 @@
         <v>45924</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21962,7 +21970,7 @@
         <v>45489</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22040,7 +22048,7 @@
         <v>44791</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22113,7 +22121,7 @@
         <v>45273</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22186,7 +22194,7 @@
         <v>46150</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22259,7 +22267,7 @@
         <v>46153</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22332,7 +22340,7 @@
         <v>46153</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22405,7 +22413,7 @@
         <v>45919</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22483,7 +22491,7 @@
         <v>45936</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22556,7 +22564,7 @@
         <v>45936</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22629,7 +22637,7 @@
         <v>45126</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22702,7 +22710,7 @@
         <v>45936</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22775,7 +22783,7 @@
         <v>45937</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22853,7 +22861,7 @@
         <v>45685</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22926,7 +22934,7 @@
         <v>44987</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23004,7 +23012,7 @@
         <v>45189</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23077,7 +23085,7 @@
         <v>45939</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23155,7 +23163,7 @@
         <v>45376</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23228,7 +23236,7 @@
         <v>44869</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23301,7 +23309,7 @@
         <v>45006</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23374,7 +23382,7 @@
         <v>45428</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23447,7 +23455,7 @@
         <v>46155</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23520,7 +23528,7 @@
         <v>45562</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23598,7 +23606,7 @@
         <v>45930</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23671,7 +23679,7 @@
         <v>45409</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23744,7 +23752,7 @@
         <v>45645</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23817,7 +23825,7 @@
         <v>46107</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23890,7 +23898,7 @@
         <v>45409</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23963,7 +23971,7 @@
         <v>45959</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24036,7 +24044,7 @@
         <v>45959</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24109,7 +24117,7 @@
         <v>46161</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24182,7 +24190,7 @@
         <v>46161</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24255,7 +24263,7 @@
         <v>46161</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24328,7 +24336,7 @@
         <v>45786</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24406,7 +24414,7 @@
         <v>45790</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24484,7 +24492,7 @@
         <v>46160</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24557,7 +24565,7 @@
         <v>45813</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24630,7 +24638,7 @@
         <v>46161</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24703,7 +24711,7 @@
         <v>46161</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24776,7 +24784,7 @@
         <v>46161</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24849,7 +24857,7 @@
         <v>45793</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24927,7 +24935,7 @@
         <v>46161</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25000,7 +25008,7 @@
         <v>46161</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25073,7 +25081,7 @@
         <v>45147</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25146,7 +25154,7 @@
         <v>45972</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25224,7 +25232,7 @@
         <v>45462</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25297,7 +25305,7 @@
         <v>46162</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25370,7 +25378,7 @@
         <v>45972</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25448,7 +25456,7 @@
         <v>46162</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25521,7 +25529,7 @@
         <v>45832</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25594,7 +25602,7 @@
         <v>45161</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25672,7 +25680,7 @@
         <v>45418</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25745,7 +25753,7 @@
         <v>45091</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25818,7 +25826,7 @@
         <v>45975</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25896,7 +25904,7 @@
         <v>45975</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25974,7 +25982,7 @@
         <v>45978</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26052,7 +26060,7 @@
         <v>44937</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26125,7 +26133,7 @@
         <v>45979</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26203,7 +26211,7 @@
         <v>45979</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26276,7 +26284,7 @@
         <v>45979</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26349,7 +26357,7 @@
         <v>45979</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26422,7 +26430,7 @@
         <v>45979</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26500,7 +26508,7 @@
         <v>45979</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26578,7 +26586,7 @@
         <v>45979</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26656,7 +26664,7 @@
         <v>45981</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26734,7 +26742,7 @@
         <v>45981</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26812,7 +26820,7 @@
         <v>45723</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26885,7 +26893,7 @@
         <v>45733</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26958,7 +26966,7 @@
         <v>45293</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27031,7 +27039,7 @@
         <v>46167</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27104,7 +27112,7 @@
         <v>46167</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27177,7 +27185,7 @@
         <v>45987</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27250,7 +27258,7 @@
         <v>45392</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27323,7 +27331,7 @@
         <v>45044</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27396,7 +27404,7 @@
         <v>44951</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27474,7 +27482,7 @@
         <v>45638</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27547,7 +27555,7 @@
         <v>46149</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27620,7 +27628,7 @@
         <v>45992</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27693,7 +27701,7 @@
         <v>44897</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27766,7 +27774,7 @@
         <v>45044</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27844,7 +27852,7 @@
         <v>45126</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27917,7 +27925,7 @@
         <v>46168</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27990,7 +27998,7 @@
         <v>44732</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28063,7 +28071,7 @@
         <v>45999</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28136,7 +28144,7 @@
         <v>45999</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28209,7 +28217,7 @@
         <v>44596</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28287,7 +28295,7 @@
         <v>45999</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28360,7 +28368,7 @@
         <v>45985</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28433,7 +28441,7 @@
         <v>44706</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28506,7 +28514,7 @@
         <v>45512</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28579,7 +28587,7 @@
         <v>46000</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28652,7 +28660,7 @@
         <v>46170</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28725,7 +28733,7 @@
         <v>46170</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28798,7 +28806,7 @@
         <v>46174</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28871,7 +28879,7 @@
         <v>45646</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28944,7 +28952,7 @@
         <v>46013</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29017,7 +29025,7 @@
         <v>45329</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29090,7 +29098,7 @@
         <v>45910</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29163,7 +29171,7 @@
         <v>46094</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29236,7 +29244,7 @@
         <v>45616</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29314,7 +29322,7 @@
         <v>45320</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29387,7 +29395,7 @@
         <v>46023</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29460,7 +29468,7 @@
         <v>46023</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29533,7 +29541,7 @@
         <v>46024</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29606,7 +29614,7 @@
         <v>46024</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29679,7 +29687,7 @@
         <v>46165</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29752,7 +29760,7 @@
         <v>46024</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29825,7 +29833,7 @@
         <v>46026</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29898,7 +29906,7 @@
         <v>46024</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29971,7 +29979,7 @@
         <v>45035</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30044,7 +30052,7 @@
         <v>46175</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30117,7 +30125,7 @@
         <v>46029</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30190,7 +30198,7 @@
         <v>46029</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30263,7 +30271,7 @@
         <v>46030</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30336,7 +30344,7 @@
         <v>45163</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30409,7 +30417,7 @@
         <v>46029</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30482,7 +30490,7 @@
         <v>46029</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30555,7 +30563,7 @@
         <v>46030</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30628,7 +30636,7 @@
         <v>46034</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30701,7 +30709,7 @@
         <v>44853</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30774,7 +30782,7 @@
         <v>46035</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30847,7 +30855,7 @@
         <v>45138</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30920,7 +30928,7 @@
         <v>46175</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30993,7 +31001,7 @@
         <v>46175</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31066,7 +31074,7 @@
         <v>46178</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31139,7 +31147,7 @@
         <v>46177</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31212,7 +31220,7 @@
         <v>46177</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31285,7 +31293,7 @@
         <v>46177</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31358,7 +31366,7 @@
         <v>46177</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31431,7 +31439,7 @@
         <v>46178</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31504,7 +31512,7 @@
         <v>46038</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31577,7 +31585,7 @@
         <v>46038</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31650,7 +31658,7 @@
         <v>46177</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31723,7 +31731,7 @@
         <v>46042</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31796,7 +31804,7 @@
         <v>45531</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31874,7 +31882,7 @@
         <v>44867</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31947,7 +31955,7 @@
         <v>46045</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32020,7 +32028,7 @@
         <v>46181</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32093,7 +32101,7 @@
         <v>46182</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32166,7 +32174,7 @@
         <v>45390</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32239,7 +32247,7 @@
         <v>45678</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32317,7 +32325,7 @@
         <v>46055</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32390,7 +32398,7 @@
         <v>46052</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32463,7 +32471,7 @@
         <v>46052</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32536,7 +32544,7 @@
         <v>46052</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32614,7 +32622,7 @@
         <v>46056</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32687,7 +32695,7 @@
         <v>45072</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32765,7 +32773,7 @@
         <v>44676</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32838,7 +32846,7 @@
         <v>46184</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32911,7 +32919,7 @@
         <v>46063</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32984,7 +32992,7 @@
         <v>46065</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33057,7 +33065,7 @@
         <v>46065</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33135,7 +33143,7 @@
         <v>46065</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33213,7 +33221,7 @@
         <v>46065</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33291,7 +33299,7 @@
         <v>46065</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33364,7 +33372,7 @@
         <v>45015</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33442,7 +33450,7 @@
         <v>46070</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33515,7 +33523,7 @@
         <v>46071</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33588,7 +33596,7 @@
         <v>46071</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33661,7 +33669,7 @@
         <v>46188</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33734,7 +33742,7 @@
         <v>46072</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33807,7 +33815,7 @@
         <v>46072</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33880,7 +33888,7 @@
         <v>45749</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33953,7 +33961,7 @@
         <v>46077</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34026,7 +34034,7 @@
         <v>46080</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34099,7 +34107,7 @@
         <v>45800</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34172,7 +34180,7 @@
         <v>45313</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34245,7 +34253,7 @@
         <v>46189</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34318,7 +34326,7 @@
         <v>46085</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34391,7 +34399,7 @@
         <v>46064</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34464,7 +34472,7 @@
         <v>45622</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34537,7 +34545,7 @@
         <v>46189</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34610,7 +34618,7 @@
         <v>46087</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34688,7 +34696,7 @@
         <v>46189</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34761,7 +34769,7 @@
         <v>46189</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34834,7 +34842,7 @@
         <v>46091</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34907,7 +34915,7 @@
         <v>46190</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34980,7 +34988,7 @@
         <v>46189</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35053,7 +35061,7 @@
         <v>44971</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35131,7 +35139,7 @@
         <v>46091</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35204,7 +35212,7 @@
         <v>46091</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35277,7 +35285,7 @@
         <v>46091</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35350,7 +35358,7 @@
         <v>46091</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35423,7 +35431,7 @@
         <v>46191</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35501,7 +35509,7 @@
         <v>45148</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35574,7 +35582,7 @@
         <v>45243</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35647,7 +35655,7 @@
         <v>46094</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35725,7 +35733,7 @@
         <v>44845</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35798,7 +35806,7 @@
         <v>46094</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35871,7 +35879,7 @@
         <v>45409</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35944,7 +35952,7 @@
         <v>44580</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36017,7 +36025,7 @@
         <v>46195</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36090,7 +36098,7 @@
         <v>46195</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36163,7 +36171,7 @@
         <v>46104</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36236,7 +36244,7 @@
         <v>46195</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36309,7 +36317,7 @@
         <v>46195</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36382,7 +36390,7 @@
         <v>44894</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36455,7 +36463,7 @@
         <v>46195</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36528,7 +36536,7 @@
         <v>45366</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36601,7 +36609,7 @@
         <v>46101</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36679,7 +36687,7 @@
         <v>46105</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36752,7 +36760,7 @@
         <v>46105</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36825,7 +36833,7 @@
         <v>46106</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36898,7 +36906,7 @@
         <v>46195</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36971,7 +36979,7 @@
         <v>46105</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37044,7 +37052,7 @@
         <v>45251</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37117,7 +37125,7 @@
         <v>46105</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37190,7 +37198,7 @@
         <v>44498</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37263,7 +37271,7 @@
         <v>46107</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37336,7 +37344,7 @@
         <v>46107</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37409,7 +37417,7 @@
         <v>45376</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37482,7 +37490,7 @@
         <v>46107</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37555,7 +37563,7 @@
         <v>46113</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37633,7 +37641,7 @@
         <v>46120</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37706,7 +37714,7 @@
         <v>44865</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37784,7 +37792,7 @@
         <v>45699</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37857,7 +37865,7 @@
         <v>46122</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37930,7 +37938,7 @@
         <v>45044</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38008,7 +38016,7 @@
         <v>45502</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38081,7 +38089,7 @@
         <v>44726</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38154,7 +38162,7 @@
         <v>46127</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38227,7 +38235,7 @@
         <v>46133</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38300,7 +38308,7 @@
         <v>46132</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38373,7 +38381,7 @@
         <v>46133</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38446,7 +38454,7 @@
         <v>46203</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38524,7 +38532,7 @@
         <v>44889</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38602,7 +38610,7 @@
         <v>46204</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38675,7 +38683,7 @@
         <v>46204</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38748,7 +38756,7 @@
         <v>44755</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38821,7 +38829,7 @@
         <v>46204</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38894,7 +38902,7 @@
         <v>46204</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38967,7 +38975,7 @@
         <v>44881</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39045,7 +39053,7 @@
         <v>45194</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39118,7 +39126,7 @@
         <v>46205</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39191,7 +39199,7 @@
         <v>46205</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39264,7 +39272,7 @@
         <v>46205</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39337,7 +39345,7 @@
         <v>45505</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39415,7 +39423,7 @@
         <v>44847</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39493,7 +39501,7 @@
         <v>46206</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39566,7 +39574,7 @@
         <v>46206</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39639,7 +39647,7 @@
         <v>44847</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39717,7 +39725,7 @@
         <v>46206</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39790,7 +39798,7 @@
         <v>45800</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39863,7 +39871,7 @@
         <v>46206</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39936,7 +39944,7 @@
         <v>45723</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40009,7 +40017,7 @@
         <v>45482</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40087,7 +40095,7 @@
         <v>46209</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40160,7 +40168,7 @@
         <v>45328</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40238,7 +40246,7 @@
         <v>45328</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40316,7 +40324,7 @@
         <v>46211</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40389,7 +40397,7 @@
         <v>45390</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40462,7 +40470,7 @@
         <v>44496</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40535,7 +40543,7 @@
         <v>44875</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40608,7 +40616,7 @@
         <v>44531</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40681,7 +40689,7 @@
         <v>45729</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40754,7 +40762,7 @@
         <v>46211</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40827,7 +40835,7 @@
         <v>45545</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40900,7 +40908,7 @@
         <v>45595</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40973,7 +40981,7 @@
         <v>45595</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41046,7 +41054,7 @@
         <v>46215</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41119,7 +41127,7 @@
         <v>46215</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41192,7 +41200,7 @@
         <v>45348</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41265,7 +41273,7 @@
         <v>46213</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41338,7 +41346,7 @@
         <v>46213</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41411,7 +41419,7 @@
         <v>45280</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41484,7 +41492,7 @@
         <v>44694</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41562,7 +41570,7 @@
         <v>46219</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41635,7 +41643,7 @@
         <v>46219</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41708,7 +41716,7 @@
         <v>46219</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41781,7 +41789,7 @@
         <v>46213</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41854,7 +41862,7 @@
         <v>46203</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41927,7 +41935,7 @@
         <v>46161</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42000,7 +42008,7 @@
         <v>44743</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42073,7 +42081,7 @@
         <v>44806</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42146,7 +42154,7 @@
         <v>44806</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42219,7 +42227,7 @@
         <v>45714</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42292,7 +42300,7 @@
         <v>46275</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42365,7 +42373,7 @@
         <v>44991</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42443,7 +42451,7 @@
         <v>46274</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42516,7 +42524,7 @@
         <v>45250</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42589,7 +42597,7 @@
         <v>45580</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42662,7 +42670,7 @@
         <v>46232</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42735,7 +42743,7 @@
         <v>45281</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42808,7 +42816,7 @@
         <v>44957</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42881,7 +42889,7 @@
         <v>45265</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42959,7 +42967,7 @@
         <v>45476</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43032,7 +43040,7 @@
         <v>45476</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43105,7 +43113,7 @@
         <v>46237</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43183,7 +43191,7 @@
         <v>45166</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43261,7 +43269,7 @@
         <v>46281</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43334,7 +43342,7 @@
         <v>44855</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43407,7 +43415,7 @@
         <v>44890</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43485,7 +43493,7 @@
         <v>46281</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43558,7 +43566,7 @@
         <v>46239</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43636,7 +43644,7 @@
         <v>46282</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43709,7 +43717,7 @@
         <v>44945</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43787,7 +43795,7 @@
         <v>46189</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43860,7 +43868,7 @@
         <v>44903</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43938,7 +43946,7 @@
         <v>46070</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44011,7 +44019,7 @@
         <v>46286</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44089,7 +44097,7 @@
         <v>46286</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44167,7 +44175,7 @@
         <v>45251</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44240,7 +44248,7 @@
         <v>46244</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44318,7 +44326,7 @@
         <v>46287</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44396,7 +44404,7 @@
         <v>46181</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44469,7 +44477,7 @@
         <v>46288</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44542,7 +44550,7 @@
         <v>45512</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44615,7 +44623,7 @@
         <v>45723</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44688,7 +44696,7 @@
         <v>44497</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44761,7 +44769,7 @@
         <v>44502</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44834,7 +44842,7 @@
         <v>46288</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44907,7 +44915,7 @@
         <v>46286</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44980,7 +44988,7 @@
         <v>45323</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45053,7 +45061,7 @@
         <v>46288</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45126,7 +45134,7 @@
         <v>45639</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45199,7 +45207,7 @@
         <v>44609</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45277,7 +45285,7 @@
         <v>44952</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45350,7 +45358,7 @@
         <v>46248</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45423,7 +45431,7 @@
         <v>44747</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45496,7 +45504,7 @@
         <v>45152</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45569,7 +45577,7 @@
         <v>45099</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45647,7 +45655,7 @@
         <v>45629</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45720,7 +45728,7 @@
         <v>45000</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45798,7 +45806,7 @@
         <v>45000</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45876,7 +45884,7 @@
         <v>46252</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45949,7 +45957,7 @@
         <v>44819</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46027,7 +46035,7 @@
         <v>45762</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46100,7 +46108,7 @@
         <v>46251</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46178,7 +46186,7 @@
         <v>45163</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46251,7 +46259,7 @@
         <v>46296</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46329,7 +46337,7 @@
         <v>46296</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46407,7 +46415,7 @@
         <v>46296</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46485,7 +46493,7 @@
         <v>46296</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46563,7 +46571,7 @@
         <v>46297</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46636,7 +46644,7 @@
         <v>46288</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46709,7 +46717,7 @@
         <v>46297</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46787,7 +46795,7 @@
         <v>45107</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46860,7 +46868,7 @@
         <v>45685</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46933,7 +46941,7 @@
         <v>46258</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47006,7 +47014,7 @@
         <v>45776</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47079,7 +47087,7 @@
         <v>45776</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47152,7 +47160,7 @@
         <v>45782</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47230,7 +47238,7 @@
         <v>45782</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47308,7 +47316,7 @@
         <v>45562</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47381,7 +47389,7 @@
         <v>46301</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47454,7 +47462,7 @@
         <v>45578</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47527,7 +47535,7 @@
         <v>46303</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47605,7 +47613,7 @@
         <v>46260</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47678,7 +47686,7 @@
         <v>45574</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47751,7 +47759,7 @@
         <v>45791</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47824,7 +47832,7 @@
         <v>45342</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47897,7 +47905,7 @@
         <v>45433</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47970,7 +47978,7 @@
         <v>45351</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48043,7 +48051,7 @@
         <v>45793</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48121,7 +48129,7 @@
         <v>46307</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48194,7 +48202,7 @@
         <v>45579</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48267,7 +48275,7 @@
         <v>44571</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48340,7 +48348,7 @@
         <v>45266</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48413,7 +48421,7 @@
         <v>46262</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48486,7 +48494,7 @@
         <v>45516</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48559,7 +48567,7 @@
         <v>45799</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48637,7 +48645,7 @@
         <v>45139</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48710,7 +48718,7 @@
         <v>46049</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48783,7 +48791,7 @@
         <v>46304</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48856,7 +48864,7 @@
         <v>45803</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48929,7 +48937,7 @@
         <v>45762</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49002,7 +49010,7 @@
         <v>45800</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49080,7 +49088,7 @@
         <v>46309</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49153,7 +49161,7 @@
         <v>45805</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49226,7 +49234,7 @@
         <v>45630</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49299,7 +49307,7 @@
         <v>46265</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49377,7 +49385,7 @@
         <v>45205</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49450,7 +49458,7 @@
         <v>45811</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49523,7 +49531,7 @@
         <v>46309</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49596,7 +49604,7 @@
         <v>45812</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49669,7 +49677,7 @@
         <v>46309</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49742,7 +49750,7 @@
         <v>45812</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49815,7 +49823,7 @@
         <v>46309</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49888,7 +49896,7 @@
         <v>45825</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49961,7 +49969,7 @@
         <v>45825</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50034,7 +50042,7 @@
         <v>45825</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50107,7 +50115,7 @@
         <v>45825</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50180,7 +50188,7 @@
         <v>45824</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50258,7 +50266,7 @@
         <v>45826</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50336,7 +50344,7 @@
         <v>45833</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50414,7 +50422,7 @@
         <v>45833</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50492,7 +50500,7 @@
         <v>45833</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50570,7 +50578,7 @@
         <v>45833</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50648,7 +50656,7 @@
         <v>45833</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50726,7 +50734,7 @@
         <v>45834</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50799,7 +50807,7 @@
         <v>45811</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50872,7 +50880,7 @@
         <v>45834</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50945,7 +50953,7 @@
         <v>45837</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51023,7 +51031,7 @@
         <v>45837</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51101,7 +51109,7 @@
         <v>45840</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51174,7 +51182,7 @@
         <v>45840</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51247,7 +51255,7 @@
         <v>45749</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51320,7 +51328,7 @@
         <v>45848</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51393,7 +51401,7 @@
         <v>45848</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51466,7 +51474,7 @@
         <v>45853</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51544,7 +51552,7 @@
         <v>44973</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51617,7 +51625,7 @@
         <v>45741</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51690,7 +51698,7 @@
         <v>45793</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51763,7 +51771,7 @@
         <v>45729</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51836,7 +51844,7 @@
         <v>45574</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51909,7 +51917,7 @@
         <v>45741</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51982,7 +51990,7 @@
         <v>45874</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52055,7 +52063,7 @@
         <v>45874</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52128,7 +52136,7 @@
         <v>45874</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52201,7 +52209,7 @@
         <v>45874</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52274,7 +52282,7 @@
         <v>45880</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52347,7 +52355,7 @@
         <v>44393</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52420,7 +52428,7 @@
         <v>45323</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52498,7 +52506,7 @@
         <v>45733</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52576,7 +52584,7 @@
         <v>45755</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52649,7 +52657,7 @@
         <v>45793</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52727,7 +52735,7 @@
         <v>46078</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52805,7 +52813,7 @@
         <v>46073</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52878,7 +52886,7 @@
         <v>46093</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52956,7 +52964,7 @@
         <v>46156</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53029,7 +53037,7 @@
         <v>46267</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>

--- a/Översikt HÄRNÖSAND.xlsx
+++ b/Översikt HÄRNÖSAND.xlsx
@@ -601,7 +601,7 @@
         <v>45335</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>45978</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>46288</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>45328</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>46044</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>45763</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>46189</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>45938</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>44686</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>45546</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>45394</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>45930</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>45763</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45139</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>45805</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>45484</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>45826</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>45616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>45082</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45027</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>46183</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>44874</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>45188</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>45593</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>45957</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>45548</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>45567</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>45352</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>45593</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>44979</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>46176</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>45971</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>45513</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>45477</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>46251</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>45848</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>45560</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>45314</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         <v>45323</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>45790</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>44686</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>44755</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>45930</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>46003</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>46244</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>45617</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         <v>45182</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>45355</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>45596</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>45526</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>44664</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>46141</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>45930</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>45376</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>45910</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>45267</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>45967</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         <v>46244</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>44874</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>45847</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>45513</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>46303</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>45575</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>45618</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>45793</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>45996</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>44676</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>44585</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8592,7 +8592,7 @@
         <v>44655</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>45919</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>45554</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>45276</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>46176</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>46189</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>46184</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>45428</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>45352</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>46213</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>46031</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>45805</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>45805</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>45811</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>45837</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>46127</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>46191</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         <v>45583</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>45008</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>44837</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10747,7 +10747,7 @@
         <v>45649</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>44559</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>45350</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>45372</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>45456</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>44874</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>44664</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>44806</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>44846</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>44875</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>44532</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>44608</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>44720</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>44600</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>44824</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>44734</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>44512</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>44517</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v>44728</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>44664</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>44804</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>44512</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>44503</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>44735</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>44581</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>44848</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
         <v>44672</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>44652</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>44515</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13059,7 +13059,7 @@
         <v>44664</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>44616</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>44496</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>44532</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
         <v>44512</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13424,7 +13424,7 @@
         <v>44571</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>44664</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>44536</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>44522</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>44585</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13789,7 +13789,7 @@
         <v>45888</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>45887</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13940,7 +13940,7 @@
         <v>45483</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>44889</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>45289</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>44845</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>45044</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>45761</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>45887</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>45890</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>45890</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         <v>45072</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>45891</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         <v>45328</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>45328</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>45194</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>45289</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>45897</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>44580</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>45476</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>45901</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>45006</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>45531</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>45803</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>45409</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>45300</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>46161</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
         <v>45832</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>46161</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>46161</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         <v>45035</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16097,7 +16097,7 @@
         <v>44987</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>46161</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         <v>46161</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>46162</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>46161</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
         <v>45786</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
         <v>45813</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>46162</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>45790</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>46161</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>46161</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>45915</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>44869</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>45915</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>45917</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>45392</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>45919</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>46168</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>45922</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17514,7 +17514,7 @@
         <v>45985</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>46167</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>45922</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17733,7 +17733,7 @@
         <v>45923</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         <v>45924</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>45638</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>45924</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18030,7 +18030,7 @@
         <v>45924</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18103,7 +18103,7 @@
         <v>46167</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>45924</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>45924</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>46149</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>45000</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18473,7 +18473,7 @@
         <v>45000</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>45250</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>46165</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>46170</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>45910</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>45044</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>45126</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>45919</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19072,7 +19072,7 @@
         <v>46170</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19145,7 +19145,7 @@
         <v>45936</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>46175</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19291,7 +19291,7 @@
         <v>46175</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>46094</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>45936</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19510,7 +19510,7 @@
         <v>45936</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>45937</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>46175</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>45939</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>45762</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>45180</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>46174</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20031,7 +20031,7 @@
         <v>44806</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>44806</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>46177</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
         <v>45580</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>46177</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>45147</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20469,7 +20469,7 @@
         <v>46177</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>46177</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         <v>44809</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>46177</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>44853</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>46178</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>46181</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>46178</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>45251</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>45482</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>46182</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21277,7 +21277,7 @@
         <v>46184</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>45769</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>45646</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>45107</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>45959</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21647,7 +21647,7 @@
         <v>45959</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>46189</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>45800</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
         <v>46188</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>46189</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>46189</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22085,7 +22085,7 @@
         <v>46189</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>46189</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>46191</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>46190</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>46195</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>46195</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22528,7 +22528,7 @@
         <v>46195</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>45723</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>45793</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>46195</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>46195</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22898,7 +22898,7 @@
         <v>46195</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>45097</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>45972</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>44855</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>45972</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>45629</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
         <v>45975</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>45978</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>45323</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23575,7 +23575,7 @@
         <v>45578</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23648,7 +23648,7 @@
         <v>45578</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23721,7 +23721,7 @@
         <v>44951</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45975</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>45979</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>45979</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>45979</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>45531</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>45979</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>45979</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>45512</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>45281</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>45979</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24554,7 +24554,7 @@
         <v>45979</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24627,7 +24627,7 @@
         <v>44867</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>46203</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>45981</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>45981</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>46204</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25007,7 +25007,7 @@
         <v>46204</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25080,7 +25080,7 @@
         <v>46205</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25153,7 +25153,7 @@
         <v>45281</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25226,7 +25226,7 @@
         <v>45729</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25299,7 +25299,7 @@
         <v>46204</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>46204</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>46205</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>46205</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25591,7 +25591,7 @@
         <v>45800</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25664,7 +25664,7 @@
         <v>45489</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25742,7 +25742,7 @@
         <v>46206</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>46206</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>46206</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25961,7 +25961,7 @@
         <v>46206</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>45987</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26107,7 +26107,7 @@
         <v>46209</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>46211</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         <v>45376</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         <v>46211</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26399,7 +26399,7 @@
         <v>45730</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>46213</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26545,7 +26545,7 @@
         <v>45992</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>45348</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26691,7 +26691,7 @@
         <v>46213</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         <v>45462</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>46215</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26910,7 +26910,7 @@
         <v>46215</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>45126</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27056,7 +27056,7 @@
         <v>45999</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27129,7 +27129,7 @@
         <v>45999</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27202,7 +27202,7 @@
         <v>45999</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27275,7 +27275,7 @@
         <v>46219</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27348,7 +27348,7 @@
         <v>46219</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27421,7 +27421,7 @@
         <v>46219</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27494,7 +27494,7 @@
         <v>45685</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>46000</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27640,7 +27640,7 @@
         <v>45776</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>46161</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27786,7 +27786,7 @@
         <v>46203</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27859,7 +27859,7 @@
         <v>45776</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27932,7 +27932,7 @@
         <v>46213</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28005,7 +28005,7 @@
         <v>45273</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>45782</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>45782</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28234,7 +28234,7 @@
         <v>45562</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28307,7 +28307,7 @@
         <v>46232</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>46013</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>46237</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28531,7 +28531,7 @@
         <v>44952</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28604,7 +28604,7 @@
         <v>45578</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28677,7 +28677,7 @@
         <v>46282</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>46281</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28823,7 +28823,7 @@
         <v>46024</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28896,7 +28896,7 @@
         <v>46024</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>46023</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>46024</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29115,7 +29115,7 @@
         <v>46239</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29193,7 +29193,7 @@
         <v>46023</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29266,7 +29266,7 @@
         <v>46024</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>46281</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>46026</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>46029</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>46029</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29631,7 +29631,7 @@
         <v>46029</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29704,7 +29704,7 @@
         <v>46030</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>46029</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>46030</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29923,7 +29923,7 @@
         <v>45791</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>45342</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
         <v>46034</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>45574</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30215,7 +30215,7 @@
         <v>45433</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>46286</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30366,7 +30366,7 @@
         <v>45351</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30439,7 +30439,7 @@
         <v>46181</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>46035</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>46038</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>46286</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>46038</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>44571</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30882,7 +30882,7 @@
         <v>46042</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>46070</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>45579</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>46288</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31174,7 +31174,7 @@
         <v>45793</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>45266</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31325,7 +31325,7 @@
         <v>46286</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>45516</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31471,7 +31471,7 @@
         <v>45139</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31544,7 +31544,7 @@
         <v>46288</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31617,7 +31617,7 @@
         <v>46244</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31695,7 +31695,7 @@
         <v>46287</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31773,7 +31773,7 @@
         <v>45799</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31851,7 +31851,7 @@
         <v>46045</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>46189</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>46288</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>45800</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>46052</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>45803</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32294,7 +32294,7 @@
         <v>46052</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32367,7 +32367,7 @@
         <v>45762</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32440,7 +32440,7 @@
         <v>46052</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32518,7 +32518,7 @@
         <v>45805</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>46055</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32664,7 +32664,7 @@
         <v>46056</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>45630</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32810,7 +32810,7 @@
         <v>45205</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32883,7 +32883,7 @@
         <v>45811</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>45812</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>45812</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>46063</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33175,7 +33175,7 @@
         <v>46065</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33253,7 +33253,7 @@
         <v>46065</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33331,7 +33331,7 @@
         <v>46065</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33409,7 +33409,7 @@
         <v>46248</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33482,7 +33482,7 @@
         <v>46065</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>46065</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>46070</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>45511</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33774,7 +33774,7 @@
         <v>46072</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33847,7 +33847,7 @@
         <v>45243</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33920,7 +33920,7 @@
         <v>46071</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33993,7 +33993,7 @@
         <v>46071</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34066,7 +34066,7 @@
         <v>46072</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34139,7 +34139,7 @@
         <v>46296</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34217,7 +34217,7 @@
         <v>45824</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34295,7 +34295,7 @@
         <v>46077</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34368,7 +34368,7 @@
         <v>46252</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>46296</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>45825</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34592,7 +34592,7 @@
         <v>45825</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>45825</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34738,7 +34738,7 @@
         <v>45825</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34811,7 +34811,7 @@
         <v>46296</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34889,7 +34889,7 @@
         <v>45826</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34967,7 +34967,7 @@
         <v>46296</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35045,7 +35045,7 @@
         <v>46080</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35118,7 +35118,7 @@
         <v>44881</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35196,7 +35196,7 @@
         <v>46085</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>46064</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44865</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>45833</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35498,7 +35498,7 @@
         <v>45833</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>45834</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35649,7 +35649,7 @@
         <v>45833</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35727,7 +35727,7 @@
         <v>46087</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35805,7 +35805,7 @@
         <v>45833</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35883,7 +35883,7 @@
         <v>46297</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35961,7 +35961,7 @@
         <v>45833</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36039,7 +36039,7 @@
         <v>45834</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36112,7 +36112,7 @@
         <v>46091</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>46091</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>46091</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36331,7 +36331,7 @@
         <v>45811</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36404,7 +36404,7 @@
         <v>46091</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>46091</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>45837</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36628,7 +36628,7 @@
         <v>45840</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>46251</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>46094</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36857,7 +36857,7 @@
         <v>46094</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36930,7 +36930,7 @@
         <v>45840</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37003,7 +37003,7 @@
         <v>45476</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37076,7 +37076,7 @@
         <v>46297</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37149,7 +37149,7 @@
         <v>46288</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>44937</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>45531</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37368,7 +37368,7 @@
         <v>46101</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37446,7 +37446,7 @@
         <v>45848</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>45848</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37592,7 +37592,7 @@
         <v>46104</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37665,7 +37665,7 @@
         <v>46105</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37738,7 +37738,7 @@
         <v>46105</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>46105</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>46301</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>46105</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38030,7 +38030,7 @@
         <v>46258</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>46107</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38176,7 +38176,7 @@
         <v>45749</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38249,7 +38249,7 @@
         <v>46107</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38322,7 +38322,7 @@
         <v>46107</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>46106</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38468,7 +38468,7 @@
         <v>45853</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38546,7 +38546,7 @@
         <v>45793</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>45729</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>45741</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38765,7 +38765,7 @@
         <v>44973</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38838,7 +38838,7 @@
         <v>46113</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38916,7 +38916,7 @@
         <v>45574</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>45741</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>44498</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39135,7 +39135,7 @@
         <v>44853</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39208,7 +39208,7 @@
         <v>46120</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39281,7 +39281,7 @@
         <v>45874</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39354,7 +39354,7 @@
         <v>46122</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39427,7 +39427,7 @@
         <v>45874</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39500,7 +39500,7 @@
         <v>45729</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39573,7 +39573,7 @@
         <v>45874</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39646,7 +39646,7 @@
         <v>45874</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>46127</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39792,7 +39792,7 @@
         <v>46303</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39870,7 +39870,7 @@
         <v>46260</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>46304</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40016,7 +40016,7 @@
         <v>45880</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>45293</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>46132</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40235,7 +40235,7 @@
         <v>45562</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40308,7 +40308,7 @@
         <v>44531</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>45884</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>46133</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>46049</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>46133</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40673,7 +40673,7 @@
         <v>46265</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40751,7 +40751,7 @@
         <v>46307</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40824,7 +40824,7 @@
         <v>46262</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>45209</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>46309</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41048,7 +41048,7 @@
         <v>44897</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>45558</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41194,7 +41194,7 @@
         <v>45904</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41267,7 +41267,7 @@
         <v>46309</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41340,7 +41340,7 @@
         <v>46309</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41413,7 +41413,7 @@
         <v>45526</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41486,7 +41486,7 @@
         <v>44881</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41564,7 +41564,7 @@
         <v>46309</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41637,7 +41637,7 @@
         <v>46065</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>44894</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41788,7 +41788,7 @@
         <v>46314</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>44609</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>45576</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42017,7 +42017,7 @@
         <v>46316</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42095,7 +42095,7 @@
         <v>45771</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42168,7 +42168,7 @@
         <v>46315</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42241,7 +42241,7 @@
         <v>46316</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>45320</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42392,7 +42392,7 @@
         <v>46315</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42470,7 +42470,7 @@
         <v>45825</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42543,7 +42543,7 @@
         <v>45523</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42616,7 +42616,7 @@
         <v>46274</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42689,7 +42689,7 @@
         <v>45840</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42762,7 +42762,7 @@
         <v>45887</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42835,7 +42835,7 @@
         <v>46317</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42913,7 +42913,7 @@
         <v>46072</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42986,7 +42986,7 @@
         <v>46024</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43059,7 +43059,7 @@
         <v>46275</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43132,7 +43132,7 @@
         <v>46142</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43205,7 +43205,7 @@
         <v>45701</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>46142</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43356,7 +43356,7 @@
         <v>45757</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>46317</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>45390</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43580,7 +43580,7 @@
         <v>45505</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>44755</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>46150</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         <v>46107</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43877,7 +43877,7 @@
         <v>46153</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43950,7 +43950,7 @@
         <v>44747</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44023,7 +44023,7 @@
         <v>46153</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44096,7 +44096,7 @@
         <v>45622</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44169,7 +44169,7 @@
         <v>46155</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>44732</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>45930</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>46160</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>45293</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44534,7 +44534,7 @@
         <v>44890</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>45015</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44690,7 +44690,7 @@
         <v>45314</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44763,7 +44763,7 @@
         <v>44971</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>45638</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         <v>44743</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44987,7 +44987,7 @@
         <v>44847</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45065,7 +45065,7 @@
         <v>45667</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45138,7 +45138,7 @@
         <v>45645</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45168</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45284,7 +45284,7 @@
         <v>44853</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
         <v>45138</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45430,7 +45430,7 @@
         <v>45545</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45503,7 +45503,7 @@
         <v>44980</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45576,7 +45576,7 @@
         <v>45678</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45654,7 +45654,7 @@
         <v>45764</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45732,7 +45732,7 @@
         <v>44971</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45810,7 +45810,7 @@
         <v>44936</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45883,7 +45883,7 @@
         <v>45769</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45961,7 +45961,7 @@
         <v>45685</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46034,7 +46034,7 @@
         <v>45749</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46107,7 +46107,7 @@
         <v>45749</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46180,7 +46180,7 @@
         <v>44603</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46253,7 +46253,7 @@
         <v>45044</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46331,7 +46331,7 @@
         <v>45203</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46404,7 +46404,7 @@
         <v>45106</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46482,7 +46482,7 @@
         <v>45714</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46555,7 +46555,7 @@
         <v>44596</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46633,7 +46633,7 @@
         <v>45099</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46711,7 +46711,7 @@
         <v>45723</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46784,7 +46784,7 @@
         <v>45562</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46862,7 +46862,7 @@
         <v>44991</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46940,7 +46940,7 @@
         <v>45293</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47013,7 +47013,7 @@
         <v>44497</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47086,7 +47086,7 @@
         <v>45329</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47159,7 +47159,7 @@
         <v>44847</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47237,7 +47237,7 @@
         <v>45352</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47315,7 +47315,7 @@
         <v>45265</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47393,7 +47393,7 @@
         <v>45281</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47466,7 +47466,7 @@
         <v>45409</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47539,7 +47539,7 @@
         <v>44819</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47617,7 +47617,7 @@
         <v>45278</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47695,7 +47695,7 @@
         <v>45502</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>44791</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47841,7 +47841,7 @@
         <v>45418</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47914,7 +47914,7 @@
         <v>44502</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47987,7 +47987,7 @@
         <v>45126</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48060,7 +48060,7 @@
         <v>45228</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48133,7 +48133,7 @@
         <v>45161</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48211,7 +48211,7 @@
         <v>45390</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>45148</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48357,7 +48357,7 @@
         <v>45173</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48435,7 +48435,7 @@
         <v>45342</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48508,7 +48508,7 @@
         <v>44496</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48581,7 +48581,7 @@
         <v>45405</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>45409</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48727,7 +48727,7 @@
         <v>45334</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48800,7 +48800,7 @@
         <v>45628</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>44641</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48946,7 +48946,7 @@
         <v>45168</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49019,7 +49019,7 @@
         <v>45512</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>45639</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49165,7 +49165,7 @@
         <v>45147</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49238,7 +49238,7 @@
         <v>45595</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49311,7 +49311,7 @@
         <v>45595</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49384,7 +49384,7 @@
         <v>45616</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49462,7 +49462,7 @@
         <v>44676</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49535,7 +49535,7 @@
         <v>44694</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49613,7 +49613,7 @@
         <v>45617</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49686,7 +49686,7 @@
         <v>45762</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49759,7 +49759,7 @@
         <v>44617</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49832,7 +49832,7 @@
         <v>45428</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49905,7 +49905,7 @@
         <v>45163</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45152</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50051,7 +50051,7 @@
         <v>44858</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50124,7 +50124,7 @@
         <v>45163</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50197,7 +50197,7 @@
         <v>44706</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50270,7 +50270,7 @@
         <v>44728</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50343,7 +50343,7 @@
         <v>45181</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50416,7 +50416,7 @@
         <v>44728</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>45189</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50562,7 +50562,7 @@
         <v>45699</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50635,7 +50635,7 @@
         <v>45168</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50708,7 +50708,7 @@
         <v>44726</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>45723</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50854,7 +50854,7 @@
         <v>45166</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50932,7 +50932,7 @@
         <v>45251</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51005,7 +51005,7 @@
         <v>45350</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51083,7 +51083,7 @@
         <v>45293</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51156,7 +51156,7 @@
         <v>45320</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51229,7 +51229,7 @@
         <v>45231</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51302,7 +51302,7 @@
         <v>44747</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51375,7 +51375,7 @@
         <v>45072</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51448,7 +51448,7 @@
         <v>45313</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51521,7 +51521,7 @@
         <v>45366</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51594,7 +51594,7 @@
         <v>44853</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51667,7 +51667,7 @@
         <v>45749</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51740,7 +51740,7 @@
         <v>45757</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51813,7 +51813,7 @@
         <v>44792</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51886,7 +51886,7 @@
         <v>45733</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51959,7 +51959,7 @@
         <v>45496</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52032,7 +52032,7 @@
         <v>45352</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52110,7 +52110,7 @@
         <v>45091</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52183,7 +52183,7 @@
         <v>45280</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52256,7 +52256,7 @@
         <v>45462</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52329,7 +52329,7 @@
         <v>44875</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52402,7 +52402,7 @@
         <v>45482</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52480,7 +52480,7 @@
         <v>45496</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52553,7 +52553,7 @@
         <v>44957</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52626,7 +52626,7 @@
         <v>44903</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52704,7 +52704,7 @@
         <v>44945</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52782,7 +52782,7 @@
         <v>45376</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52855,7 +52855,7 @@
         <v>44393</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52928,7 +52928,7 @@
         <v>45323</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53006,7 +53006,7 @@
         <v>45733</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53084,7 +53084,7 @@
         <v>45755</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53157,7 +53157,7 @@
         <v>46078</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53235,7 +53235,7 @@
         <v>46073</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53308,7 +53308,7 @@
         <v>46093</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53386,7 +53386,7 @@
         <v>46156</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53459,7 +53459,7 @@
         <v>46267</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
